--- a/data_cripto/top_flow.xlsx
+++ b/data_cripto/top_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,482 +513,450 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qx9n80t5q7tfmutzaj0ramzzzsvtveara68zntc</t>
+          <t>https://intel.arkm.com/explorer/address/0x4200000000000000000000000000000000000006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bc1qx9n80t5q7tfmutzaj0ramzzzsvtveara68zntc</t>
+          <t>0x4200000000000000000000000000000000000006</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kraken</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>5181263782.136086</v>
+        <v>5486875032.853655</v>
       </c>
       <c r="L2" t="n">
-        <v>5661058696.59375</v>
+        <v>5473830598.234919</v>
       </c>
       <c r="M2" t="n">
-        <v>58722.24818257</v>
+        <v>1811070.080476356</v>
       </c>
       <c r="N2" t="n">
-        <v>64186.61890506</v>
+        <v>1807168.437985781</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1KbDEg1tDz2ErYgaDbaDhhawnLrSQFaFx5</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1KbDEg1tDz2ErYgaDbaDhhawnLrSQFaFx5</t>
+          <t>0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Binance Deposit</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4332441241.253247</v>
+        <v>3793317049.74327</v>
       </c>
       <c r="L3" t="n">
-        <v>4316835249.657695</v>
+        <v>3763358336.982445</v>
       </c>
       <c r="M3" t="n">
-        <v>48624.35701303</v>
+        <v>1253831.249362666</v>
       </c>
       <c r="N3" t="n">
-        <v>48450.59731041</v>
+        <v>1244145.76947663</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/34PhCF947JMQtCn7FD1J3Xd3c2VSxAwda8</t>
+          <t>https://intel.arkm.com/explorer/address/0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34PhCF947JMQtCn7FD1J3Xd3c2VSxAwda8</t>
+          <t>0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>jaredfromsubway (MEV)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>mev</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MEV Bot</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K4" t="n">
-        <v>840646976</v>
+        <v>2429883191.866974</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2429886213.67873</v>
       </c>
       <c r="M4" t="n">
-        <v>9551.069985599999</v>
+        <v>801998.7975301587</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>801999.7653357279</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qjasf9z3h7w3jspkhtgatgpyvvzgpa2wwd2lr0eh5tx44reyn2k7sfc27a4</t>
+          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bc1qjasf9z3h7w3jspkhtgatgpyvvzgpa2wwd2lr0eh5tx44reyn2k7sfc27a4</t>
+          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tether</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stablecoin</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://tether.to/</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bitcoin Reserves</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>778702208.4915583</v>
+        <v>1380449619.705878</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1362669735.491392</v>
       </c>
       <c r="M5" t="n">
-        <v>8888.888894260001</v>
+        <v>453489.1777541857</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>448556.16924823</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/12DezRFkKToAiLTDNru1g7FuvtAWMwCZ7N</t>
+          <t>https://intel.arkm.com/explorer/address/0xb23639385a208265f4891A89C27F37b084532DC3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12DezRFkKToAiLTDNru1g7FuvtAWMwCZ7N</t>
+          <t>0xb23639385a208265f4891A89C27F37b084532DC3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>8519351280.572376</v>
+        <v>975266241.335169</v>
       </c>
       <c r="L6" t="n">
-        <v>8517370211.078125</v>
+        <v>975266240.7557733</v>
       </c>
       <c r="M6" t="n">
-        <v>94755.14042914999</v>
+        <v>323386.2973543156</v>
       </c>
       <c r="N6" t="n">
-        <v>94755.13992915</v>
+        <v>323386.2973543155</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q42kvqt0e3f27qhd2ucnprarl5ywpuj7tu0h9v2</t>
+          <t>https://intel.arkm.com/explorer/address/0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bc1q42kvqt0e3f27qhd2ucnprarl5ywpuj7tu0h9v2</t>
+          <t>0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>FalconX</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://falconx.io/</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Wrapped Ether (WETH)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1252858640.240402</v>
+        <v>20259438932.99068</v>
       </c>
       <c r="L7" t="n">
-        <v>1200412245.446109</v>
+        <v>20367055258.39912</v>
       </c>
       <c r="M7" t="n">
-        <v>14256.43421203</v>
+        <v>6642242.125249802</v>
       </c>
       <c r="N7" t="n">
-        <v>13640.51676859</v>
+        <v>6672559.979974744</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qcfkga3lyvflf53vt0n2hjd9mr03870pvjw2z72</t>
+          <t>https://intel.arkm.com/explorer/address/0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bc1qcfkga3lyvflf53vt0n2hjd9mr03870pvjw2z72</t>
+          <t>0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>custodian</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://paxos.com</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Eth2 Beacon Deposit Contract</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9743785746.779785</v>
       </c>
       <c r="L8" t="n">
-        <v>637261120</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3185819.797795997</v>
       </c>
       <c r="N8" t="n">
-        <v>6757.16150495</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qzzfkyk3z94fhk26fu545fchk5v947ghhjfuc2t</t>
+          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bc1qzzfkyk3z94fhk26fu545fchk5v947ghhjfuc2t</t>
+          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -998,167 +966,201 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K9" t="n">
-        <v>1368462592</v>
+        <v>9369390178.64414</v>
       </c>
       <c r="L9" t="n">
-        <v>1363357440</v>
+        <v>9091454900.127726</v>
       </c>
       <c r="M9" t="n">
-        <v>15611.91659811</v>
+        <v>3100793.821522709</v>
       </c>
       <c r="N9" t="n">
-        <v>15611.91659811</v>
+        <v>3006182.88541323</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qk0ukgq09wfuj43lfwrxc3cvcujrk5akvp0lqll</t>
+          <t>https://intel.arkm.com/explorer/address/0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bc1qk0ukgq09wfuj43lfwrxc3cvcujrk5akvp0lqll</t>
+          <t>0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Uniswap v4 Positions NFT (UNI-V4-POSM)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K10" t="n">
-        <v>1530858476</v>
+        <v>1193275630.128648</v>
       </c>
       <c r="L10" t="n">
-        <v>1478899958.034462</v>
+        <v>1193275629.786555</v>
       </c>
       <c r="M10" t="n">
-        <v>16895.22958233</v>
+        <v>394289.2269956106</v>
       </c>
       <c r="N10" t="n">
-        <v>16261.55363876</v>
+        <v>394289.2269956106</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qn2cpj0hrl37wqh5q94kwrlhtj2lx8ahtw7ef5rg35tswxsqtvufqfmmrq2</t>
+          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bc1qn2cpj0hrl37wqh5q94kwrlhtj2lx8ahtw7ef5rg35tswxsqtvufqfmmrq2</t>
+          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Market Maker</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1051530232.55556</v>
+        <v>3062792793.929688</v>
       </c>
       <c r="L11" t="n">
-        <v>1026853849.833294</v>
+        <v>3062702158.183423</v>
       </c>
       <c r="M11" t="n">
-        <v>11738.0355311</v>
+        <v>1011451.927096179</v>
       </c>
       <c r="N11" t="n">
-        <v>11472.53813037</v>
+        <v>1011445.095432548</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3MsfxyCEY5B4NUwKP66iqsbZsS5XRDm3Vj</t>
+          <t>https://intel.arkm.com/explorer/address/0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3MsfxyCEY5B4NUwKP66iqsbZsS5XRDm3Vj</t>
+          <t>0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
@@ -1168,51 +1170,53 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>713136640</v>
+        <v>1702646058.536583</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1702645343.315669</v>
       </c>
       <c r="M12" t="n">
-        <v>8144.91996985</v>
+        <v>563496.1170835318</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>563495.8795240488</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/38ACfxHJwKnKFW2Evmnk58Aj9CBF7t3T88</t>
+          <t>https://intel.arkm.com/explorer/address/0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38ACfxHJwKnKFW2Evmnk58Aj9CBF7t3T88</t>
+          <t>0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1222,57 +1226,67 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K13" t="n">
-        <v>574414355.6092997</v>
+        <v>1393302544.028083</v>
       </c>
       <c r="L13" t="n">
-        <v>631692726.9306631</v>
+        <v>1395170004.140732</v>
       </c>
       <c r="M13" t="n">
-        <v>6488.57436362</v>
+        <v>456792.2656770762</v>
       </c>
       <c r="N13" t="n">
-        <v>7096.85830225</v>
+        <v>457242.1943745955</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q0y5m6wdxjre0fs9m3u0j3pv2fcja6qw3a2f6ql</t>
+          <t>https://intel.arkm.com/explorer/address/0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bc1q0y5m6wdxjre0fs9m3u0j3pv2fcja6qw3a2f6ql</t>
+          <t>0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1282,309 +1296,315 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1316808887.357698</v>
       </c>
       <c r="L14" t="n">
-        <v>1390938416</v>
+        <v>1326095348.503178</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>434123.9310645718</v>
       </c>
       <c r="N14" t="n">
-        <v>15972.00001596</v>
+        <v>437033.0216208</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3LUATjKp4YfmCSSiN1h3juwrqNTyksXAjp</t>
+          <t>https://intel.arkm.com/explorer/address/0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3LUATjKp4YfmCSSiN1h3juwrqNTyksXAjp</t>
+          <t>0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Fidelity FBTC ETF Inflows</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.fidelity.com/</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>FBTC Inflows (Fidelity Custody Deposit)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1211731899.873139</v>
       </c>
       <c r="L15" t="n">
-        <v>674422062.8809814</v>
+        <v>1211731899.368315</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>399963.4473773648</v>
       </c>
       <c r="N15" t="n">
-        <v>7603.32414266</v>
+        <v>399963.4473773648</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qm34lsc65zpw79lxes69zkqmk6ee3ewf0j77s3h</t>
+          <t>https://intel.arkm.com/explorer/address/0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bc1qm34lsc65zpw79lxes69zkqmk6ee3ewf0j77s3h</t>
+          <t>0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Coinbase Prime Deposit</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>15516427931.15735</v>
+        <v>941419448.3637171</v>
       </c>
       <c r="L16" t="n">
-        <v>15656132518.51617</v>
+        <v>928499614</v>
       </c>
       <c r="M16" t="n">
-        <v>174332.05054857</v>
+        <v>313972.6993268693</v>
       </c>
       <c r="N16" t="n">
-        <v>175819.491127</v>
+        <v>308954.4792646671</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1p2mlwrss9tmvtfvu0tcxul2h0w67ej8vyjpj3ksctt67vd9r752ksqx6uqm</t>
+          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bc1p2mlwrss9tmvtfvu0tcxul2h0w67ej8vyjpj3ksctt67vd9r752ksqx6uqm</t>
+          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Binance Deposit</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K17" t="n">
-        <v>833113965.0117188</v>
+        <v>4631714624.43821</v>
       </c>
       <c r="L17" t="n">
-        <v>754659271.2068161</v>
+        <v>4626269745.695312</v>
       </c>
       <c r="M17" t="n">
-        <v>9364.59320822</v>
+        <v>1527482.304299085</v>
       </c>
       <c r="N17" t="n">
-        <v>8476.64192532</v>
+        <v>1525271.742356705</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/352zzNHvsBTaUUNzqB5xbMo8EYdpvHJQB2</t>
+          <t>https://intel.arkm.com/explorer/address/0xd01607c3C5eCABa394D8be377a08590149325722</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>352zzNHvsBTaUUNzqB5xbMo8EYdpvHJQB2</t>
+          <t>0xd01607c3C5eCABa394D8be377a08590149325722</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>lending-decentralized</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>https://aave.com</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>WrappedTokenGatewayV3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K18" t="n">
-        <v>6691692133.189903</v>
+        <v>3233974767.903385</v>
       </c>
       <c r="L18" t="n">
-        <v>6699227111.416937</v>
+        <v>3233974769.579787</v>
       </c>
       <c r="M18" t="n">
-        <v>75158.69773515</v>
+        <v>1078157.994433303</v>
       </c>
       <c r="N18" t="n">
-        <v>75232.82282282</v>
+        <v>1078157.994433303</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q9n37v8rdr2tla849xp2znxyp70lnqu8rw0m02a</t>
+          <t>https://intel.arkm.com/explorer/address/0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bc1q9n37v8rdr2tla849xp2znxyp70lnqu8rw0m02a</t>
+          <t>0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Coinbase Prime</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1594,125 +1614,125 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://www.coinbase.com/prime</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1408247624</v>
+        <v>3158175817.574128</v>
       </c>
       <c r="L19" t="n">
-        <v>1741029888</v>
+        <v>3166011420.527831</v>
       </c>
       <c r="M19" t="n">
-        <v>16172.69578732</v>
+        <v>1031277.4065851</v>
       </c>
       <c r="N19" t="n">
-        <v>19908.98001931</v>
+        <v>1035451.67634964</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3JZ3byZy7TTrfy8zdxrm9iqJrdsaZ5CrNw</t>
+          <t>https://intel.arkm.com/explorer/address/0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3JZ3byZy7TTrfy8zdxrm9iqJrdsaZ5CrNw</t>
+          <t>0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Crypto.com</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://crypto.com</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K20" t="n">
-        <v>727600715.354599</v>
+        <v>1805690736.550816</v>
       </c>
       <c r="L20" t="n">
-        <v>661005746.7650909</v>
+        <v>1789915482.375</v>
       </c>
       <c r="M20" t="n">
-        <v>8190.96423</v>
+        <v>594733.0817238287</v>
       </c>
       <c r="N20" t="n">
-        <v>7406.96123</v>
+        <v>589057.6272406335</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1FrFvcV3MEkPHViU5tsDNbKwC872xfXL2h</t>
+          <t>https://intel.arkm.com/explorer/address/0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1FrFvcV3MEkPHViU5tsDNbKwC872xfXL2h</t>
+          <t>0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1722,57 +1742,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K21" t="n">
-        <v>513114496</v>
+        <v>1344068978.838293</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1328825799.614612</v>
       </c>
       <c r="M21" t="n">
-        <v>5869.3979992</v>
+        <v>442305.5390923287</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>437809.72259879</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q0d3k8zue8z5ztqt0r35rsd7gua5z4ser6gt46c</t>
+          <t>https://intel.arkm.com/explorer/address/0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bc1q0d3k8zue8z5ztqt0r35rsd7gua5z4ser6gt46c</t>
+          <t>0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1782,7 +1812,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1792,55 +1822,57 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2029878574.70939</v>
+        <v>1293343038.434332</v>
       </c>
       <c r="L22" t="n">
-        <v>2026472876.942573</v>
+        <v>1324391575.568359</v>
       </c>
       <c r="M22" t="n">
-        <v>22685.07717914</v>
+        <v>429238.3701466272</v>
       </c>
       <c r="N22" t="n">
-        <v>22657.64460305</v>
+        <v>438759.19883991</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qr4dl5wa7kl8yu792dceg9z5knl2gkn220lk7a9</t>
+          <t>https://intel.arkm.com/explorer/address/0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bc1qr4dl5wa7kl8yu792dceg9z5knl2gkn220lk7a9</t>
+          <t>0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crypto.com</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1850,65 +1882,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://crypto.com</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1780723091.56448</v>
+        <v>1173967760.719858</v>
       </c>
       <c r="L23" t="n">
-        <v>1590476152.710537</v>
+        <v>1270163990.661506</v>
       </c>
       <c r="M23" t="n">
-        <v>20022.19667198</v>
+        <v>386660.557370076</v>
       </c>
       <c r="N23" t="n">
-        <v>17907.66361606</v>
+        <v>418910.38966375</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q7cyrfmck2ffu2ud3rn5l5a8yv6f0chkp0zpemf</t>
+          <t>https://intel.arkm.com/explorer/address/0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bc1q7cyrfmck2ffu2ud3rn5l5a8yv6f0chkp0zpemf</t>
+          <t>0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crypto.com</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1918,7 +1952,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://crypto.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1928,111 +1962,127 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1543277924.057187</v>
+        <v>1382897029.985585</v>
       </c>
       <c r="L24" t="n">
-        <v>1654789711.893487</v>
+        <v>1488603550.892896</v>
       </c>
       <c r="M24" t="n">
-        <v>17361.00957206</v>
+        <v>460613.5539768328</v>
       </c>
       <c r="N24" t="n">
-        <v>18588.82293071</v>
+        <v>492936.2972540337</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q7trt2zh5lzd5sap0mqgd246kuq9g0kwg6zhhy3</t>
+          <t>https://intel.arkm.com/explorer/address/0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bc1q7trt2zh5lzd5sap0mqgd246kuq9g0kwg6zhhy3</t>
+          <t>0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2739248825.129715</v>
+        <v>3368416794.522798</v>
       </c>
       <c r="L25" t="n">
-        <v>2717886038</v>
+        <v>3349470505.026005</v>
       </c>
       <c r="M25" t="n">
-        <v>30536.40046463</v>
+        <v>1112673.025008726</v>
       </c>
       <c r="N25" t="n">
-        <v>30327.53268886</v>
+        <v>1105829.295316693</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1Kr6QSydW9bFQG1mXiPNNu6WpJGmUa9i1g</t>
+          <t>https://intel.arkm.com/explorer/address/0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1Kr6QSydW9bFQG1mXiPNNu6WpJGmUa9i1g</t>
+          <t>0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bitfinex</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2042,7 +2092,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://bitfinex.com</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2052,219 +2102,227 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>931750222.3808618</v>
+        <v>3312209265.272538</v>
       </c>
       <c r="L26" t="n">
-        <v>1176093813.754185</v>
+        <v>3152875530.776313</v>
       </c>
       <c r="M26" t="n">
-        <v>10618.72915694</v>
+        <v>1097443.74367123</v>
       </c>
       <c r="N26" t="n">
-        <v>13338.28925354</v>
+        <v>1045229.99456863</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qmakjy7ns2z8vwgptf9vs8fndp304fg0p9xafm2</t>
+          <t>https://intel.arkm.com/explorer/address/0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bc1qmakjy7ns2z8vwgptf9vs8fndp304fg0p9xafm2</t>
+          <t>0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Coinbase Prime Custody</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>852237999.390131</v>
+        <v>3139024069.153679</v>
       </c>
       <c r="L27" t="n">
-        <v>752332957.5</v>
+        <v>3139024076.247688</v>
       </c>
       <c r="M27" t="n">
-        <v>9530.16326116</v>
+        <v>1030681.991847288</v>
       </c>
       <c r="N27" t="n">
-        <v>8401.94441846</v>
+        <v>1030681.991847288</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/13XJwZdXMh7D4rGd2og4sowZRz4vxNH1LB</t>
+          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13XJwZdXMh7D4rGd2og4sowZRz4vxNH1LB</t>
+          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Coinbase Prime</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/prime</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K28" t="n">
-        <v>711111168</v>
+        <v>2526004292.352442</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2520657881.674536</v>
       </c>
       <c r="M28" t="n">
-        <v>7657.8023727</v>
+        <v>838106.0445600834</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>836593.2035643058</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qsg6x2cvm75xuddn5g0ss9zglaamgz90q8vcp8w</t>
+          <t>https://intel.arkm.com/explorer/address/0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bc1qsg6x2cvm75xuddn5g0ss9zglaamgz90q8vcp8w</t>
+          <t>0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>custodian</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://paxos.com</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>637261120</v>
+        <v>1920208684.670458</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1920208675.760169</v>
       </c>
       <c r="M29" t="n">
-        <v>6757.16137194</v>
+        <v>634952.1039373239</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>634952.1039373239</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/37GgrfZcywSLuBpQDf1t6aJicWzHRf2GFB</t>
+          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>37GgrfZcywSLuBpQDf1t6aJicWzHRf2GFB</t>
+          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Twenty One Capital</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2274,173 +2332,187 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://xxi.money/</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1828583320.51047</v>
       </c>
       <c r="L30" t="n">
-        <v>2438727424</v>
+        <v>1817198543.676425</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>600960.0841306447</v>
       </c>
       <c r="N30" t="n">
-        <v>26917.22442797</v>
+        <v>597144.7303148605</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3KNViZo8uJwnLyxrWed5gRavbPZibEdAq3</t>
+          <t>https://intel.arkm.com/explorer/address/0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3KNViZo8uJwnLyxrWed5gRavbPZibEdAq3</t>
+          <t>0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Anchorage Digital</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>custodian</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://www.anchorage.com</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1795113175.857878</v>
       </c>
       <c r="L31" t="n">
-        <v>985967603.09375</v>
+        <v>1795113173.933729</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>594172.2191319884</v>
       </c>
       <c r="N31" t="n">
-        <v>11284.59564648</v>
+        <v>594172.2191319884</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/36YZXcTVLPdyapYuqXdJEt46oMVB2NrzVv</t>
+          <t>https://intel.arkm.com/explorer/address/0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>36YZXcTVLPdyapYuqXdJEt46oMVB2NrzVv</t>
+          <t>0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lido</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>liquid-staking</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://lido.fi</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Coinbase Prime Deposit</t>
+          <t>Lido Staked Ether Token (STETH)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2056327465.400953</v>
+        <v>1123517169.793615</v>
       </c>
       <c r="L32" t="n">
-        <v>1997158098</v>
+        <v>1093206077.320312</v>
       </c>
       <c r="M32" t="n">
-        <v>23083.18547267</v>
+        <v>365163.3887365008</v>
       </c>
       <c r="N32" t="n">
-        <v>22444.11152656</v>
+        <v>354502.1732189195</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1G47mSr3oANXMafVrR8UC4pzV7FEAzo3r9</t>
+          <t>https://intel.arkm.com/explorer/address/0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1G47mSr3oANXMafVrR8UC4pzV7FEAzo3r9</t>
+          <t>0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2450,7 +2522,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://gate.com</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2460,103 +2532,127 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>550576330.3153577</v>
+        <v>947683471.8005881</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>927957386.6976464</v>
       </c>
       <c r="M33" t="n">
-        <v>6158.99849773</v>
+        <v>314588.904508293</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>305710.734681</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qttmz4kvr8tr6alvmn3zpd5mg53e787rq8v06z0qyqrru4992hsmqxnzkyl</t>
+          <t>https://intel.arkm.com/explorer/address/0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bc1qttmz4kvr8tr6alvmn3zpd5mg53e787rq8v06z0qyqrru4992hsmqxnzkyl</t>
+          <t>0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Eth2 Staking</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>890992256</v>
+        <v>1110263200</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>10113.64902039</v>
+        <v>360000</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3JZq4atUahhuA9rLhXLMhhTo133J9rF97j</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3JZq4atUahhuA9rLhXLMhhTo133J9rF97j</t>
+          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bitfinex</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2566,127 +2662,111 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://bitfinex.com</t>
+          <t>https://coinbase.com</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>6522517760.568218</v>
       </c>
       <c r="L35" t="n">
-        <v>700752000</v>
+        <v>6544406569.882905</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2152151.738769514</v>
       </c>
       <c r="N35" t="n">
-        <v>8000.00008502</v>
+        <v>2159937.155797073</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qppunwskzl7t3mtmcarlvpxjuzd8jy7l7ga49av2c78xg47fujncsrc76y6</t>
+          <t>https://intel.arkm.com/explorer/address/0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bc1qppunwskzl7t3mtmcarlvpxjuzd8jy7l7ga49av2c78xg47fujncsrc76y6</t>
+          <t>0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Bitstamp</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://bitstamp.net</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>1387214137.397675</v>
+        <v>2166026395.65625</v>
       </c>
       <c r="L36" t="n">
-        <v>1448960083.95829</v>
+        <v>2166026369.46875</v>
       </c>
       <c r="M36" t="n">
-        <v>15532.23774416</v>
+        <v>705536</v>
       </c>
       <c r="N36" t="n">
-        <v>16216.92452783</v>
+        <v>705536</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q8wyf76hse8w4dr0qmmapmnuywlpf2upv5are5y9993gdsnvdt97qsem5pp</t>
+          <t>https://intel.arkm.com/explorer/address/0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bc1q8wyf76hse8w4dr0qmmapmnuywlpf2upv5are5y9993gdsnvdt97qsem5pp</t>
+          <t>0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
@@ -2696,129 +2776,121 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>758845248</v>
+        <v>1562000453.175918</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1561998837.875261</v>
       </c>
       <c r="M37" t="n">
-        <v>8613.649007</v>
+        <v>506460.5407311035</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>506460.0250524727</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1DLeNApsHNNzUMNZJVoXeyEY5sdp8vzx3w</t>
+          <t>https://intel.arkm.com/explorer/address/0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1DLeNApsHNNzUMNZJVoXeyEY5sdp8vzx3w</t>
+          <t>0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://bybit.com</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>BatchDeposit</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2394592469.560097</v>
+        <v>1545610913.739746</v>
       </c>
       <c r="L38" t="n">
-        <v>2401397480.780167</v>
+        <v>1545878735.992676</v>
       </c>
       <c r="M38" t="n">
-        <v>26902.33768776</v>
+        <v>504146.34</v>
       </c>
       <c r="N38" t="n">
-        <v>26984.89785832</v>
+        <v>504235.746</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q9exg34dkmgxu28yektgn929jpjpzukhhl2r3zr</t>
+          <t>https://intel.arkm.com/explorer/address/0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bc1q9exg34dkmgxu28yektgn929jpjpzukhhl2r3zr</t>
+          <t>0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2828,109 +2900,121 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1241813491.256122</v>
+        <v>1077965793.272252</v>
       </c>
       <c r="L39" t="n">
-        <v>1293132826.946991</v>
+        <v>1069771973.026666</v>
       </c>
       <c r="M39" t="n">
-        <v>13910.46445868</v>
+        <v>357123.4331164974</v>
       </c>
       <c r="N39" t="n">
-        <v>14488.87039104</v>
+        <v>354504.72875264</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1HDbEPC4ATYM9iebLgyWMwsicSZtYLmnEq</t>
+          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1HDbEPC4ATYM9iebLgyWMwsicSZtYLmnEq</t>
+          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PoolManager</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K40" t="n">
-        <v>504081504</v>
+        <v>3174996166.897975</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3166791861.890373</v>
       </c>
       <c r="M40" t="n">
-        <v>5869.39809786</v>
+        <v>1047889.130250069</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1045368.98854005</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1PHpKcFBaUcNadBKEWutz3uMTWKupe8QHq</t>
+          <t>https://intel.arkm.com/explorer/address/0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1PHpKcFBaUcNadBKEWutz3uMTWKupe8QHq</t>
+          <t>0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
@@ -2940,239 +3024,231 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>2984899075.064578</v>
       </c>
       <c r="L41" t="n">
-        <v>711176192</v>
+        <v>2984899247.759352</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>938725.8018690519</v>
       </c>
       <c r="N41" t="n">
-        <v>7658.50237493</v>
+        <v>938725.8573831373</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3MqUP6G1daVS5YTD8fz3QgwjZortWwxXFd</t>
+          <t>https://intel.arkm.com/explorer/address/0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3MqUP6G1daVS5YTD8fz3QgwjZortWwxXFd</t>
+          <t>0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Coinbase Prime</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/prime</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>12392146220.32094</v>
+        <v>1621622386.878073</v>
       </c>
       <c r="L42" t="n">
-        <v>12394372895.79762</v>
+        <v>1615157383.680816</v>
       </c>
       <c r="M42" t="n">
-        <v>138836.60664855</v>
+        <v>535149.7368909797</v>
       </c>
       <c r="N42" t="n">
-        <v>138865.14155407</v>
+        <v>532584.4342944291</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3EaWHFAWjgG7189kFD2P3hrMqt8qgbdrzN</t>
+          <t>https://intel.arkm.com/explorer/address/0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3EaWHFAWjgG7189kFD2P3hrMqt8qgbdrzN</t>
+          <t>0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K43" t="n">
-        <v>909467272.0109024</v>
+        <v>1539116512.23613</v>
       </c>
       <c r="L43" t="n">
-        <v>879535382</v>
+        <v>1468841741</v>
       </c>
       <c r="M43" t="n">
-        <v>10143.97468692</v>
+        <v>507035.1332085576</v>
       </c>
       <c r="N43" t="n">
-        <v>9839.09337852</v>
+        <v>486483.7066143855</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1KNm4K8GUK8sMoxc2Z3zU8Uv5FDVjrA72p</t>
+          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1KNm4K8GUK8sMoxc2Z3zU8Uv5FDVjrA72p</t>
+          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jump Crypto</t>
+          <t>Kyber Network</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://jumptrading.com</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>https://kyber.network</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Aggregator Executor V3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K44" t="n">
-        <v>554271338.9586639</v>
+        <v>1107427684.254632</v>
       </c>
       <c r="L44" t="n">
-        <v>677227188.2988281</v>
+        <v>1107251329.719594</v>
       </c>
       <c r="M44" t="n">
-        <v>6224.45349429</v>
+        <v>362874.9629761748</v>
       </c>
       <c r="N44" t="n">
-        <v>7527.63991861</v>
+        <v>362823.5284547307</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qjcm02r55a90v88xwe4alew4y4uyft2htvnywv2</t>
+          <t>https://intel.arkm.com/explorer/address/0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bc1qjcm02r55a90v88xwe4alew4y4uyft2htvnywv2</t>
+          <t>0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3182,183 +3258,209 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://robinhood.com/</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Eth2 Staking</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1110263200</v>
       </c>
       <c r="L45" t="n">
-        <v>578351338.296875</v>
+        <v>1102789560</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="N45" t="n">
-        <v>6497.17225553</v>
+        <v>360000</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qptc9cz269u2mc5yguun5a5d6yd5c7f7ne4qj26</t>
+          <t>https://intel.arkm.com/explorer/address/0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bc1qptc9cz269u2mc5yguun5a5d6yd5c7f7ne4qj26</t>
+          <t>0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
-        <v>1408599936.265086</v>
+        <v>918001940.1768073</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>918598516.78125</v>
       </c>
       <c r="M46" t="n">
-        <v>16400.04538128</v>
+        <v>302134.900001667</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>302134.9</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qvzgrkefd8v536de2vqhx4d25e5rly7lgk3p2vp</t>
+          <t>https://intel.arkm.com/explorer/address/0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>bc1qvzgrkefd8v536de2vqhx4d25e5rly7lgk3p2vp</t>
+          <t>0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://uniswap.org</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Quoter</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1915668582.754017</v>
+        <v>1816100064.355804</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1816099803.189476</v>
       </c>
       <c r="M47" t="n">
-        <v>21901.75749903</v>
+        <v>596859.0595989513</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>596858.9761758528</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/15DomY3arDPw5jD658Mbf3AY3wT3YCDmW2</t>
+          <t>https://intel.arkm.com/explorer/address/0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15DomY3arDPw5jD658Mbf3AY3wT3YCDmW2</t>
+          <t>0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3368,483 +3470,495 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1596873961.650391</v>
+        <v>1297623623.14208</v>
       </c>
       <c r="L48" t="n">
-        <v>1688945221.837891</v>
+        <v>1273154808.163356</v>
       </c>
       <c r="M48" t="n">
-        <v>17844.52639709</v>
+        <v>429917.0145423929</v>
       </c>
       <c r="N48" t="n">
-        <v>18855.98617503</v>
+        <v>422000.41295201</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3M7VitwPb1NytoSGb9C3TfrfoNPTt5nZqV</t>
+          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3M7VitwPb1NytoSGb9C3TfrfoNPTt5nZqV</t>
+          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K49" t="n">
-        <v>890987712</v>
+        <v>1254014411.370105</v>
       </c>
       <c r="L49" t="n">
-        <v>888248576</v>
+        <v>1259993271.693302</v>
       </c>
       <c r="M49" t="n">
-        <v>10144.91987561</v>
+        <v>413614.5619807786</v>
       </c>
       <c r="N49" t="n">
-        <v>10144.91987561</v>
+        <v>414981.55872983</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q8s3h3vw5xufdas890q29lpuca56r0ezqar0mvs</t>
+          <t>https://intel.arkm.com/explorer/address/0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bc1q8s3h3vw5xufdas890q29lpuca56r0ezqar0mvs</t>
+          <t>0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cumberland DRW</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://cumberland.io</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>https://ether.fi/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LiquidityPool (Proxy)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K50" t="n">
-        <v>815350081.766449</v>
+        <v>1078240797.985406</v>
       </c>
       <c r="L50" t="n">
-        <v>733927690.8494632</v>
+        <v>1075335264.820105</v>
       </c>
       <c r="M50" t="n">
-        <v>9085.51926313</v>
+        <v>346849.2485119854</v>
       </c>
       <c r="N50" t="n">
-        <v>8174.84360642</v>
+        <v>356677.2505183262</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/324H9uyTV9bPgAVgmdJNxPKKKZmowk5CYq</t>
+          <t>https://intel.arkm.com/explorer/address/0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>324H9uyTV9bPgAVgmdJNxPKKKZmowk5CYq</t>
+          <t>0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bullish.com</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://bullish.com/</t>
+          <t>https://ether.fi/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>StakingManager (Proxy)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>633025663.25</v>
+        <v>1024680392</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1024680400</v>
       </c>
       <c r="M51" t="n">
-        <v>7081.68847928</v>
+        <v>340000</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qfnv2t4ntuhu52ykp06u6uy3nj7ctm2388cs80e</t>
+          <t>https://intel.arkm.com/explorer/address/0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bc1qfnv2t4ntuhu52ykp06u6uy3nj7ctm2388cs80e</t>
+          <t>0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FalconX</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://falconx.io/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>996835501.585402</v>
       </c>
       <c r="L52" t="n">
-        <v>1412894464</v>
+        <v>913513631.0803859</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>337423.6618982208</v>
       </c>
       <c r="N52" t="n">
-        <v>16450.04551928</v>
+        <v>309146.26829891</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:38</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1quhruqrghgcca950rvhtrg7cpd7u8k6svpzgzmrjy8xyukacl5lkq0r8l2d</t>
+          <t>https://intel.arkm.com/explorer/address/0xA712eF381fA0e8c0733Bd281A17974FBFAeab0b3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bc1quhruqrghgcca950rvhtrg7cpd7u8k6svpzgzmrjy8xyukacl5lkq0r8l2d</t>
+          <t>0xA712eF381fA0e8c0733Bd281A17974FBFAeab0b3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Coinbase Deposit</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>2378566201.031429</v>
+        <v>14510156.75</v>
       </c>
       <c r="L53" t="n">
-        <v>2371067480.086669</v>
+        <v>14499727.25</v>
       </c>
       <c r="M53" t="n">
-        <v>26761.6328191</v>
+        <v>1168734.40484002</v>
       </c>
       <c r="N53" t="n">
-        <v>26647.71028181</v>
+        <v>1168734.405206887</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/12XZMdaAGmcHf4ocFSqpd8jFd1WH7RHUPs</t>
+          <t>https://intel.arkm.com/explorer/address/0x7C876bdaA5c038E19F633714f622F6Def949B102</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12XZMdaAGmcHf4ocFSqpd8jFd1WH7RHUPs</t>
+          <t>0x7C876bdaA5c038E19F633714f622F6Def949B102</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>https://bybit.com</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
-        <v>2354876506.074745</v>
+        <v>47250057.32232746</v>
       </c>
       <c r="L54" t="n">
-        <v>2364654993.733749</v>
+        <v>47260034.796875</v>
       </c>
       <c r="M54" t="n">
-        <v>26432.98073594</v>
+        <v>3715883.819405941</v>
       </c>
       <c r="N54" t="n">
-        <v>26543.62021151</v>
+        <v>3715882.828758016</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1GrwDkr33gT6LuumniYjKEGjTLhsL5kmqC</t>
+          <t>https://intel.arkm.com/explorer/address/0x16463c6ce596C91d337495AE699F44D627C8357D</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1GrwDkr33gT6LuumniYjKEGjTLhsL5kmqC</t>
+          <t>0x16463c6ce596C91d337495AE699F44D627C8357D</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>https://bybit.com</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
-        <v>2242784747.941905</v>
+        <v>19406606.00152278</v>
       </c>
       <c r="L55" t="n">
-        <v>2246961173.165423</v>
+        <v>19561140.5</v>
       </c>
       <c r="M55" t="n">
-        <v>25232.85438639</v>
+        <v>1439999.000112</v>
       </c>
       <c r="N55" t="n">
-        <v>25281.40615983</v>
+        <v>1452824</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3M219KR5vEneNb47ewrPfWyb5jQ2DjxRP6</t>
+          <t>https://intel.arkm.com/explorer/address/0x651641299C7eC0aA44AD7eD9b7E12702fED2022f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3M219KR5vEneNb47ewrPfWyb5jQ2DjxRP6</t>
+          <t>0x651641299C7eC0aA44AD7eD9b7E12702fED2022f</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3854,515 +3968,633 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://bybit.com</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1614113024.495659</v>
+        <v>20785196.20952347</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>24857220.30625832</v>
       </c>
       <c r="M56" t="n">
-        <v>18419.33900546</v>
+        <v>1611108.109023147</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1929692.61043282</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/335umQ4egqMjDo6wSXYwQZYPntZzMveNTJ</t>
+          <t>https://intel.arkm.com/explorer/address/0xa71Dbf81620EFc74E9089b413BC6357D6ad7edaf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>335umQ4egqMjDo6wSXYwQZYPntZzMveNTJ</t>
+          <t>0xa71Dbf81620EFc74E9089b413BC6357D6ad7edaf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
-        <v>1467541277.34375</v>
+        <v>28171344</v>
       </c>
       <c r="L57" t="n">
-        <v>1464197973.625</v>
+        <v>28216598</v>
       </c>
       <c r="M57" t="n">
-        <v>16312.04830612</v>
+        <v>2262758.519376952</v>
       </c>
       <c r="N57" t="n">
-        <v>16264.48841612</v>
+        <v>2262758.519376952</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3E8T3FPyyd4daRyjQdCNi8WV97v92XvQKu</t>
+          <t>https://intel.arkm.com/explorer/address/0x177a7376860a04eEA6BF7fb3F39Bf10c49D3b42C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3E8T3FPyyd4daRyjQdCNi8WV97v92XvQKu</t>
+          <t>0x177a7376860a04eEA6BF7fb3F39Bf10c49D3b42C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blackhole</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blackhole.xyz/</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>523105164</v>
+        <v>262203979.8933285</v>
       </c>
       <c r="L58" t="n">
-        <v>735605620</v>
+        <v>262241925.7994927</v>
       </c>
       <c r="M58" t="n">
-        <v>5949</v>
+        <v>20402860.94111584</v>
       </c>
       <c r="N58" t="n">
-        <v>7923.092641</v>
+        <v>20406555.90127004</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3P4Fjuyn8SMeMV3SVCLUw88zhTk38aqCB8</t>
+          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3P4Fjuyn8SMeMV3SVCLUw88zhTk38aqCB8</t>
+          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kyber Network</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://kyber.network</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Aggregator Executor V3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>17335785.89675013</v>
       </c>
       <c r="L59" t="n">
-        <v>890987712</v>
+        <v>17338213.05145394</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1352146.247353066</v>
       </c>
       <c r="N59" t="n">
-        <v>10144.91999566</v>
+        <v>1352339.464412661</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3FsDiWdG76meMpdCLbVV4dUXhrFyaLrtxL</t>
+          <t>https://intel.arkm.com/explorer/address/0xFAD57d2039C21811C8F2B5D5B65308aa99D31559</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3FsDiWdG76meMpdCLbVV4dUXhrFyaLrtxL</t>
+          <t>0xFAD57d2039C21811C8F2B5D5B65308aa99D31559</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>LINK-USDC</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K60" t="n">
-        <v>2438636800</v>
+        <v>13183824.34509114</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>13127334.08421058</v>
       </c>
       <c r="M60" t="n">
-        <v>26916.22491951</v>
+        <v>1021576.206992282</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1020446.956855342</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1Pzaqw98PeRfyHypfqyEgg5yycJRsENrE7</t>
+          <t>https://intel.arkm.com/explorer/address/0xB1dB79aea0a13382DD9E279d96Bc9a468A2F4E87</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1Pzaqw98PeRfyHypfqyEgg5yycJRsENrE7</t>
+          <t>0xB1dB79aea0a13382DD9E279d96Bc9a468A2F4E87</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>258654097.6192747</v>
       </c>
       <c r="L61" t="n">
-        <v>683098676</v>
+        <v>258640310.4384772</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>20127850.08390066</v>
       </c>
       <c r="N61" t="n">
-        <v>7522.0005088</v>
+        <v>20126774.38648785</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q6ccnyxn32035zwzrlt7z9nkufwrn27d8ezm8xa</t>
+          <t>https://intel.arkm.com/explorer/address/0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bc1q6ccnyxn32035zwzrlt7z9nkufwrn27d8ezm8xa</t>
+          <t>0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CoW Protocol</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>dex-aggregator</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://cow.fi</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K62" t="n">
-        <v>830185264</v>
+        <v>25394317.49581813</v>
       </c>
       <c r="L62" t="n">
-        <v>834285328</v>
+        <v>25392649.6682221</v>
       </c>
       <c r="M62" t="n">
-        <v>8995.22959506</v>
+        <v>1987335.693707502</v>
       </c>
       <c r="N62" t="n">
-        <v>8995.22959506</v>
+        <v>1987206.488999467</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3EX1HHEwPtkxitrcYpymHFWu91LNsn8wD4</t>
+          <t>https://intel.arkm.com/explorer/address/0x9c17f630DBde24eECe8fd248fAA2E51f690FF79B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3EX1HHEwPtkxitrcYpymHFWu91LNsn8wD4</t>
+          <t>0x9c17f630DBde24eECe8fd248fAA2E51f690FF79B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Chainlink</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://chain.link</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Non-Circulating Supply</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>884654976</v>
+        <v>91370238.60000038</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>10051.07</v>
+        <v>7249999</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q4d2sd88fht2jsj6k530ga0ck8f8afr9yq4k0u7</t>
+          <t>https://intel.arkm.com/explorer/address/0x5d4F3C6fA16908609BAC31Ff148Bd002AA6b8c83</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bc1q4d2sd88fht2jsj6k530ga0ck8f8afr9yq4k0u7</t>
+          <t>0x5d4F3C6fA16908609BAC31Ff148Bd002AA6b8c83</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>LINK 2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>20986348.1480168</v>
       </c>
       <c r="L64" t="n">
-        <v>645647996</v>
+        <v>20849287.89497352</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1621112.308700075</v>
       </c>
       <c r="N64" t="n">
-        <v>7276.00003787</v>
+        <v>1611812.735932898</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qactqjuk4kghfgaqqt454hzzzs5lsaysunf80gh</t>
+          <t>https://intel.arkm.com/explorer/address/0x841ed663F2636863D40be4EE76243377dff13a34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bc1qactqjuk4kghfgaqqt454hzzzs5lsaysunf80gh</t>
+          <t>0x841ed663F2636863D40be4EE76243377dff13a34</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://robinhood.com/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K65" t="n">
-        <v>6691564479.210578</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>6691706526.219632</v>
+        <v>12852238.72442627</v>
       </c>
       <c r="M65" t="n">
-        <v>75158.85967737999</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>75158.85967737999</v>
+        <v>1013423.50366701</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:22</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf3fB9691c4BFF980C0352339fb297c5bF52Dd354</t>
+          <t>https://intel.arkm.com/explorer/address/0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xf3fB9691c4BFF980C0352339fb297c5bF52Dd354</t>
+          <t>0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4371,7 +4603,7 @@
         </is>
       </c>
       <c r="D66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -4382,37 +4614,37 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>51100252.74521483</v>
+        <v>47871193.90512696</v>
       </c>
       <c r="L66" t="n">
-        <v>51070560.23671532</v>
+        <v>47982489.66482782</v>
       </c>
       <c r="M66" t="n">
-        <v>304861.3110393503</v>
+        <v>3669792.511902842</v>
       </c>
       <c r="N66" t="n">
-        <v>304733.8316610589</v>
+        <v>3670827.390721438</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x6A6f987882E0D19aAA1155e96beab1e4a9ed474C</t>
+          <t>https://intel.arkm.com/explorer/address/0x79dD9327352BcF1dd16941899705E97b61F4DEcB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x6A6f987882E0D19aAA1155e96beab1e4a9ed474C</t>
+          <t>0x79dD9327352BcF1dd16941899705E97b61F4DEcB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4426,43 +4658,63 @@
       <c r="E67" t="b">
         <v>0</v>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://kraken.com</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K67" t="n">
-        <v>9063341</v>
+        <v>34382215.58863229</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>35643654.26248869</v>
       </c>
       <c r="M67" t="n">
-        <v>58450.53999999999</v>
+        <v>2702342.378479484</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2786947.17555979</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x0BB7a4Fdea32910038DEc59c20ccAe3a6E66b09f</t>
+          <t>https://intel.arkm.com/explorer/address/0xeFE267E44A58815DD2e319F3b9a679a5202da1ce</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x0BB7a4Fdea32910038DEc59c20ccAe3a6E66b09f</t>
+          <t>0xeFE267E44A58815DD2e319F3b9a679a5202da1ce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4479,40 +4731,48 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Gnosis Safe Proxy</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K68" t="n">
-        <v>7326132.582962036</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>7326132.542770261</v>
+        <v>12630000</v>
       </c>
       <c r="M68" t="n">
-        <v>44771.0441099437</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>44771.04400404834</v>
+        <v>1000000</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>https://intel.arkm.com/explorer/address/0x4bD9a84F22bD479f630E2f6c3311285D6eb6B768</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>0x4bD9a84F22bD479f630E2f6c3311285D6eb6B768</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4526,63 +4786,43 @@
       <c r="E69" t="b">
         <v>0</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
-        <v>44951044.56505138</v>
+        <v>12826594.625</v>
       </c>
       <c r="L69" t="n">
-        <v>46010199.17980665</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>272264.4201498198</v>
+        <v>978232.900842485</v>
       </c>
       <c r="N69" t="n">
-        <v>279298.94900067</v>
+        <v>0</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
+          <t>https://intel.arkm.com/explorer/address/0xa42D0A18B834F52e41bEDdEaA2940165db3DA9a3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
+          <t>0xa42D0A18B834F52e41bEDdEaA2940165db3DA9a3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4596,43 +4836,63 @@
       <c r="E70" t="b">
         <v>0</v>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Chainlink</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://chain.link</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Non-Circulating Supply</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K70" t="n">
-        <v>24378531.78031057</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>24370867.51250732</v>
+        <v>50479988</v>
       </c>
       <c r="M70" t="n">
-        <v>144099.9960580334</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>144247.3316469564</v>
+        <v>3999999</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x8A6d3630928802e157595eE18d6D10A4cd4fAB0D</t>
+          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x8A6d3630928802e157595eE18d6D10A4cd4fAB0D</t>
+          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4646,43 +4906,63 @@
       <c r="E71" t="b">
         <v>0</v>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K71" t="n">
-        <v>10685062.625</v>
+        <v>104095106.5184093</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>93949095.64109012</v>
       </c>
       <c r="M71" t="n">
-        <v>68731.90945583291</v>
+        <v>8051733.00265503</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>7276679.69490672</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x927C6aaA6aAd7aF5252237af8B85be10B2DE0DBB</t>
+          <t>https://intel.arkm.com/explorer/address/0x5fA0199427243EB13B14409Fb5197e641805c78B</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x927C6aaA6aAd7aF5252237af8B85be10B2DE0DBB</t>
+          <t>0x5fA0199427243EB13B14409Fb5197e641805c78B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4691,7 +4971,7 @@
         </is>
       </c>
       <c r="D72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -4699,40 +4979,48 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Gnosis Safe Proxy</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K72" t="n">
-        <v>106039300.926618</v>
+        <v>20519058.25</v>
       </c>
       <c r="L72" t="n">
-        <v>106050539.7503563</v>
+        <v>19617667.609375</v>
       </c>
       <c r="M72" t="n">
-        <v>639206.9701238428</v>
+        <v>1521320.56</v>
       </c>
       <c r="N72" t="n">
-        <v>639216.9630778197</v>
+        <v>1456373.058080187</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xBA12222222228d8Ba445958a75a0704d566BF2C8</t>
+          <t>https://intel.arkm.com/explorer/address/0x2B83aaCB0dD973866B563cFb0EF0AEF24B93200b</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xBA12222222228d8Ba445958a75a0704d566BF2C8</t>
+          <t>0x2B83aaCB0dD973866B563cFb0EF0AEF24B93200b</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4741,29 +5029,17 @@
         </is>
       </c>
       <c r="D73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Balancer</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>https://balancer.fi</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Vault</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4772,37 +5048,37 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>43013695.5134902</v>
+        <v>22546754.3841916</v>
       </c>
       <c r="L73" t="n">
-        <v>38187384.59604504</v>
+        <v>25562102.421875</v>
       </c>
       <c r="M73" t="n">
-        <v>258434.4638692765</v>
+        <v>1783210.356187327</v>
       </c>
       <c r="N73" t="n">
-        <v>228892.541762406</v>
+        <v>2006886.552708601</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
+          <t>https://intel.arkm.com/explorer/address/0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
+          <t>0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4811,17 +5087,29 @@
         </is>
       </c>
       <c r="D74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Market Maker</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4830,37 +5118,37 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>25622071.87448567</v>
+        <v>19629004.43666135</v>
       </c>
       <c r="L74" t="n">
-        <v>25689073.7132586</v>
+        <v>20273150.78455508</v>
       </c>
       <c r="M74" t="n">
-        <v>156918.3871562057</v>
+        <v>1523763.185222645</v>
       </c>
       <c r="N74" t="n">
-        <v>157316.7932409542</v>
+        <v>1566978.97891103</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>https://intel.arkm.com/explorer/address/0x628f0371870B0997914b29acE817C2281E4aB268</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>0x628f0371870B0997914b29acE817C2281E4aB268</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4869,29 +5157,17 @@
         </is>
       </c>
       <c r="D75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Market Maker</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4900,37 +5176,37 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>55941544.72612505</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>55320754.66756926</v>
+        <v>13848439.28125</v>
       </c>
       <c r="M75" t="n">
-        <v>336166.9742283435</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>333297.9233615868</v>
+        <v>1093628.876695701</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x3cf2E61F85A95fC964C1ad9D8208D069f5Cf2bc8</t>
+          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x3cf2E61F85A95fC964C1ad9D8208D069f5Cf2bc8</t>
+          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4944,43 +5220,63 @@
       <c r="E76" t="b">
         <v>0</v>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K76" t="n">
-        <v>45853847.77490953</v>
+        <v>388838618.8703228</v>
       </c>
       <c r="L76" t="n">
-        <v>45824204.30992083</v>
+        <v>384595566.8322228</v>
       </c>
       <c r="M76" t="n">
-        <v>280877.096942142</v>
+        <v>30272473.60057416</v>
       </c>
       <c r="N76" t="n">
-        <v>280667.5984426902</v>
+        <v>30006323.15754343</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x80787af194C33b74a811f5e5c549316269d7Ee1A</t>
+          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x80787af194C33b74a811f5e5c549316269d7Ee1A</t>
+          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4996,22 +5292,22 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HitBTC</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://hitbtc.com</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5020,37 +5316,37 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>17872908.30516368</v>
+        <v>68467747.39763168</v>
       </c>
       <c r="L77" t="n">
-        <v>18064155.43359375</v>
+        <v>68496976.63085938</v>
       </c>
       <c r="M77" t="n">
-        <v>108056.6874525968</v>
+        <v>5300003.494641677</v>
       </c>
       <c r="N77" t="n">
-        <v>110819.7566118507</v>
+        <v>5300003.494641677</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4A4aaA0155237881FBD5C34BfaE16e985A7B068D</t>
+          <t>https://intel.arkm.com/explorer/address/0x60030D523A80488e4c5D669E6608022Caba471d9</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x4A4aaA0155237881FBD5C34BfaE16e985A7B068D</t>
+          <t>0x60030D523A80488e4c5D669E6608022Caba471d9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5064,24 +5360,12 @@
       <c r="E78" t="b">
         <v>0</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5090,37 +5374,37 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>15011196.39321142</v>
+        <v>21270900.5001344</v>
       </c>
       <c r="L78" t="n">
-        <v>14808004.47106934</v>
+        <v>21249335.80026245</v>
       </c>
       <c r="M78" t="n">
-        <v>91223.50703274571</v>
+        <v>1589824.00001</v>
       </c>
       <c r="N78" t="n">
-        <v>90398.03651497001</v>
+        <v>1589844.00003</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xd85A69Ec2C7A0d42E599519c574b15571F3C60CA</t>
+          <t>https://intel.arkm.com/explorer/address/0x835678a611B28684005a5e2233695fB6cbbB0007</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xd85A69Ec2C7A0d42E599519c574b15571F3C60CA</t>
+          <t>0x835678a611B28684005a5e2233695fB6cbbB0007</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5134,12 +5418,24 @@
       <c r="E79" t="b">
         <v>0</v>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5148,37 +5444,37 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>28224716.9190239</v>
+        <v>19774932.25140645</v>
       </c>
       <c r="L79" t="n">
-        <v>18313278.6875</v>
+        <v>16389601</v>
       </c>
       <c r="M79" t="n">
-        <v>179781.7323103313</v>
+        <v>1443824.000102</v>
       </c>
       <c r="N79" t="n">
-        <v>113197.3437390483</v>
+        <v>1189376</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA3222357a0eCCF60C73606170be6c99ADeCb59b3</t>
+          <t>https://intel.arkm.com/explorer/address/0xA69babEF1cA67A37Ffaf7a485DfFF3382056e78C</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xA3222357a0eCCF60C73606170be6c99ADeCb59b3</t>
+          <t>0xA69babEF1cA67A37Ffaf7a485DfFF3382056e78C</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5194,22 +5490,22 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HitBTC</t>
+          <t>Symbolic Capital Partners</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://hitbtc.com</t>
+          <t>https://symbolic.partners</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>MEV Bot</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5218,37 +5514,37 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>22121695.236926</v>
+        <v>15441920.96195602</v>
       </c>
       <c r="L80" t="n">
-        <v>22139940.38245201</v>
+        <v>15487824.16600609</v>
       </c>
       <c r="M80" t="n">
-        <v>136646.8711714712</v>
+        <v>1215029.865619221</v>
       </c>
       <c r="N80" t="n">
-        <v>136845.45605223</v>
+        <v>1218159.352874641</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xF72d6A06Ea0066dc9694156Ca544F5d463a26bf4</t>
+          <t>https://intel.arkm.com/explorer/address/0x345366e5142828A66Ee80163b1f30dbE2eAbd566</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xF72d6A06Ea0066dc9694156Ca544F5d463a26bf4</t>
+          <t>0x345366e5142828A66Ee80163b1f30dbE2eAbd566</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5257,7 +5553,7 @@
         </is>
       </c>
       <c r="D81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -5265,40 +5561,48 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K81" t="n">
-        <v>18258227.953125</v>
+        <v>13254146</v>
       </c>
       <c r="L81" t="n">
-        <v>18365079.90625</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>110389.3342385961</v>
+        <v>1062030.95984429</v>
       </c>
       <c r="N81" t="n">
-        <v>111029.7415213561</v>
+        <v>0</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xE91B373212f8aE32925CbCf39AB3a7B0763C27C9</t>
+          <t>https://intel.arkm.com/explorer/address/0xF977814e90dA44bFA03b6295A0616a897441aceC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xE91B373212f8aE32925CbCf39AB3a7B0763C27C9</t>
+          <t>0xF977814e90dA44bFA03b6295A0616a897441aceC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5312,12 +5616,24 @@
       <c r="E82" t="b">
         <v>0</v>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Binance Deposit</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5326,37 +5642,37 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>13363217.90536661</v>
+        <v>90764924.25</v>
       </c>
       <c r="L82" t="n">
-        <v>12717098.3984375</v>
+        <v>41280000</v>
       </c>
       <c r="M82" t="n">
-        <v>82338.11461266951</v>
+        <v>7178890.169000001</v>
       </c>
       <c r="N82" t="n">
-        <v>78654.4303276695</v>
+        <v>3000000</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x70Fedb8c3cddC74f238DAb098AbF956a17936F39</t>
+          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x70Fedb8c3cddC74f238DAb098AbF956a17936F39</t>
+          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5365,48 +5681,68 @@
         </is>
       </c>
       <c r="D83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>PoolManager</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>53894257.19942954</v>
       </c>
       <c r="L83" t="n">
-        <v>6238865.84375</v>
+        <v>53352933.35450052</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4226218.01933802</v>
       </c>
       <c r="N83" t="n">
-        <v>39361.79458921947</v>
+        <v>4173730.660834217</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC17A40852E4BfE04Bc81Af355Fdf132C539bA753</t>
+          <t>https://intel.arkm.com/explorer/address/0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xC17A40852E4BfE04Bc81Af355Fdf132C539bA753</t>
+          <t>0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5415,7 +5751,7 @@
         </is>
       </c>
       <c r="D84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -5425,7 +5761,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Binance Deposit</t>
+          <t>Market Maker</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5434,37 +5770,37 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>11287022.92022675</v>
+        <v>18744344.71636626</v>
       </c>
       <c r="L84" t="n">
-        <v>11089437.859375</v>
+        <v>18713528.14398619</v>
       </c>
       <c r="M84" t="n">
-        <v>68605.86506391646</v>
+        <v>1460533.54276921</v>
       </c>
       <c r="N84" t="n">
-        <v>68255.42206391646</v>
+        <v>1457944.470146326</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xe792b339818Ae6fc4C43C8BEF57352D28E7f7aFb</t>
+          <t>https://intel.arkm.com/explorer/address/0x35264C7443CB18E22FC3fC0517519E769b644EBD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xe792b339818Ae6fc4C43C8BEF57352D28E7f7aFb</t>
+          <t>0x35264C7443CB18E22FC3fC0517519E769b644EBD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5481,40 +5817,48 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Coinbase Deposit</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K85" t="n">
-        <v>7505042</v>
+        <v>16534754</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>16525757</v>
       </c>
       <c r="M85" t="n">
-        <v>43354.17999999999</v>
+        <v>1239816.64</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1239816.6401</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x8f85D8d9d232883d63c992DFf303C10DDA2e428F</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x8f85D8d9d232883d63c992DFf303C10DDA2e428F</t>
+          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5523,17 +5867,29 @@
         </is>
       </c>
       <c r="D86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>HitBTC Deposit</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5542,37 +5898,37 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>18839898.13611194</v>
+        <v>217202021.8592823</v>
       </c>
       <c r="L86" t="n">
-        <v>18872064.39892578</v>
+        <v>216820271.0632039</v>
       </c>
       <c r="M86" t="n">
-        <v>114597.4496126732</v>
+        <v>17047341.1926138</v>
       </c>
       <c r="N86" t="n">
-        <v>114202.0696026732</v>
+        <v>17020768.79973299</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>https://intel.arkm.com/explorer/address/0xf5213a6a2f0890321712520b8048D9886c1A9900</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>0xf5213a6a2f0890321712520b8048D9886c1A9900</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5586,63 +5942,43 @@
       <c r="E87" t="b">
         <v>0</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
-        <v>50693442.19249003</v>
+        <v>23113137.42625093</v>
       </c>
       <c r="L87" t="n">
-        <v>51139307.30533504</v>
+        <v>22962400.11697388</v>
       </c>
       <c r="M87" t="n">
-        <v>305041.0856406344</v>
+        <v>1787250.399245857</v>
       </c>
       <c r="N87" t="n">
-        <v>309448.85035</v>
+        <v>1773772.35222</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>https://intel.arkm.com/explorer/address/0x5a52E96BAcdaBb82fd05763E25335261B270Efcb</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>0x5a52E96BAcdaBb82fd05763E25335261B270Efcb</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5673,7 +6009,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5682,37 +6018,37 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>44269518.61017749</v>
+        <v>16389601</v>
       </c>
       <c r="L88" t="n">
-        <v>45898991.04729974</v>
+        <v>60951732.25</v>
       </c>
       <c r="M88" t="n">
-        <v>267852.13568369</v>
+        <v>1189376</v>
       </c>
       <c r="N88" t="n">
-        <v>278172.98877498</v>
+        <v>4803824</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>https://intel.arkm.com/explorer/address/0x7914663715665dB7BE9B17Af046292A879c06f48</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>0x7914663715665dB7BE9B17Af046292A879c06f48</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5726,63 +6062,43 @@
       <c r="E89" t="b">
         <v>0</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Kyber Network</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>https://kyber.network</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Aggregator Executor V3</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
-        <v>17837281.75099536</v>
+        <v>15439457.0640564</v>
       </c>
       <c r="L89" t="n">
-        <v>17836438.18812654</v>
+        <v>15439457.0640564</v>
       </c>
       <c r="M89" t="n">
-        <v>109796.005970909</v>
+        <v>1188891.18322697</v>
       </c>
       <c r="N89" t="n">
-        <v>109790.8984974709</v>
+        <v>1188891.18322697</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x33fcf9c2c057b3d4e16F2eef8296a3f97B61d4d6</t>
+          <t>https://intel.arkm.com/explorer/address/0x0D0707963952f2fBA59dD06f2b425ace40b492Fe</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x33fcf9c2c057b3d4e16F2eef8296a3f97B61d4d6</t>
+          <t>0x0D0707963952f2fBA59dD06f2b425ace40b492Fe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5796,12 +6112,24 @@
       <c r="E90" t="b">
         <v>0</v>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://gate.com</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5810,37 +6138,37 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>12216604.6111277</v>
+        <v>14800213.49018702</v>
       </c>
       <c r="L90" t="n">
-        <v>9545697</v>
+        <v>14440999.72962726</v>
       </c>
       <c r="M90" t="n">
-        <v>74781.05557799786</v>
+        <v>1147515.815346689</v>
       </c>
       <c r="N90" t="n">
-        <v>58846.4902698841</v>
+        <v>1124207.685366812</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x0e240e9A7B40aD11Fdd69f952bA3Bbd29a238BbD</t>
+          <t>https://intel.arkm.com/explorer/address/0xD8B671d6f61f40025d8538208a1bD3B57A127805</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x0e240e9A7B40aD11Fdd69f952bA3Bbd29a238BbD</t>
+          <t>0xD8B671d6f61f40025d8538208a1bD3B57A127805</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5849,7 +6177,7 @@
         </is>
       </c>
       <c r="D91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
@@ -5859,7 +6187,7 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Gnosis Safe Proxy</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5868,37 +6196,37 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>12630000</v>
       </c>
       <c r="L91" t="n">
-        <v>23886750</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="N91" t="n">
-        <v>156000.20005</v>
+        <v>0</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5907,29 +6235,29 @@
         </is>
       </c>
       <c r="D92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Market Maker</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5938,37 +6266,37 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>65041331.28089902</v>
+        <v>126133310.2011374</v>
       </c>
       <c r="L92" t="n">
-        <v>65265554.94469833</v>
+        <v>126073586.4216383</v>
       </c>
       <c r="M92" t="n">
-        <v>412752.7683716223</v>
+        <v>9735019.949889055</v>
       </c>
       <c r="N92" t="n">
-        <v>412133.5571044118</v>
+        <v>9726177.28969945</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>https://intel.arkm.com/explorer/address/0x5E8C8A7243651DB1384C0dDfDbE39761E8e7E51a</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>0x5E8C8A7243651DB1384C0dDfDbE39761E8e7E51a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5984,22 +6312,22 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>lending-decentralized</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
+          <t>https://aave.com</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Aave Ethereum LINK (aEthLINK)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6008,37 +6336,37 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>68382611.43131302</v>
+        <v>27438966.90139333</v>
       </c>
       <c r="L93" t="n">
-        <v>67955532.11496162</v>
+        <v>16867064.22702047</v>
       </c>
       <c r="M93" t="n">
-        <v>401122.5778898222</v>
+        <v>2167282.538720507</v>
       </c>
       <c r="N93" t="n">
-        <v>398248.85748494</v>
+        <v>1320037.131739111</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x41a5E4A6c3679CF253D0D0f74251F40D587A518f</t>
+          <t>https://intel.arkm.com/explorer/address/0xD50f074Ec5c7997cE1DaacB513Ec194C480878Af</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x41a5E4A6c3679CF253D0D0f74251F40D587A518f</t>
+          <t>0xD50f074Ec5c7997cE1DaacB513Ec194C480878Af</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6047,7 +6375,7 @@
         </is>
       </c>
       <c r="D94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
@@ -6057,7 +6385,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Coinbase Prime Deposit</t>
+          <t>Gnosis Safe Proxy</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6066,37 +6394,37 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>23886750</v>
+        <v>25535238</v>
       </c>
       <c r="L94" t="n">
-        <v>23925750</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>156000.20005</v>
+        <v>2024999</v>
       </c>
       <c r="N94" t="n">
-        <v>156000.20005</v>
+        <v>0</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xe401A6A38024d8f5aB88f1B08cad476cCaCA45E8</t>
+          <t>https://intel.arkm.com/explorer/address/0xAC64829CDa33bb11C26074CE66E8549e4b8a66A2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xe401A6A38024d8f5aB88f1B08cad476cCaCA45E8</t>
+          <t>0xAC64829CDa33bb11C26074CE66E8549e4b8a66A2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6110,24 +6438,12 @@
       <c r="E95" t="b">
         <v>0</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Bybit Deposit</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6136,37 +6452,37 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>12255815.69881986</v>
+        <v>22619529.95669994</v>
       </c>
       <c r="L95" t="n">
-        <v>12250235.046875</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>74189.981212706</v>
+        <v>1800871.669636466</v>
       </c>
       <c r="N95" t="n">
-        <v>74189.98120865</v>
+        <v>0</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
+          <t>https://intel.arkm.com/explorer/address/0x3db910Fac1dbE434f397c07c2B473983eFcf25DC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
+          <t>0x3db910Fac1dbE434f397c07c2B473983eFcf25DC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6175,68 +6491,48 @@
         </is>
       </c>
       <c r="D96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Nonfungible Position Manager</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>13133860.875</v>
       </c>
       <c r="L96" t="n">
-        <v>6419935.3072404</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1052392.729393878</v>
       </c>
       <c r="N96" t="n">
-        <v>41847.30403062452</v>
+        <v>0</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
+          <t>https://intel.arkm.com/explorer/address/0xEff6cb8b614999d130E537751Ee99724D01aA167</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
+          <t>0xEff6cb8b614999d130E537751Ee99724D01aA167</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6250,24 +6546,12 @@
       <c r="E97" t="b">
         <v>0</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>CoW Protocol</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>dex-aggregator</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>https://cow.fi</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Settlement</t>
+          <t>MEV Bot</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6276,37 +6560,37 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>129873526.9748434</v>
+        <v>13356031.31905337</v>
       </c>
       <c r="L97" t="n">
-        <v>129873281.3128259</v>
+        <v>13374846.82567835</v>
       </c>
       <c r="M97" t="n">
-        <v>780120.3310673292</v>
+        <v>1024197.022098323</v>
       </c>
       <c r="N97" t="n">
-        <v>780106.1599782986</v>
+        <v>1024596.241967763</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xAD85405cbB1476825B78a021fa9E543bF7937549</t>
+          <t>https://intel.arkm.com/explorer/address/0x09ad18BD5D19d6893444B73b6245eC55319F046c</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xAD85405cbB1476825B78a021fa9E543bF7937549</t>
+          <t>0x09ad18BD5D19d6893444B73b6245eC55319F046c</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6322,7 +6606,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6332,12 +6616,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://bybit.com</t>
+          <t>https://coinbase.com</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6346,37 +6630,37 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>24444306.43977574</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>22060614.44546628</v>
+        <v>12958983</v>
       </c>
       <c r="M98" t="n">
-        <v>150624.8441244085</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>134346.86686649</v>
+        <v>1035062.502286183</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x91bf7e6FFA4608FA2280F81D2B23a8b8FB70b14B</t>
+          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x91bf7e6FFA4608FA2280F81D2B23a8b8FB70b14B</t>
+          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6390,43 +6674,63 @@
       <c r="E99" t="b">
         <v>0</v>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K99" t="n">
-        <v>12451656.57188018</v>
+        <v>82361081.56773783</v>
       </c>
       <c r="L99" t="n">
-        <v>12451656.56961991</v>
+        <v>79307599.98178592</v>
       </c>
       <c r="M99" t="n">
-        <v>69366.48644186962</v>
+        <v>6387366.921905445</v>
       </c>
       <c r="N99" t="n">
-        <v>69366.48644186962</v>
+        <v>6151497.25202778</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
+          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
+          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6442,7 +6746,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FalconX</t>
+          <t>Coinbase Prime</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6452,7 +6756,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://falconx.io/</t>
+          <t>https://www.coinbase.com/prime</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6466,37 +6770,37 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>10507022.22328352</v>
+        <v>52032983.21669314</v>
       </c>
       <c r="L100" t="n">
-        <v>10724238.65353632</v>
+        <v>52029688.80140877</v>
       </c>
       <c r="M100" t="n">
-        <v>66087.94986831218</v>
+        <v>4097981.268737037</v>
       </c>
       <c r="N100" t="n">
-        <v>64895.67021373</v>
+        <v>4097870.976269291</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x47cA539b3F546078d97bD851130741c6bF370100</t>
+          <t>https://intel.arkm.com/explorer/address/0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0x47cA539b3F546078d97bD851130741c6bF370100</t>
+          <t>0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6505,64 +6809,60 @@
         </is>
       </c>
       <c r="D101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stani Kulechov</t>
+          <t>B2C2 Group</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>individual</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Gnosis Safe Proxy</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.b2c2.com</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
-        <v>14636410.97094727</v>
+        <v>24003399.83726284</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>19574642.12304688</v>
       </c>
       <c r="M101" t="n">
-        <v>84032.94725614057</v>
+        <v>1857918.800906841</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1547125.794475885</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x59c38b6775Ded821f010DbD30eCabdCF84E04756</t>
+          <t>https://intel.arkm.com/explorer/address/0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x59c38b6775Ded821f010DbD30eCabdCF84E04756</t>
+          <t>0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6593,7 +6893,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>UNI-AAVE 2</t>
+          <t>Nonfungible Position Manager</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6602,37 +6902,37 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>8438715.804674095</v>
+        <v>14660567.20819966</v>
       </c>
       <c r="L102" t="n">
-        <v>7988093.775049517</v>
+        <v>15006904.95429163</v>
       </c>
       <c r="M102" t="n">
-        <v>50192.30545940617</v>
+        <v>1179676.867001697</v>
       </c>
       <c r="N102" t="n">
-        <v>48084.92339963777</v>
+        <v>1207587.055316765</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4a79B0168296c0eF7b8F314973B82aD406a29f1B</t>
+          <t>https://intel.arkm.com/explorer/address/0x7f604D597c15b2e2F60DC645844f68b1D781b752</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x4a79B0168296c0eF7b8F314973B82aD406a29f1B</t>
+          <t>0x7f604D597c15b2e2F60DC645844f68b1D781b752</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6648,53 +6948,61 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Bitstamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://aerodrome.finance/</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>https://bitstamp.net</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K103" t="n">
-        <v>217239299.6941044</v>
+        <v>12076628.14051428</v>
       </c>
       <c r="L103" t="n">
-        <v>217056802.7336599</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>1307139.307941608</v>
+        <v>940434.4009390965</v>
       </c>
       <c r="N103" t="n">
-        <v>1306266.428144907</v>
+        <v>0</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4da27a545c0c5B758a6BA100e3a049001de870f5</t>
+          <t>https://intel.arkm.com/explorer/address/0xd312d0403a2196d95BC4eB5BEac60703a93B1944</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0x4da27a545c0c5B758a6BA100e3a049001de870f5</t>
+          <t>0xd312d0403a2196d95BC4eB5BEac60703a93B1944</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6703,29 +7011,17 @@
         </is>
       </c>
       <c r="D104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Aave</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>lending-decentralized</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>https://aave.com</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Staked Aave (stkAAVE)</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6734,37 +7030,37 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>20327385.41520842</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>57796966.31281979</v>
+        <v>13034408</v>
       </c>
       <c r="M104" t="n">
-        <v>123388.0004989238</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>334159.6782401801</v>
+        <v>1024486.356466608</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x990636ecB3FF04d33D92e970d3d588bF5cD8d086</t>
+          <t>https://intel.arkm.com/explorer/address/0x9B1c1752B6B6eAF62a8c491A8681B32C1F7ecDE9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0x990636ecB3FF04d33D92e970d3d588bF5cD8d086</t>
+          <t>0x9B1c1752B6B6eAF62a8c491A8681B32C1F7ecDE9</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6773,7 +7069,7 @@
         </is>
       </c>
       <c r="D105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
@@ -6781,40 +7077,48 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Binance Deposit</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K105" t="n">
-        <v>7282421.535093386</v>
+        <v>116314976</v>
       </c>
       <c r="L105" t="n">
-        <v>7290536.871422145</v>
+        <v>116379500</v>
       </c>
       <c r="M105" t="n">
-        <v>45073.71175144233</v>
+        <v>9224998</v>
       </c>
       <c r="N105" t="n">
-        <v>45123.29227136062</v>
+        <v>9225000</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x5eE84D30c7EE57F63f71c92247Ff31f95E26916B</t>
+          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0x5eE84D30c7EE57F63f71c92247Ff31f95E26916B</t>
+          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6828,43 +7132,63 @@
       <c r="E106" t="b">
         <v>0</v>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K106" t="n">
-        <v>8096674.170935631</v>
+        <v>75972994.53531809</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>76755203.00034046</v>
       </c>
       <c r="M106" t="n">
-        <v>47370.4370073888</v>
+        <v>5822669.652420743</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5879527.71360408</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
+          <t>https://intel.arkm.com/explorer/address/0xf440838830CC265DB72C81bfBa240E5A4cEb1CC4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
+          <t>0xf440838830CC265DB72C81bfBa240E5A4cEb1CC4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6878,63 +7202,43 @@
       <c r="E107" t="b">
         <v>0</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>14847004.20944018</v>
+        <v>21186788.51102374</v>
       </c>
       <c r="L107" t="n">
-        <v>14389143.62116385</v>
+        <v>16534754</v>
       </c>
       <c r="M107" t="n">
-        <v>91299.52459177992</v>
+        <v>1649999.498895133</v>
       </c>
       <c r="N107" t="n">
-        <v>89256.52128335</v>
+        <v>1239816.64</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x549d835356d92983AbB76E4cae639f7857963425</t>
+          <t>https://intel.arkm.com/explorer/address/0xa6Cc3C2531FdaA6Ae1A3CA84c2855806728693e8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0x549d835356d92983AbB76E4cae639f7857963425</t>
+          <t>0xa6Cc3C2531FdaA6Ae1A3CA84c2855806728693e8</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6943,48 +7247,68 @@
         </is>
       </c>
       <c r="D108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LINK</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>114301863.7321532</v>
       </c>
       <c r="L108" t="n">
-        <v>7813237.970905304</v>
+        <v>102948106.4250945</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>8850577.389278222</v>
       </c>
       <c r="N108" t="n">
-        <v>44998.01731</v>
+        <v>7982873.473790661</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xDDC4eAb490469f073Ab8Cd5937B1a0f585687931</t>
+          <t>https://intel.arkm.com/explorer/address/0xDdfF0cdb9A67fda3363488140ea3E2159A43c2D4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0xDDC4eAb490469f073Ab8Cd5937B1a0f585687931</t>
+          <t>0xDdfF0cdb9A67fda3363488140ea3E2159A43c2D4</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7001,742 +7325,36 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>24048506.95477332</v>
       </c>
       <c r="L109" t="n">
-        <v>6658000.125</v>
+        <v>15380007</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>1806049.954646585</v>
       </c>
       <c r="N109" t="n">
-        <v>39332.58495218402</v>
+        <v>1229169.366962116</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-01-12 17:01:30</t>
+          <t>2026-01-12 17:04:43</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x5aB53EE1d50eeF2C1DD3d5402789cd27bB52c1bB</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>0x5aB53EE1d50eeF2C1DD3d5402789cd27bB52c1bB</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D110" t="b">
-        <v>1</v>
-      </c>
-      <c r="E110" t="b">
-        <v>0</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>AAVE</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>64262823.22424708</v>
-      </c>
-      <c r="L110" t="n">
-        <v>60647255.94288167</v>
-      </c>
-      <c r="M110" t="n">
-        <v>384219.573298466</v>
-      </c>
-      <c r="N110" t="n">
-        <v>366242.7446528305</v>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D111" t="b">
-        <v>0</v>
-      </c>
-      <c r="E111" t="b">
-        <v>0</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Binance Deposit</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>58514406.16923433</v>
-      </c>
-      <c r="L111" t="n">
-        <v>58493737.51171875</v>
-      </c>
-      <c r="M111" t="n">
-        <v>354572.107293369</v>
-      </c>
-      <c r="N111" t="n">
-        <v>354572.107293369</v>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x5A1b2aCd0c9992e14F2b6d8a326023E35a097A3a</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>0x5A1b2aCd0c9992e14F2b6d8a326023E35a097A3a</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D112" t="b">
-        <v>1</v>
-      </c>
-      <c r="E112" t="b">
-        <v>0</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>0x</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>https://0x.org</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>MainnetSettler</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
-        <v>41206314.06721063</v>
-      </c>
-      <c r="L112" t="n">
-        <v>41206313.90364154</v>
-      </c>
-      <c r="M112" t="n">
-        <v>246811.3695642646</v>
-      </c>
-      <c r="N112" t="n">
-        <v>246811.3695642646</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x9bA0CF1588E1DFA905eC948F7FE5104dD40EDa31</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>0x9bA0CF1588E1DFA905eC948F7FE5104dD40EDa31</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D113" t="b">
-        <v>1</v>
-      </c>
-      <c r="E113" t="b">
-        <v>0</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>TrustedVolumes</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Market Maker</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
-        <v>29676143.63311828</v>
-      </c>
-      <c r="L113" t="n">
-        <v>29181757.84821576</v>
-      </c>
-      <c r="M113" t="n">
-        <v>179420.882564851</v>
-      </c>
-      <c r="N113" t="n">
-        <v>179169.2647959933</v>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D114" t="b">
-        <v>0</v>
-      </c>
-      <c r="E114" t="b">
-        <v>0</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>B2C2 Group</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>https://www.b2c2.com</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="n">
-        <v>12261828.89010045</v>
-      </c>
-      <c r="L114" t="n">
-        <v>13696612.2166748</v>
-      </c>
-      <c r="M114" t="n">
-        <v>71935.19852265104</v>
-      </c>
-      <c r="N114" t="n">
-        <v>82621.63880818005</v>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D115" t="b">
-        <v>0</v>
-      </c>
-      <c r="E115" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
-        <v>135821899.8161055</v>
-      </c>
-      <c r="L115" t="n">
-        <v>137570715.8189098</v>
-      </c>
-      <c r="M115" t="n">
-        <v>825305.1581284256</v>
-      </c>
-      <c r="N115" t="n">
-        <v>832680.1929673799</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xa923B13270F8622B5d5960634200Dc4302b7611E</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>0xa923B13270F8622B5d5960634200Dc4302b7611E</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D116" t="b">
-        <v>1</v>
-      </c>
-      <c r="E116" t="b">
-        <v>0</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Gnosis Safe Proxy</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K116" t="n">
-        <v>40917945.5625</v>
-      </c>
-      <c r="L116" t="n">
-        <v>39380708.04328918</v>
-      </c>
-      <c r="M116" t="n">
-        <v>231775.4541938402</v>
-      </c>
-      <c r="N116" t="n">
-        <v>231770.4148689859</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xA700b4eB416Be35b2911fd5Dee80678ff64fF6C9</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>0xA700b4eB416Be35b2911fd5Dee80678ff64fF6C9</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D117" t="b">
-        <v>1</v>
-      </c>
-      <c r="E117" t="b">
-        <v>0</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Aave</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>lending-decentralized</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>https://aave.com</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Aave Ethereum AAVE (aEthAAVE)</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K117" t="n">
-        <v>33285928.21031378</v>
-      </c>
-      <c r="L117" t="n">
-        <v>37262611.17628589</v>
-      </c>
-      <c r="M117" t="n">
-        <v>200323.0401265247</v>
-      </c>
-      <c r="N117" t="n">
-        <v>224443.1809807224</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x7D94077f58593F8b97c5cAB56c8924E13b49946E</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>0x7D94077f58593F8b97c5cAB56c8924E13b49946E</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D118" t="b">
-        <v>0</v>
-      </c>
-      <c r="E118" t="b">
-        <v>0</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Kraken</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K118" t="n">
-        <v>15818051.81704458</v>
-      </c>
-      <c r="L118" t="n">
-        <v>16411178.72861157</v>
-      </c>
-      <c r="M118" t="n">
-        <v>99618.44080260988</v>
-      </c>
-      <c r="N118" t="n">
-        <v>102430.65650883</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xC30F6eE36a1746DD71C7E81529EEae7Ce2f52252</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>0xC30F6eE36a1746DD71C7E81529EEae7Ce2f52252</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D119" t="b">
-        <v>1</v>
-      </c>
-      <c r="E119" t="b">
-        <v>0</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="n">
-        <v>17168900.25</v>
-      </c>
-      <c r="L119" t="n">
-        <v>17233665.7578125</v>
-      </c>
-      <c r="M119" t="n">
-        <v>99926.74939270625</v>
-      </c>
-      <c r="N119" t="n">
-        <v>100325.2573139125</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>aave</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x73E4E2726c688A09af7e72107eE92a372EeB3012</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>0x73E4E2726c688A09af7e72107eE92a372EeB3012</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D120" t="b">
-        <v>0</v>
-      </c>
-      <c r="E120" t="b">
-        <v>0</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Coinbase Deposit</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
-        <v>8468227.906531449</v>
-      </c>
-      <c r="L120" t="n">
-        <v>8464954</v>
-      </c>
-      <c r="M120" t="n">
-        <v>51763.97394</v>
-      </c>
-      <c r="N120" t="n">
-        <v>51763.97394</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:01:30</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>aave</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>

--- a/data_cripto/top_flow.xlsx
+++ b/data_cripto/top_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,78 +513,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4200000000000000000000000000000000000006</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qvzgrkefd8v536de2vqhx4d25e5rly7lgk3p2vp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x4200000000000000000000000000000000000006</t>
+          <t>bc1qvzgrkefd8v536de2vqhx4d25e5rly7lgk3p2vp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://kraken.com</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cold Wallet</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K2" t="n">
-        <v>5486875032.853655</v>
+        <v>1915668582.754017</v>
       </c>
       <c r="L2" t="n">
-        <v>5473830598.234919</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1811070.080476356</v>
+        <v>21901.75749903</v>
       </c>
       <c r="N2" t="n">
-        <v>1807168.437985781</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q9n37v8rdr2tla849xp2znxyp70lnqu8rw0m02a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
+          <t>bc1q9n37v8rdr2tla849xp2znxyp70lnqu8rw0m02a</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,369 +610,345 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3793317049.74327</v>
+        <v>1408247624</v>
       </c>
       <c r="L3" t="n">
-        <v>3763358336.982445</v>
+        <v>1741029888</v>
       </c>
       <c r="M3" t="n">
-        <v>1253831.249362666</v>
+        <v>16172.69578732</v>
       </c>
       <c r="N3" t="n">
-        <v>1244145.76947663</v>
+        <v>19908.98001931</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
+          <t>https://intel.arkm.com/explorer/address/bc1p2mlwrss9tmvtfvu0tcxul2h0w67ej8vyjpj3ksctt67vd9r752ksqx6uqm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
+          <t>bc1p2mlwrss9tmvtfvu0tcxul2h0w67ej8vyjpj3ksctt67vd9r752ksqx6uqm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>jaredfromsubway (MEV)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>mev</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>MEV Bot</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>2429883191.866974</v>
+        <v>833113965.0117188</v>
       </c>
       <c r="L4" t="n">
-        <v>2429886213.67873</v>
+        <v>754659271.2068161</v>
       </c>
       <c r="M4" t="n">
-        <v>801998.7975301587</v>
+        <v>9364.59320822</v>
       </c>
       <c r="N4" t="n">
-        <v>801999.7653357279</v>
+        <v>8476.64192532</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q4d2sd88fht2jsj6k530ga0ck8f8afr9yq4k0u7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>bc1q4d2sd88fht2jsj6k530ga0ck8f8afr9yq4k0u7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>1380449619.705878</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1362669735.491392</v>
+        <v>645647996</v>
       </c>
       <c r="M5" t="n">
-        <v>453489.1777541857</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>448556.16924823</v>
+        <v>7276.00003787</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xb23639385a208265f4891A89C27F37b084532DC3</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q0d3k8zue8z5ztqt0r35rsd7gua5z4ser6gt46c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xb23639385a208265f4891A89C27F37b084532DC3</t>
+          <t>bc1q0d3k8zue8z5ztqt0r35rsd7gua5z4ser6gt46c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Cold Wallet</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K6" t="n">
-        <v>975266241.335169</v>
+        <v>2029878574.70939</v>
       </c>
       <c r="L6" t="n">
-        <v>975266240.7557733</v>
+        <v>2026472876.942573</v>
       </c>
       <c r="M6" t="n">
-        <v>323386.2973543156</v>
+        <v>22685.07717914</v>
       </c>
       <c r="N6" t="n">
-        <v>323386.2973543155</v>
+        <v>22657.64460305</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
+          <t>https://intel.arkm.com/explorer/address/3M219KR5vEneNb47ewrPfWyb5jQ2DjxRP6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
+          <t>3M219KR5vEneNb47ewrPfWyb5jQ2DjxRP6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Wrapped Ether (WETH)</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20259438932.99068</v>
+        <v>1614113024.495659</v>
       </c>
       <c r="L7" t="n">
-        <v>20367055258.39912</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6642242.125249802</v>
+        <v>18419.33900546</v>
       </c>
       <c r="N7" t="n">
-        <v>6672559.979974744</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qfnv2t4ntuhu52ykp06u6uy3nj7ctm2388cs80e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
+          <t>bc1qfnv2t4ntuhu52ykp06u6uy3nj7ctm2388cs80e</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Eth2 Beacon Deposit Contract</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>9743785746.779785</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1412894464</v>
       </c>
       <c r="M8" t="n">
-        <v>3185819.797795997</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>16450.04551928</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q0y5m6wdxjre0fs9m3u0j3pv2fcja6qw3a2f6ql</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
+          <t>bc1q0y5m6wdxjre0fs9m3u0j3pv2fcja6qw3a2f6ql</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -966,321 +958,311 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9369390178.64414</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9091454900.127726</v>
+        <v>1390938416</v>
       </c>
       <c r="M9" t="n">
-        <v>3100793.821522709</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3006182.88541323</v>
+        <v>15972.00001596</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
+          <t>https://intel.arkm.com/explorer/address/1KbDEg1tDz2ErYgaDbaDhhawnLrSQFaFx5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
+          <t>1KbDEg1tDz2ErYgaDbaDhhawnLrSQFaFx5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://uniswap.org</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Uniswap v4 Positions NFT (UNI-V4-POSM)</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1193275630.128648</v>
+        <v>4333417509.065747</v>
       </c>
       <c r="L10" t="n">
-        <v>1193275629.786555</v>
+        <v>4316835249.657695</v>
       </c>
       <c r="M10" t="n">
-        <v>394289.2269956106</v>
+        <v>48634.95698303</v>
       </c>
       <c r="N10" t="n">
-        <v>394289.2269956106</v>
+        <v>48450.59731041</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>https://intel.arkm.com/explorer/address/1GrwDkr33gT6LuumniYjKEGjTLhsL5kmqC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>1GrwDkr33gT6LuumniYjKEGjTLhsL5kmqC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://bybit.com</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Market Maker</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3062792793.929688</v>
+        <v>2242805250.209483</v>
       </c>
       <c r="L11" t="n">
-        <v>3062702158.183423</v>
+        <v>2247419338.196673</v>
       </c>
       <c r="M11" t="n">
-        <v>1011451.927096179</v>
+        <v>25233.07699274</v>
       </c>
       <c r="N11" t="n">
-        <v>1011445.095432548</v>
+        <v>25286.38075337</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qr4dl5wa7kl8yu792dceg9z5knl2gkn220lk7a9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
+          <t>bc1qr4dl5wa7kl8yu792dceg9z5knl2gkn220lk7a9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Crypto.com</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://crypto.com</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cold Wallet</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K12" t="n">
-        <v>1702646058.536583</v>
+        <v>1790258067.125271</v>
       </c>
       <c r="L12" t="n">
-        <v>1702645343.315669</v>
+        <v>1590476152.710537</v>
       </c>
       <c r="M12" t="n">
-        <v>563496.1170835318</v>
+        <v>20125.72405849</v>
       </c>
       <c r="N12" t="n">
-        <v>563495.8795240488</v>
+        <v>17907.66361606</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
+          <t>https://intel.arkm.com/explorer/address/1PHpKcFBaUcNadBKEWutz3uMTWKupe8QHq</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
+          <t>1PHpKcFBaUcNadBKEWutz3uMTWKupe8QHq</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>1393302544.028083</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1395170004.140732</v>
+        <v>711176192</v>
       </c>
       <c r="M13" t="n">
-        <v>456792.2656770762</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>457242.1943745955</v>
+        <v>7658.50237493</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
+          <t>https://intel.arkm.com/explorer/address/1Pzaqw98PeRfyHypfqyEgg5yycJRsENrE7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
+          <t>1Pzaqw98PeRfyHypfqyEgg5yycJRsENrE7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="b">
         <v>0</v>
       </c>
@@ -1301,438 +1283,392 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1316808887.357698</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1326095348.503178</v>
+        <v>683098676</v>
       </c>
       <c r="M14" t="n">
-        <v>434123.9310645718</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>437033.0216208</v>
+        <v>7522.0005088</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qcfkga3lyvflf53vt0n2hjd9mr03870pvjw2z72</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
+          <t>bc1qcfkga3lyvflf53vt0n2hjd9mr03870pvjw2z72</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>custodian</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://paxos.com</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Cold Wallet</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K15" t="n">
-        <v>1211731899.873139</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1211731899.368315</v>
+        <v>637261120</v>
       </c>
       <c r="M15" t="n">
-        <v>399963.4473773648</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>399963.4473773648</v>
+        <v>6757.16150495</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
+          <t>https://intel.arkm.com/explorer/address/3FsDiWdG76meMpdCLbVV4dUXhrFyaLrtxL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
+          <t>3FsDiWdG76meMpdCLbVV4dUXhrFyaLrtxL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Coinbase Prime Deposit</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>941419448.3637171</v>
+        <v>2438636800</v>
       </c>
       <c r="L16" t="n">
-        <v>928499614</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>313972.6993268693</v>
+        <v>26916.22491951</v>
       </c>
       <c r="N16" t="n">
-        <v>308954.4792646671</v>
+        <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q8wyf76hse8w4dr0qmmapmnuywlpf2upv5are5y9993gdsnvdt97qsem5pp</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
+          <t>bc1q8wyf76hse8w4dr0qmmapmnuywlpf2upv5are5y9993gdsnvdt97qsem5pp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="b">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Binance Deposit</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>4631714624.43821</v>
+        <v>758845248</v>
       </c>
       <c r="L17" t="n">
-        <v>4626269745.695312</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1527482.304299085</v>
+        <v>8613.649007</v>
       </c>
       <c r="N17" t="n">
-        <v>1525271.742356705</v>
+        <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xd01607c3C5eCABa394D8be377a08590149325722</t>
+          <t>https://intel.arkm.com/explorer/address/1FrFvcV3MEkPHViU5tsDNbKwC872xfXL2h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xd01607c3C5eCABa394D8be377a08590149325722</t>
+          <t>1FrFvcV3MEkPHViU5tsDNbKwC872xfXL2h</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lending-decentralized</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://aave.com</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>WrappedTokenGatewayV3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>3233974767.903385</v>
+        <v>513114496</v>
       </c>
       <c r="L18" t="n">
-        <v>3233974769.579787</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1078157.994433303</v>
+        <v>5869.3979992</v>
       </c>
       <c r="N18" t="n">
-        <v>1078157.994433303</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
+          <t>https://intel.arkm.com/explorer/address/3KNViZo8uJwnLyxrWed5gRavbPZibEdAq3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
+          <t>3KNViZo8uJwnLyxrWed5gRavbPZibEdAq3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>Anchorage Digital</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>custodian</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://www.anchorage.com</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>3158175817.574128</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3166011420.527831</v>
+        <v>985967603.09375</v>
       </c>
       <c r="M19" t="n">
-        <v>1031277.4065851</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1035451.67634964</v>
+        <v>11284.59564648</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qttmz4kvr8tr6alvmn3zpd5mg53e787rq8v06z0qyqrru4992hsmqxnzkyl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
+          <t>bc1qttmz4kvr8tr6alvmn3zpd5mg53e787rq8v06z0qyqrru4992hsmqxnzkyl</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Coinbase Prime Custody</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>1805690736.550816</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1789915482.375</v>
+        <v>890992256</v>
       </c>
       <c r="M20" t="n">
-        <v>594733.0817238287</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>589057.6272406335</v>
+        <v>10113.64902039</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
+          <t>https://intel.arkm.com/explorer/address/3MqUP6G1daVS5YTD8fz3QgwjZortWwxXFd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
+          <t>3MqUP6G1daVS5YTD8fz3QgwjZortWwxXFd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Coinbase Prime</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1742,7 +1678,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://www.coinbase.com/prime</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1752,197 +1688,171 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1344068978.838293</v>
+        <v>12392146220.32094</v>
       </c>
       <c r="L21" t="n">
-        <v>1328825799.614612</v>
+        <v>12411872085.79762</v>
       </c>
       <c r="M21" t="n">
-        <v>442305.5390923287</v>
+        <v>138836.60664855</v>
       </c>
       <c r="N21" t="n">
-        <v>437809.72259879</v>
+        <v>139055.14156168</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q9exg34dkmgxu28yektgn929jpjpzukhhl2r3zr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
+          <t>bc1q9exg34dkmgxu28yektgn929jpjpzukhhl2r3zr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1293343038.434332</v>
+        <v>1253649135.318622</v>
       </c>
       <c r="L22" t="n">
-        <v>1324391575.568359</v>
+        <v>1293132826.946991</v>
       </c>
       <c r="M22" t="n">
-        <v>429238.3701466272</v>
+        <v>14038.9716853</v>
       </c>
       <c r="N22" t="n">
-        <v>438759.19883991</v>
+        <v>14488.87039104</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
+          <t>https://intel.arkm.com/explorer/address/3M7VitwPb1NytoSGb9C3TfrfoNPTt5nZqV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
+          <t>3M7VitwPb1NytoSGb9C3TfrfoNPTt5nZqV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>1173967760.719858</v>
+        <v>890987712</v>
       </c>
       <c r="L23" t="n">
-        <v>1270163990.661506</v>
+        <v>888248576</v>
       </c>
       <c r="M23" t="n">
-        <v>386660.557370076</v>
+        <v>10144.91987561</v>
       </c>
       <c r="N23" t="n">
-        <v>418910.38966375</v>
+        <v>10144.91987561</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
+          <t>https://intel.arkm.com/explorer/address/38ACfxHJwKnKFW2Evmnk58Aj9CBF7t3T88</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
+          <t>38ACfxHJwKnKFW2Evmnk58Aj9CBF7t3T88</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1952,567 +1862,505 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>1382897029.985585</v>
+        <v>574414355.6092997</v>
       </c>
       <c r="L24" t="n">
-        <v>1488603550.892896</v>
+        <v>631692726.9306631</v>
       </c>
       <c r="M24" t="n">
-        <v>460613.5539768328</v>
+        <v>6488.57436362</v>
       </c>
       <c r="N24" t="n">
-        <v>492936.2972540337</v>
+        <v>7096.85830225</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
+          <t>https://intel.arkm.com/explorer/address/3P4Fjuyn8SMeMV3SVCLUw88zhTk38aqCB8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
+          <t>3P4Fjuyn8SMeMV3SVCLUw88zhTk38aqCB8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>3368416794.522798</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3349470505.026005</v>
+        <v>890987712</v>
       </c>
       <c r="M25" t="n">
-        <v>1112673.025008726</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1105829.295316693</v>
+        <v>10144.91999566</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q7trt2zh5lzd5sap0mqgd246kuq9g0kwg6zhhy3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
+          <t>bc1q7trt2zh5lzd5sap0mqgd246kuq9g0kwg6zhhy3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3312209265.272538</v>
+        <v>2739248825.129715</v>
       </c>
       <c r="L26" t="n">
-        <v>3152875530.776313</v>
+        <v>2717886038</v>
       </c>
       <c r="M26" t="n">
-        <v>1097443.74367123</v>
+        <v>30536.40046463</v>
       </c>
       <c r="N26" t="n">
-        <v>1045229.99456863</v>
+        <v>30327.53268886</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q8s3h3vw5xufdas890q29lpuca56r0ezqar0mvs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
+          <t>bc1q8s3h3vw5xufdas890q29lpuca56r0ezqar0mvs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="b">
         <v>0</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Cumberland DRW</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://cumberland.io</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>3139024069.153679</v>
+        <v>815350081.766449</v>
       </c>
       <c r="L27" t="n">
-        <v>3139024076.247688</v>
+        <v>733927690.8494632</v>
       </c>
       <c r="M27" t="n">
-        <v>1030681.991847288</v>
+        <v>9085.51926313</v>
       </c>
       <c r="N27" t="n">
-        <v>1030681.991847288</v>
+        <v>8174.84360642</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qsg6x2cvm75xuddn5g0ss9zglaamgz90q8vcp8w</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>bc1qsg6x2cvm75xuddn5g0ss9zglaamgz90q8vcp8w</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>Paxos</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>custodian</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://paxos.com</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>2526004292.352442</v>
+        <v>637261120</v>
       </c>
       <c r="L28" t="n">
-        <v>2520657881.674536</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>838106.0445600834</v>
+        <v>6757.16137194</v>
       </c>
       <c r="N28" t="n">
-        <v>836593.2035643058</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
+          <t>https://intel.arkm.com/explorer/address/1KNm4K8GUK8sMoxc2Z3zU8Uv5FDVjrA72p</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
+          <t>1KNm4K8GUK8sMoxc2Z3zU8Uv5FDVjrA72p</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jump Crypto</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://jumptrading.com</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>1920208684.670458</v>
+        <v>554282389.6969452</v>
       </c>
       <c r="L29" t="n">
-        <v>1920208675.760169</v>
+        <v>677227188.2988281</v>
       </c>
       <c r="M29" t="n">
-        <v>634952.1039373239</v>
+        <v>6224.57347929</v>
       </c>
       <c r="N29" t="n">
-        <v>634952.1039373239</v>
+        <v>7527.63991861</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>https://intel.arkm.com/explorer/address/3EX1HHEwPtkxitrcYpymHFWu91LNsn8wD4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>3EX1HHEwPtkxitrcYpymHFWu91LNsn8wD4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
         <v>0</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>1828583320.51047</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1817198543.676425</v>
+        <v>884654976</v>
       </c>
       <c r="M30" t="n">
-        <v>600960.0841306447</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>597144.7303148605</v>
+        <v>10051.07</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
+          <t>https://intel.arkm.com/explorer/address/3JZq4atUahhuA9rLhXLMhhTo133J9rF97j</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
+          <t>3JZq4atUahhuA9rLhXLMhhTo133J9rF97j</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="b">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bitfinex</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://bitfinex.com</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Cold Wallet</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K31" t="n">
-        <v>1795113175.857878</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1795113173.933729</v>
+        <v>700752000</v>
       </c>
       <c r="M31" t="n">
-        <v>594172.2191319884</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>594172.2191319884</v>
+        <v>8000.00008502</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
+          <t>https://intel.arkm.com/explorer/address/34PhCF947JMQtCn7FD1J3Xd3c2VSxAwda8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
+          <t>34PhCF947JMQtCn7FD1J3Xd3c2VSxAwda8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="b">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Lido</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>liquid-staking</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://lido.fi</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Lido Staked Ether Token (STETH)</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>1123517169.793615</v>
+        <v>840646976</v>
       </c>
       <c r="L32" t="n">
-        <v>1093206077.320312</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>365163.3887365008</v>
+        <v>9551.069985599999</v>
       </c>
       <c r="N32" t="n">
-        <v>354502.1732189195</v>
+        <v>0</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q7cyrfmck2ffu2ud3rn5l5a8yv6f0chkp0zpemf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
+          <t>bc1q7cyrfmck2ffu2ud3rn5l5a8yv6f0chkp0zpemf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Crypto.com</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2522,7 +2370,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://crypto.com</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2532,57 +2380,55 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>947683471.8005881</v>
+        <v>1543277924.057187</v>
       </c>
       <c r="L33" t="n">
-        <v>927957386.6976464</v>
+        <v>1659599051.558694</v>
       </c>
       <c r="M33" t="n">
-        <v>314588.904508293</v>
+        <v>17361.00957206</v>
       </c>
       <c r="N33" t="n">
-        <v>305710.734681</v>
+        <v>18641.03400396</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qzzfkyk3z94fhk26fu545fchk5v947ghhjfuc2t</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
+          <t>bc1qzzfkyk3z94fhk26fu545fchk5v947ghhjfuc2t</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2592,67 +2438,57 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Eth2 Staking</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://kraken.com</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1368462592</v>
       </c>
       <c r="L34" t="n">
-        <v>1110263200</v>
+        <v>1363357440</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>15611.91659811</v>
       </c>
       <c r="N34" t="n">
-        <v>360000</v>
+        <v>15611.91659811</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q42kvqt0e3f27qhd2ucnprarl5ywpuj7tu0h9v2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>bc1q42kvqt0e3f27qhd2ucnprarl5ywpuj7tu0h9v2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D35" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>FalconX</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2662,7 +2498,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
+          <t>https://falconx.io/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2672,215 +2508,243 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>6522517760.568218</v>
+        <v>1252858640.240402</v>
       </c>
       <c r="L35" t="n">
-        <v>6544406569.882905</v>
+        <v>1200412245.446109</v>
       </c>
       <c r="M35" t="n">
-        <v>2152151.738769514</v>
+        <v>14256.43421203</v>
       </c>
       <c r="N35" t="n">
-        <v>2159937.155797073</v>
+        <v>13640.51676859</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
+          <t>https://intel.arkm.com/explorer/address/3JZ3byZy7TTrfy8zdxrm9iqJrdsaZ5CrNw</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
+          <t>3JZ3byZy7TTrfy8zdxrm9iqJrdsaZ5CrNw</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D36" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Crypto.com</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://crypto.com</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>2166026395.65625</v>
+        <v>727600715.354599</v>
       </c>
       <c r="L36" t="n">
-        <v>2166026369.46875</v>
+        <v>661005746.7650909</v>
       </c>
       <c r="M36" t="n">
-        <v>705536</v>
+        <v>8190.96423</v>
       </c>
       <c r="N36" t="n">
-        <v>705536</v>
+        <v>7406.96123</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qjcm02r55a90v88xwe4alew4y4uyft2htvnywv2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
+          <t>bc1qjcm02r55a90v88xwe4alew4y4uyft2htvnywv2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D37" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://robinhood.com/</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>1562000453.175918</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1561998837.875261</v>
+        <v>578351338.296875</v>
       </c>
       <c r="M37" t="n">
-        <v>506460.5407311035</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>506460.0250524727</v>
+        <v>6497.17225553</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
+          <t>https://intel.arkm.com/explorer/address/12DezRFkKToAiLTDNru1g7FuvtAWMwCZ7N</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
+          <t>12DezRFkKToAiLTDNru1g7FuvtAWMwCZ7N</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BatchDeposit</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1545610913.739746</v>
+        <v>8519351280.572376</v>
       </c>
       <c r="L38" t="n">
-        <v>1545878735.992676</v>
+        <v>8517370211.078125</v>
       </c>
       <c r="M38" t="n">
-        <v>504146.34</v>
+        <v>94755.14042914999</v>
       </c>
       <c r="N38" t="n">
-        <v>504235.746</v>
+        <v>94755.13992915</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
+          <t>https://intel.arkm.com/explorer/address/3EaWHFAWjgG7189kFD2P3hrMqt8qgbdrzN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
+          <t>3EaWHFAWjgG7189kFD2P3hrMqt8qgbdrzN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2890,181 +2754,175 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
-        <v>1077965793.272252</v>
+        <v>909467272.0109024</v>
       </c>
       <c r="L39" t="n">
-        <v>1069771973.026666</v>
+        <v>879535382</v>
       </c>
       <c r="M39" t="n">
-        <v>357123.4331164974</v>
+        <v>10143.97468692</v>
       </c>
       <c r="N39" t="n">
-        <v>354504.72875264</v>
+        <v>9839.09337852</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qmakjy7ns2z8vwgptf9vs8fndp304fg0p9xafm2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
+          <t>bc1qmakjy7ns2z8vwgptf9vs8fndp304fg0p9xafm2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="b">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PoolManager</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>3174996166.897975</v>
+        <v>852237999.390131</v>
       </c>
       <c r="L40" t="n">
-        <v>3166791861.890373</v>
+        <v>752332957.5</v>
       </c>
       <c r="M40" t="n">
-        <v>1047889.130250069</v>
+        <v>9530.16326116</v>
       </c>
       <c r="N40" t="n">
-        <v>1045368.98854005</v>
+        <v>8401.94441846</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
+          <t>https://intel.arkm.com/explorer/address/3LUATjKp4YfmCSSiN1h3juwrqNTyksXAjp</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
+          <t>3LUATjKp4YfmCSSiN1h3juwrqNTyksXAjp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D41" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="b">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fidelity FBTC ETF Inflows</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.fidelity.com/</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FBTC Inflows (Fidelity Custody Deposit)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K41" t="n">
-        <v>2984899075.064578</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2984899247.759352</v>
+        <v>674422062.8809814</v>
       </c>
       <c r="M41" t="n">
-        <v>938725.8018690519</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>938725.8573831373</v>
+        <v>7603.32414266</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qactqjuk4kghfgaqqt454hzzzs5lsaysunf80gh</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
+          <t>bc1qactqjuk4kghfgaqqt454hzzzs5lsaysunf80gh</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="b">
         <v>0</v>
       </c>
@@ -3074,181 +2932,179 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>1621622386.878073</v>
+        <v>6691793271.210578</v>
       </c>
       <c r="L42" t="n">
-        <v>1615157383.680816</v>
+        <v>6691935318.219632</v>
       </c>
       <c r="M42" t="n">
-        <v>535149.7368909797</v>
+        <v>75160.49887139999</v>
       </c>
       <c r="N42" t="n">
-        <v>532584.4342944291</v>
+        <v>75160.49887140001</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
+          <t>https://intel.arkm.com/explorer/address/335umQ4egqMjDo6wSXYwQZYPntZzMveNTJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
+          <t>335umQ4egqMjDo6wSXYwQZYPntZzMveNTJ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="b">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Coinbase Prime Custody</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>1539116512.23613</v>
+        <v>1478593385.59375</v>
       </c>
       <c r="L43" t="n">
-        <v>1468841741</v>
+        <v>1464197973.625</v>
       </c>
       <c r="M43" t="n">
-        <v>507035.1332085576</v>
+        <v>16432.04817912</v>
       </c>
       <c r="N43" t="n">
-        <v>486483.7066143855</v>
+        <v>16264.48841612</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>https://intel.arkm.com/explorer/address/1Kr6QSydW9bFQG1mXiPNNu6WpJGmUa9i1g</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>1Kr6QSydW9bFQG1mXiPNNu6WpJGmUa9i1g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D44" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kyber Network</t>
+          <t>Bitfinex</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://kyber.network</t>
+          <t>https://bitfinex.com</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Aggregator Executor V3</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1107427684.254632</v>
+        <v>931750222.3808618</v>
       </c>
       <c r="L44" t="n">
-        <v>1107251329.719594</v>
+        <v>1176093813.754185</v>
       </c>
       <c r="M44" t="n">
-        <v>362874.9629761748</v>
+        <v>10618.72915694</v>
       </c>
       <c r="N44" t="n">
-        <v>362823.5284547307</v>
+        <v>13338.28925354</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qx9n80t5q7tfmutzaj0ramzzzsvtveara68zntc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
+          <t>bc1qx9n80t5q7tfmutzaj0ramzzzsvtveara68zntc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D45" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3258,601 +3114,495 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Eth2 Staking</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1110263200</v>
+        <v>5181755569.479836</v>
       </c>
       <c r="L45" t="n">
-        <v>1102789560</v>
+        <v>5661058696.59375</v>
       </c>
       <c r="M45" t="n">
-        <v>360000</v>
+        <v>58727.58783513</v>
       </c>
       <c r="N45" t="n">
-        <v>360000</v>
+        <v>64186.61890506</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
+          <t>https://intel.arkm.com/explorer/address/1HDbEPC4ATYM9iebLgyWMwsicSZtYLmnEq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
+          <t>1HDbEPC4ATYM9iebLgyWMwsicSZtYLmnEq</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://coinbase.com</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
-        <v>918001940.1768073</v>
+        <v>504081504</v>
       </c>
       <c r="L46" t="n">
-        <v>918598516.78125</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>302134.900001667</v>
+        <v>5869.39809786</v>
       </c>
       <c r="N46" t="n">
-        <v>302134.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qk0ukgq09wfuj43lfwrxc3cvcujrk5akvp0lqll</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
+          <t>bc1qk0ukgq09wfuj43lfwrxc3cvcujrk5akvp0lqll</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D47" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="b">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Quoter</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>1816100064.355804</v>
+        <v>1530858476</v>
       </c>
       <c r="L47" t="n">
-        <v>1816099803.189476</v>
+        <v>1478899958.034462</v>
       </c>
       <c r="M47" t="n">
-        <v>596859.0595989513</v>
+        <v>16895.22958233</v>
       </c>
       <c r="N47" t="n">
-        <v>596858.9761758528</v>
+        <v>16261.55363876</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qjasf9z3h7w3jspkhtgatgpyvvzgpa2wwd2lr0eh5tx44reyn2k7sfc27a4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
+          <t>bc1qjasf9z3h7w3jspkhtgatgpyvvzgpa2wwd2lr0eh5tx44reyn2k7sfc27a4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D48" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Tether</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>stablecoin</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
+          <t>https://tether.to/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Bitcoin Reserves</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1297623623.14208</v>
+        <v>778702208.4915583</v>
       </c>
       <c r="L48" t="n">
-        <v>1273154808.163356</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>429917.0145423929</v>
+        <v>8888.888894260001</v>
       </c>
       <c r="N48" t="n">
-        <v>422000.41295201</v>
+        <v>0</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>https://intel.arkm.com/explorer/address/3MsfxyCEY5B4NUwKP66iqsbZsS5XRDm3Vj</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>3MsfxyCEY5B4NUwKP66iqsbZsS5XRDm3Vj</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D49" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
-        <v>1254014411.370105</v>
+        <v>713136640</v>
       </c>
       <c r="L49" t="n">
-        <v>1259993271.693302</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>413614.5619807786</v>
+        <v>8144.91996985</v>
       </c>
       <c r="N49" t="n">
-        <v>414981.55872983</v>
+        <v>0</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
+          <t>https://intel.arkm.com/explorer/address/1G47mSr3oANXMafVrR8UC4pzV7FEAzo3r9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
+          <t>1G47mSr3oANXMafVrR8UC4pzV7FEAzo3r9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D50" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://ether.fi/</t>
+          <t>https://gate.com</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LiquidityPool (Proxy)</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1078240797.985406</v>
+        <v>550576330.3153577</v>
       </c>
       <c r="L50" t="n">
-        <v>1075335264.820105</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>346849.2485119854</v>
+        <v>6158.99849773</v>
       </c>
       <c r="N50" t="n">
-        <v>356677.2505183262</v>
+        <v>0</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
+          <t>https://intel.arkm.com/explorer/address/3E8T3FPyyd4daRyjQdCNi8WV97v92XvQKu</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
+          <t>3E8T3FPyyd4daRyjQdCNi8WV97v92XvQKu</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D51" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="b">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Ether.fi</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>misc</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://ether.fi/</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>StakingManager (Proxy)</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>1024680392</v>
+        <v>523105164</v>
       </c>
       <c r="L51" t="n">
-        <v>1024680400</v>
+        <v>735605620</v>
       </c>
       <c r="M51" t="n">
-        <v>340000</v>
+        <v>5949</v>
       </c>
       <c r="N51" t="n">
-        <v>340000</v>
+        <v>7923.092641</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qptc9cz269u2mc5yguun5a5d6yd5c7f7ne4qj26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
+          <t>bc1qptc9cz269u2mc5yguun5a5d6yd5c7f7ne4qj26</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D52" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="b">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>FalconX</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://falconx.io/</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
-        <v>996835501.585402</v>
+        <v>1408599936.265086</v>
       </c>
       <c r="L52" t="n">
-        <v>913513631.0803859</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>337423.6618982208</v>
+        <v>16400.04538128</v>
       </c>
       <c r="N52" t="n">
-        <v>309146.26829891</v>
+        <v>0</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:38</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA712eF381fA0e8c0733Bd281A17974FBFAeab0b3</t>
+          <t>https://intel.arkm.com/explorer/address/bc1q6ccnyxn32035zwzrlt7z9nkufwrn27d8ezm8xa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xA712eF381fA0e8c0733Bd281A17974FBFAeab0b3</t>
+          <t>bc1q6ccnyxn32035zwzrlt7z9nkufwrn27d8ezm8xa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D53" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Coinbase Deposit</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
-        <v>14510156.75</v>
+        <v>830185264</v>
       </c>
       <c r="L53" t="n">
-        <v>14499727.25</v>
+        <v>834285328</v>
       </c>
       <c r="M53" t="n">
-        <v>1168734.40484002</v>
+        <v>8995.22959506</v>
       </c>
       <c r="N53" t="n">
-        <v>1168734.405206887</v>
+        <v>8995.22959506</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x7C876bdaA5c038E19F633714f622F6Def949B102</t>
+          <t>https://intel.arkm.com/explorer/address/13XJwZdXMh7D4rGd2og4sowZRz4vxNH1LB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x7C876bdaA5c038E19F633714f622F6Def949B102</t>
+          <t>13XJwZdXMh7D4rGd2og4sowZRz4vxNH1LB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="b">
         <v>0</v>
       </c>
@@ -3862,103 +3612,111 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
-        <v>47250057.32232746</v>
+        <v>711111168</v>
       </c>
       <c r="L54" t="n">
-        <v>47260034.796875</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3715883.819405941</v>
+        <v>7657.8023727</v>
       </c>
       <c r="N54" t="n">
-        <v>3715882.828758016</v>
+        <v>0</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x16463c6ce596C91d337495AE699F44D627C8357D</t>
+          <t>https://intel.arkm.com/explorer/address/37GgrfZcywSLuBpQDf1t6aJicWzHRf2GFB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x16463c6ce596C91d337495AE699F44D627C8357D</t>
+          <t>37GgrfZcywSLuBpQDf1t6aJicWzHRf2GFB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="b">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Twenty One Capital</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://xxi.money/</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
-        <v>19406606.00152278</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>19561140.5</v>
+        <v>2438727424</v>
       </c>
       <c r="M55" t="n">
-        <v>1439999.000112</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1452824</v>
+        <v>26917.22442797</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x651641299C7eC0aA44AD7eD9b7E12702fED2022f</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qppunwskzl7t3mtmcarlvpxjuzd8jy7l7ga49av2c78xg47fujncsrc76y6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x651641299C7eC0aA44AD7eD9b7E12702fED2022f</t>
+          <t>bc1qppunwskzl7t3mtmcarlvpxjuzd8jy7l7ga49av2c78xg47fujncsrc76y6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Bitstamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3968,579 +3726,589 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://bybit.com</t>
+          <t>https://bitstamp.net</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>20785196.20952347</v>
+        <v>1387214137.397675</v>
       </c>
       <c r="L56" t="n">
-        <v>24857220.30625832</v>
+        <v>1448960083.95829</v>
       </c>
       <c r="M56" t="n">
-        <v>1611108.109023147</v>
+        <v>15532.23774416</v>
       </c>
       <c r="N56" t="n">
-        <v>1929692.61043282</v>
+        <v>16216.92452783</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xa71Dbf81620EFc74E9089b413BC6357D6ad7edaf</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qn2cpj0hrl37wqh5q94kwrlhtj2lx8ahtw7ef5rg35tswxsqtvufqfmmrq2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xa71Dbf81620EFc74E9089b413BC6357D6ad7edaf</t>
+          <t>bc1qn2cpj0hrl37wqh5q94kwrlhtj2lx8ahtw7ef5rg35tswxsqtvufqfmmrq2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D57" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="b">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K57" t="n">
-        <v>28171344</v>
+        <v>1051530232.55556</v>
       </c>
       <c r="L57" t="n">
-        <v>28216598</v>
+        <v>1026853849.833294</v>
       </c>
       <c r="M57" t="n">
-        <v>2262758.519376952</v>
+        <v>11738.0355311</v>
       </c>
       <c r="N57" t="n">
-        <v>2262758.519376952</v>
+        <v>11472.53813037</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x177a7376860a04eEA6BF7fb3F39Bf10c49D3b42C</t>
+          <t>https://intel.arkm.com/explorer/address/324H9uyTV9bPgAVgmdJNxPKKKZmowk5CYq</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x177a7376860a04eEA6BF7fb3F39Bf10c49D3b42C</t>
+          <t>324H9uyTV9bPgAVgmdJNxPKKKZmowk5CYq</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blackhole</t>
+          <t>Bullish.com</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blackhole.xyz/</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>https://bullish.com/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K58" t="n">
-        <v>262203979.8933285</v>
+        <v>633025663.25</v>
       </c>
       <c r="L58" t="n">
-        <v>262241925.7994927</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>20402860.94111584</v>
+        <v>7081.68847928</v>
       </c>
       <c r="N58" t="n">
-        <v>20406555.90127004</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>https://intel.arkm.com/explorer/address/36YZXcTVLPdyapYuqXdJEt46oMVB2NrzVv</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>36YZXcTVLPdyapYuqXdJEt46oMVB2NrzVv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="b">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Kyber Network</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>https://kyber.network</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Aggregator Executor V3</t>
+          <t>Coinbase Prime Deposit</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>17335785.89675013</v>
+        <v>2056327465.400953</v>
       </c>
       <c r="L59" t="n">
-        <v>17338213.05145394</v>
+        <v>1997158098</v>
       </c>
       <c r="M59" t="n">
-        <v>1352146.247353066</v>
+        <v>23083.18547267</v>
       </c>
       <c r="N59" t="n">
-        <v>1352339.464412661</v>
+        <v>22444.11152656</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xFAD57d2039C21811C8F2B5D5B65308aa99D31559</t>
+          <t>https://intel.arkm.com/explorer/address/bc1quhruqrghgcca950rvhtrg7cpd7u8k6svpzgzmrjy8xyukacl5lkq0r8l2d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFAD57d2039C21811C8F2B5D5B65308aa99D31559</t>
+          <t>bc1quhruqrghgcca950rvhtrg7cpd7u8k6svpzgzmrjy8xyukacl5lkq0r8l2d</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D60" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://uniswap.org</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LINK-USDC</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>13183824.34509114</v>
+        <v>2378584146.543148</v>
       </c>
       <c r="L60" t="n">
-        <v>13127334.08421058</v>
+        <v>2371067480.086669</v>
       </c>
       <c r="M60" t="n">
-        <v>1021576.206992282</v>
+        <v>26761.81325754</v>
       </c>
       <c r="N60" t="n">
-        <v>1020446.956855342</v>
+        <v>26647.71028181</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xB1dB79aea0a13382DD9E279d96Bc9a468A2F4E87</t>
+          <t>https://intel.arkm.com/explorer/address/12XZMdaAGmcHf4ocFSqpd8jFd1WH7RHUPs</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xB1dB79aea0a13382DD9E279d96Bc9a468A2F4E87</t>
+          <t>12XZMdaAGmcHf4ocFSqpd8jFd1WH7RHUPs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D61" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="b">
         <v>0</v>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://bybit.com</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bitcoin</t>
+        </is>
+      </c>
       <c r="K61" t="n">
-        <v>258654097.6192747</v>
+        <v>2354140692.926308</v>
       </c>
       <c r="L61" t="n">
-        <v>258640310.4384772</v>
+        <v>2364741185.374374</v>
       </c>
       <c r="M61" t="n">
-        <v>20127850.08390066</v>
+        <v>26424.7920326</v>
       </c>
       <c r="N61" t="n">
-        <v>20126774.38648785</v>
+        <v>26544.55604981</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
+          <t>https://intel.arkm.com/explorer/address/352zzNHvsBTaUUNzqB5xbMo8EYdpvHJQB2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
+          <t>352zzNHvsBTaUUNzqB5xbMo8EYdpvHJQB2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D62" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CoW Protocol</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>dex-aggregator</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://cow.fi</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Settlement</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>25394317.49581813</v>
+        <v>6691920926.439903</v>
       </c>
       <c r="L62" t="n">
-        <v>25392649.6682221</v>
+        <v>6698443988.354437</v>
       </c>
       <c r="M62" t="n">
-        <v>1987335.693707502</v>
+        <v>75160.33694707</v>
       </c>
       <c r="N62" t="n">
-        <v>1987206.488999467</v>
+        <v>75224.13043725</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9c17f630DBde24eECe8fd248fAA2E51f690FF79B</t>
+          <t>https://intel.arkm.com/explorer/address/1DLeNApsHNNzUMNZJVoXeyEY5sdp8vzx3w</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x9c17f630DBde24eECe8fd248fAA2E51f690FF79B</t>
+          <t>1DLeNApsHNNzUMNZJVoXeyEY5sdp8vzx3w</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D63" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://chain.link</t>
+          <t>https://bybit.com</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Non-Circulating Supply</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>2394592469.560097</v>
       </c>
       <c r="L63" t="n">
-        <v>91370238.60000038</v>
+        <v>2401719580.873917</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>26902.33768776</v>
       </c>
       <c r="N63" t="n">
-        <v>7249999</v>
+        <v>26988.39510686</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x5d4F3C6fA16908609BAC31Ff148Bd002AA6b8c83</t>
+          <t>https://intel.arkm.com/explorer/address/15DomY3arDPw5jD658Mbf3AY3wT3YCDmW2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x5d4F3C6fA16908609BAC31Ff148Bd002AA6b8c83</t>
+          <t>15DomY3arDPw5jD658Mbf3AY3wT3YCDmW2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D64" t="b">
-        <v>1</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://uniswap.org</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LINK 2</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>20986348.1480168</v>
+        <v>1594027023.150391</v>
       </c>
       <c r="L64" t="n">
-        <v>20849287.89497352</v>
+        <v>1688945221.837891</v>
       </c>
       <c r="M64" t="n">
-        <v>1621112.308700075</v>
+        <v>17812.92640014</v>
       </c>
       <c r="N64" t="n">
-        <v>1611812.735932898</v>
+        <v>18855.98617503</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x841ed663F2636863D40be4EE76243377dff13a34</t>
+          <t>https://intel.arkm.com/explorer/address/bc1qm34lsc65zpw79lxes69zkqmk6ee3ewf0j77s3h</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x841ed663F2636863D40be4EE76243377dff13a34</t>
+          <t>bc1qm34lsc65zpw79lxes69zkqmk6ee3ewf0j77s3h</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D65" t="b">
-        <v>0</v>
-      </c>
+          <t>bitcoin</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4550,7 +4318,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://robinhood.com/</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4560,41 +4328,41 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>evm</t>
+          <t>bitcoin</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>15521368580.2511</v>
       </c>
       <c r="L65" t="n">
-        <v>12852238.72442627</v>
+        <v>15662862954.2443</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>174385.69436206</v>
       </c>
       <c r="N65" t="n">
-        <v>1013423.50366701</v>
+        <v>175892.51344249</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:07:35</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>bitcoin</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
+          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4608,43 +4376,63 @@
       <c r="E66" t="b">
         <v>0</v>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K66" t="n">
-        <v>47871193.90512696</v>
+        <v>6522565939.249249</v>
       </c>
       <c r="L66" t="n">
-        <v>47982489.66482782</v>
+        <v>6544378730.909774</v>
       </c>
       <c r="M66" t="n">
-        <v>3669792.511902842</v>
+        <v>2152167.118176993</v>
       </c>
       <c r="N66" t="n">
-        <v>3670827.390721438</v>
+        <v>2159928.146616589</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x79dD9327352BcF1dd16941899705E97b61F4DEcB</t>
+          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x79dD9327352BcF1dd16941899705E97b61F4DEcB</t>
+          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4653,29 +4441,29 @@
         </is>
       </c>
       <c r="D67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Market Maker</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4684,37 +4472,37 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>34382215.58863229</v>
+        <v>3062792793.929688</v>
       </c>
       <c r="L67" t="n">
-        <v>35643654.26248869</v>
+        <v>3062702168.987412</v>
       </c>
       <c r="M67" t="n">
-        <v>2702342.378479484</v>
+        <v>1011451.927096179</v>
       </c>
       <c r="N67" t="n">
-        <v>2786947.17555979</v>
+        <v>1011445.098873791</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xeFE267E44A58815DD2e319F3b9a679a5202da1ce</t>
+          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xeFE267E44A58815DD2e319F3b9a679a5202da1ce</t>
+          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4723,17 +4511,29 @@
         </is>
       </c>
       <c r="D68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Coinbase Prime</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/prime</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Gnosis Safe Proxy</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4742,37 +4542,37 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2526004292.352442</v>
       </c>
       <c r="L68" t="n">
-        <v>12630000</v>
+        <v>2520657881.674536</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>838106.0445600834</v>
       </c>
       <c r="N68" t="n">
-        <v>1000000</v>
+        <v>836593.2035643058</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4bD9a84F22bD479f630E2f6c3311285D6eb6B768</t>
+          <t>https://intel.arkm.com/explorer/address/0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x4bD9a84F22bD479f630E2f6c3311285D6eb6B768</t>
+          <t>0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4781,48 +4581,68 @@
         </is>
       </c>
       <c r="D69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Quoter</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K69" t="n">
-        <v>12826594.625</v>
+        <v>1816065916.698018</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1816066438.763736</v>
       </c>
       <c r="M69" t="n">
-        <v>978232.900842485</v>
+        <v>596847.9614221724</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>596848.1282641541</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xa42D0A18B834F52e41bEDdEaA2940165db3DA9a3</t>
+          <t>https://intel.arkm.com/explorer/address/0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xa42D0A18B834F52e41bEDdEaA2940165db3DA9a3</t>
+          <t>0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4831,29 +4651,29 @@
         </is>
       </c>
       <c r="D70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://chain.link</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Non-Circulating Supply</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4862,37 +4682,37 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1316808887.357698</v>
       </c>
       <c r="L70" t="n">
-        <v>50479988</v>
+        <v>1326097428.843616</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>434123.9310645718</v>
       </c>
       <c r="N70" t="n">
-        <v>3999999</v>
+        <v>437033.67578649</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4901,29 +4721,29 @@
         </is>
       </c>
       <c r="D71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Kyber Network</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://kyber.network</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Aggregator Executor V3</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4932,37 +4752,37 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>104095106.5184093</v>
+        <v>1107493467.150809</v>
       </c>
       <c r="L71" t="n">
-        <v>93949095.64109012</v>
+        <v>1107947262.514511</v>
       </c>
       <c r="M71" t="n">
-        <v>8051733.00265503</v>
+        <v>362895.9410975733</v>
       </c>
       <c r="N71" t="n">
-        <v>7276679.69490672</v>
+        <v>363045.7600727631</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x5fA0199427243EB13B14409Fb5197e641805c78B</t>
+          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x5fA0199427243EB13B14409Fb5197e641805c78B</t>
+          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4971,17 +4791,29 @@
         </is>
       </c>
       <c r="D72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Gnosis Safe Proxy</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4990,37 +4822,37 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>20519058.25</v>
+        <v>4631714624.43821</v>
       </c>
       <c r="L72" t="n">
-        <v>19617667.609375</v>
+        <v>4633020367.695312</v>
       </c>
       <c r="M72" t="n">
-        <v>1521320.56</v>
+        <v>1527482.304299085</v>
       </c>
       <c r="N72" t="n">
-        <v>1456373.058080187</v>
+        <v>1527427.73981932</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x2B83aaCB0dD973866B563cFb0EF0AEF24B93200b</t>
+          <t>https://intel.arkm.com/explorer/address/0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x2B83aaCB0dD973866B563cFb0EF0AEF24B93200b</t>
+          <t>0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5034,12 +4866,24 @@
       <c r="E73" t="b">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5048,37 +4892,37 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>22546754.3841916</v>
+        <v>3368447720.767656</v>
       </c>
       <c r="L73" t="n">
-        <v>25562102.421875</v>
+        <v>3349778437.088505</v>
       </c>
       <c r="M73" t="n">
-        <v>1783210.356187327</v>
+        <v>1112682.88413621</v>
       </c>
       <c r="N73" t="n">
-        <v>2006886.552708601</v>
+        <v>1105927.641922176</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
+          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
+          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5094,7 +4938,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5104,7 +4948,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5118,37 +4962,37 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>19629004.43666135</v>
+        <v>1380449619.705878</v>
       </c>
       <c r="L74" t="n">
-        <v>20273150.78455508</v>
+        <v>1362671509.547991</v>
       </c>
       <c r="M74" t="n">
-        <v>1523763.185222645</v>
+        <v>453489.1777541857</v>
       </c>
       <c r="N74" t="n">
-        <v>1566978.97891103</v>
+        <v>448556.73441576</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x628f0371870B0997914b29acE817C2281E4aB268</t>
+          <t>https://intel.arkm.com/explorer/address/0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x628f0371870B0997914b29acE817C2281E4aB268</t>
+          <t>0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5162,12 +5006,24 @@
       <c r="E75" t="b">
         <v>0</v>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5176,37 +5032,37 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1293343038.434332</v>
       </c>
       <c r="L75" t="n">
-        <v>13848439.28125</v>
+        <v>1324391575.568359</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>429238.3701466272</v>
       </c>
       <c r="N75" t="n">
-        <v>1093628.876695701</v>
+        <v>438759.19883991</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
+          <t>https://intel.arkm.com/explorer/address/0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
+          <t>0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5215,29 +5071,29 @@
         </is>
       </c>
       <c r="D76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://uniswap.org</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Uniswap v4 Positions NFT (UNI-V4-POSM)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5246,37 +5102,37 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>388838618.8703228</v>
+        <v>1193275638.45775</v>
       </c>
       <c r="L76" t="n">
-        <v>384595566.8322228</v>
+        <v>1193275638.115657</v>
       </c>
       <c r="M76" t="n">
-        <v>30272473.60057416</v>
+        <v>394289.2296557389</v>
       </c>
       <c r="N76" t="n">
-        <v>30006323.15754343</v>
+        <v>394289.2296557389</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
+          <t>https://intel.arkm.com/explorer/address/0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
+          <t>0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5292,22 +5148,22 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Binance Deposit</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5316,37 +5172,37 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>68467747.39763168</v>
+        <v>1173967760.719858</v>
       </c>
       <c r="L77" t="n">
-        <v>68496976.63085938</v>
+        <v>1270163981.644237</v>
       </c>
       <c r="M77" t="n">
-        <v>5300003.494641677</v>
+        <v>386660.557370076</v>
       </c>
       <c r="N77" t="n">
-        <v>5300003.494641677</v>
+        <v>418910.38675825</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x60030D523A80488e4c5D669E6608022Caba471d9</t>
+          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x60030D523A80488e4c5D669E6608022Caba471d9</t>
+          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5355,17 +5211,29 @@
         </is>
       </c>
       <c r="D78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Binance Deposit</t>
+          <t>PoolManager</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5374,37 +5242,37 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>21270900.5001344</v>
+        <v>3174969695.376192</v>
       </c>
       <c r="L78" t="n">
-        <v>21249335.80026245</v>
+        <v>3166875855.470942</v>
       </c>
       <c r="M78" t="n">
-        <v>1589824.00001</v>
+        <v>1047880.449141952</v>
       </c>
       <c r="N78" t="n">
-        <v>1589844.00003</v>
+        <v>1045395.793743831</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x835678a611B28684005a5e2233695fB6cbbB0007</t>
+          <t>https://intel.arkm.com/explorer/address/0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x835678a611B28684005a5e2233695fB6cbbB0007</t>
+          <t>0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5435,7 +5303,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5444,37 +5312,37 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>19774932.25140645</v>
+        <v>1344068978.838293</v>
       </c>
       <c r="L79" t="n">
-        <v>16389601</v>
+        <v>1328928020.547524</v>
       </c>
       <c r="M79" t="n">
-        <v>1443824.000102</v>
+        <v>442305.5390923287</v>
       </c>
       <c r="N79" t="n">
-        <v>1189376</v>
+        <v>437842.39226071</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA69babEF1cA67A37Ffaf7a485DfFF3382056e78C</t>
+          <t>https://intel.arkm.com/explorer/address/0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xA69babEF1cA67A37Ffaf7a485DfFF3382056e78C</t>
+          <t>0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5483,29 +5351,29 @@
         </is>
       </c>
       <c r="D80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Symbolic Capital Partners</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://symbolic.partners</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MEV Bot</t>
+          <t>Eth2 Staking</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5514,37 +5382,37 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>15441920.96195602</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>15487824.16600609</v>
+        <v>1110263200</v>
       </c>
       <c r="M80" t="n">
-        <v>1215029.865619221</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1218159.352874641</v>
+        <v>360000</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x345366e5142828A66Ee80163b1f30dbE2eAbd566</t>
+          <t>https://intel.arkm.com/explorer/address/0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x345366e5142828A66Ee80163b1f30dbE2eAbd566</t>
+          <t>0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5558,12 +5426,24 @@
       <c r="E81" t="b">
         <v>0</v>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FalconX</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://falconx.io/</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5572,37 +5452,37 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>13254146</v>
+        <v>996835501.585402</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>913513631.0803859</v>
       </c>
       <c r="M81" t="n">
-        <v>1062030.95984429</v>
+        <v>337423.6618982208</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>309146.26829891</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xF977814e90dA44bFA03b6295A0616a897441aceC</t>
+          <t>https://intel.arkm.com/explorer/address/0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xF977814e90dA44bFA03b6295A0616a897441aceC</t>
+          <t>0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5633,7 +5513,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5642,37 +5522,37 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>90764924.25</v>
+        <v>947683471.8005881</v>
       </c>
       <c r="L82" t="n">
-        <v>41280000</v>
+        <v>927957507.0837395</v>
       </c>
       <c r="M82" t="n">
-        <v>7178890.169000001</v>
+        <v>314588.904508293</v>
       </c>
       <c r="N82" t="n">
-        <v>3000000</v>
+        <v>305710.772442</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
+          <t>https://intel.arkm.com/explorer/address/0x4200000000000000000000000000000000000006</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
+          <t>0x4200000000000000000000000000000000000006</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5681,68 +5561,48 @@
         </is>
       </c>
       <c r="D83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>PoolManager</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
-        <v>53894257.19942954</v>
+        <v>5488477326.124804</v>
       </c>
       <c r="L83" t="n">
-        <v>53352933.35450052</v>
+        <v>5475374837.41299</v>
       </c>
       <c r="M83" t="n">
-        <v>4226218.01933802</v>
+        <v>1811581.583997438</v>
       </c>
       <c r="N83" t="n">
-        <v>4173730.660834217</v>
+        <v>1807661.347392329</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
+          <t>https://intel.arkm.com/explorer/address/0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
+          <t>0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5751,17 +5611,29 @@
         </is>
       </c>
       <c r="D84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Market Maker</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5770,37 +5642,37 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>18744344.71636626</v>
+        <v>3312587733.3741</v>
       </c>
       <c r="L84" t="n">
-        <v>18713528.14398619</v>
+        <v>3152875530.776313</v>
       </c>
       <c r="M84" t="n">
-        <v>1460533.54276921</v>
+        <v>1097564.703663301</v>
       </c>
       <c r="N84" t="n">
-        <v>1457944.470146326</v>
+        <v>1045229.99456863</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x35264C7443CB18E22FC3fC0517519E769b644EBD</t>
+          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x35264C7443CB18E22FC3fC0517519E769b644EBD</t>
+          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5814,12 +5686,24 @@
       <c r="E85" t="b">
         <v>0</v>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Coinbase Deposit</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5828,37 +5712,37 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>16534754</v>
+        <v>1828583320.51047</v>
       </c>
       <c r="L85" t="n">
-        <v>16525757</v>
+        <v>1817198543.676425</v>
       </c>
       <c r="M85" t="n">
-        <v>1239816.64</v>
+        <v>600960.0841306447</v>
       </c>
       <c r="N85" t="n">
-        <v>1239816.6401</v>
+        <v>597144.7303148605</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>https://intel.arkm.com/explorer/address/0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5867,68 +5751,48 @@
         </is>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
-        <v>217202021.8592823</v>
+        <v>1796617438.186003</v>
       </c>
       <c r="L86" t="n">
-        <v>216820271.0632039</v>
+        <v>1796617436.308729</v>
       </c>
       <c r="M86" t="n">
-        <v>17047341.1926138</v>
+        <v>594652.6468261391</v>
       </c>
       <c r="N86" t="n">
-        <v>17020768.79973299</v>
+        <v>594652.6468261391</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf5213a6a2f0890321712520b8048D9886c1A9900</t>
+          <t>https://intel.arkm.com/explorer/address/0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xf5213a6a2f0890321712520b8048D9886c1A9900</t>
+          <t>0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5945,40 +5809,48 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K87" t="n">
-        <v>23113137.42625093</v>
+        <v>1539116512.23613</v>
       </c>
       <c r="L87" t="n">
-        <v>22962400.11697388</v>
+        <v>1468841741</v>
       </c>
       <c r="M87" t="n">
-        <v>1787250.399245857</v>
+        <v>507035.1332085576</v>
       </c>
       <c r="N87" t="n">
-        <v>1773772.35222</v>
+        <v>486483.7066143855</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x5a52E96BAcdaBb82fd05763E25335261B270Efcb</t>
+          <t>https://intel.arkm.com/explorer/address/0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x5a52E96BAcdaBb82fd05763E25335261B270Efcb</t>
+          <t>0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5987,29 +5859,29 @@
         </is>
       </c>
       <c r="D88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://ether.fi/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>LiquidityPool (Proxy)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6018,37 +5890,37 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>16389601</v>
+        <v>1078237598.939264</v>
       </c>
       <c r="L88" t="n">
-        <v>60951732.25</v>
+        <v>1075335264.820105</v>
       </c>
       <c r="M88" t="n">
-        <v>1189376</v>
+        <v>346848.2185119853</v>
       </c>
       <c r="N88" t="n">
-        <v>4803824</v>
+        <v>356677.2505183262</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x7914663715665dB7BE9B17Af046292A879c06f48</t>
+          <t>https://intel.arkm.com/explorer/address/0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x7914663715665dB7BE9B17Af046292A879c06f48</t>
+          <t>0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6068,37 +5940,37 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
-        <v>15439457.0640564</v>
+        <v>3139024069.153679</v>
       </c>
       <c r="L89" t="n">
-        <v>15439457.0640564</v>
+        <v>3139024076.247688</v>
       </c>
       <c r="M89" t="n">
-        <v>1188891.18322697</v>
+        <v>1030681.991847288</v>
       </c>
       <c r="N89" t="n">
-        <v>1188891.18322697</v>
+        <v>1030681.991847288</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x0D0707963952f2fBA59dD06f2b425ace40b492Fe</t>
+          <t>https://intel.arkm.com/explorer/address/0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x0D0707963952f2fBA59dD06f2b425ace40b492Fe</t>
+          <t>0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6107,68 +5979,48 @@
         </is>
       </c>
       <c r="D90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>https://gate.com</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
-        <v>14800213.49018702</v>
+        <v>2984899075.064578</v>
       </c>
       <c r="L90" t="n">
-        <v>14440999.72962726</v>
+        <v>2984899247.759352</v>
       </c>
       <c r="M90" t="n">
-        <v>1147515.815346689</v>
+        <v>938725.8018690519</v>
       </c>
       <c r="N90" t="n">
-        <v>1124207.685366812</v>
+        <v>938725.8573831373</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xD8B671d6f61f40025d8538208a1bD3B57A127805</t>
+          <t>https://intel.arkm.com/explorer/address/0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xD8B671d6f61f40025d8538208a1bD3B57A127805</t>
+          <t>0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6185,48 +6037,40 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Gnosis Safe Proxy</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
-        <v>12630000</v>
+        <v>1562000453.175918</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1561998837.875261</v>
       </c>
       <c r="M91" t="n">
-        <v>1000000</v>
+        <v>506460.5407311035</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>506460.0250524727</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>https://intel.arkm.com/explorer/address/0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6240,24 +6084,12 @@
       <c r="E92" t="b">
         <v>0</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Market Maker</t>
+          <t>BatchDeposit</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6266,37 +6098,37 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>126133310.2011374</v>
+        <v>1545610913.739746</v>
       </c>
       <c r="L92" t="n">
-        <v>126073586.4216383</v>
+        <v>1545878735.992676</v>
       </c>
       <c r="M92" t="n">
-        <v>9735019.949889055</v>
+        <v>504146.34</v>
       </c>
       <c r="N92" t="n">
-        <v>9726177.28969945</v>
+        <v>504235.746</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x5E8C8A7243651DB1384C0dDfDbE39761E8e7E51a</t>
+          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x5E8C8A7243651DB1384C0dDfDbE39761E8e7E51a</t>
+          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6305,29 +6137,29 @@
         </is>
       </c>
       <c r="D93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>lending-decentralized</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://aave.com</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Aave Ethereum LINK (aEthLINK)</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6336,37 +6168,37 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>27438966.90139333</v>
+        <v>1254014411.370105</v>
       </c>
       <c r="L93" t="n">
-        <v>16867064.22702047</v>
+        <v>1259960331.731031</v>
       </c>
       <c r="M93" t="n">
-        <v>2167282.538720507</v>
+        <v>413614.5619807786</v>
       </c>
       <c r="N93" t="n">
-        <v>1320037.131739111</v>
+        <v>414970.95241538</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xD50f074Ec5c7997cE1DaacB513Ec194C480878Af</t>
+          <t>https://intel.arkm.com/explorer/address/0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xD50f074Ec5c7997cE1DaacB513Ec194C480878Af</t>
+          <t>0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6385,7 +6217,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Gnosis Safe Proxy</t>
+          <t>Eth2 Beacon Deposit Contract</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6394,37 +6226,37 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>25535238</v>
+        <v>9743785746.779785</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>2024999</v>
+        <v>3185819.797795997</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xAC64829CDa33bb11C26074CE66E8549e4b8a66A2</t>
+          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xAC64829CDa33bb11C26074CE66E8549e4b8a66A2</t>
+          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6438,12 +6270,24 @@
       <c r="E95" t="b">
         <v>0</v>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6452,37 +6296,37 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>22619529.95669994</v>
+        <v>9376187036.164282</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>9091454821.006443</v>
       </c>
       <c r="M95" t="n">
-        <v>1800871.669636466</v>
+        <v>3102964.586759099</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3006182.85966278</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x3db910Fac1dbE434f397c07c2B473983eFcf25DC</t>
+          <t>https://intel.arkm.com/explorer/address/0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x3db910Fac1dbE434f397c07c2B473983eFcf25DC</t>
+          <t>0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6491,7 +6335,7 @@
         </is>
       </c>
       <c r="D96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
@@ -6502,37 +6346,37 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
-        <v>13133860.875</v>
+        <v>1920208281.705265</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1920208272.921999</v>
       </c>
       <c r="M96" t="n">
-        <v>1052392.729393878</v>
+        <v>634951.9741911336</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>634951.9742317306</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xEff6cb8b614999d130E537751Ee99724D01aA167</t>
+          <t>https://intel.arkm.com/explorer/address/0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0xEff6cb8b614999d130E537751Ee99724D01aA167</t>
+          <t>0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6541,7 +6385,7 @@
         </is>
       </c>
       <c r="D97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
@@ -6549,48 +6393,40 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>MEV Bot</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
-        <v>13356031.31905337</v>
+        <v>1621625210.809175</v>
       </c>
       <c r="L97" t="n">
-        <v>13374846.82567835</v>
+        <v>1615197603.046842</v>
       </c>
       <c r="M97" t="n">
-        <v>1024197.022098323</v>
+        <v>535150.2837216775</v>
       </c>
       <c r="N97" t="n">
-        <v>1024596.241967763</v>
+        <v>532597.2069405273</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x09ad18BD5D19d6893444B73b6245eC55319F046c</t>
+          <t>https://intel.arkm.com/explorer/address/0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0x09ad18BD5D19d6893444B73b6245eC55319F046c</t>
+          <t>0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6606,7 +6442,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6616,12 +6452,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6630,37 +6466,37 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1380580877.141225</v>
       </c>
       <c r="L98" t="n">
-        <v>12958983</v>
+        <v>1488601158.993964</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>459867.8170880997</v>
       </c>
       <c r="N98" t="n">
-        <v>1035062.502286183</v>
+        <v>492935.4977716298</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>https://intel.arkm.com/explorer/address/0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6676,61 +6512,53 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
-        <v>82361081.56773783</v>
+        <v>918001940.1768073</v>
       </c>
       <c r="L99" t="n">
-        <v>79307599.98178592</v>
+        <v>918598516.78125</v>
       </c>
       <c r="M99" t="n">
-        <v>6387366.921905445</v>
+        <v>302134.900001667</v>
       </c>
       <c r="N99" t="n">
-        <v>6151497.25202778</v>
+        <v>302134.9</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>https://intel.arkm.com/explorer/address/0xd01607c3C5eCABa394D8be377a08590149325722</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>0xd01607c3C5eCABa394D8be377a08590149325722</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6739,29 +6567,29 @@
         </is>
       </c>
       <c r="D100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>lending-decentralized</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
+          <t>https://aave.com</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>WrappedTokenGatewayV3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6770,37 +6598,37 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>52032983.21669314</v>
+        <v>3233979215.459034</v>
       </c>
       <c r="L100" t="n">
-        <v>52029688.80140877</v>
+        <v>3233979217.135644</v>
       </c>
       <c r="M100" t="n">
-        <v>4097981.268737037</v>
+        <v>1078159.414922242</v>
       </c>
       <c r="N100" t="n">
-        <v>4097870.976269291</v>
+        <v>1078159.414922242</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
+          <t>https://intel.arkm.com/explorer/address/0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
+          <t>0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6809,60 +6637,64 @@
         </is>
       </c>
       <c r="D101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>B2C2 Group</t>
+          <t>jaredfromsubway (MEV)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>https://www.b2c2.com</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>mev</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>MEV Bot</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K101" t="n">
-        <v>24003399.83726284</v>
+        <v>2429887582.636902</v>
       </c>
       <c r="L101" t="n">
-        <v>19574642.12304688</v>
+        <v>2429887579.240764</v>
       </c>
       <c r="M101" t="n">
-        <v>1857918.800906841</v>
+        <v>802000.1996770022</v>
       </c>
       <c r="N101" t="n">
-        <v>1547125.794475885</v>
+        <v>802000.2012989126</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
+          <t>https://intel.arkm.com/explorer/address/0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
+          <t>0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6871,29 +6703,29 @@
         </is>
       </c>
       <c r="D102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://uniswap.org</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Nonfungible Position Manager</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6902,37 +6734,37 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>14660567.20819966</v>
+        <v>1297623623.14208</v>
       </c>
       <c r="L102" t="n">
-        <v>15006904.95429163</v>
+        <v>1273155395.23965</v>
       </c>
       <c r="M102" t="n">
-        <v>1179676.867001697</v>
+        <v>429917.0145423929</v>
       </c>
       <c r="N102" t="n">
-        <v>1207587.055316765</v>
+        <v>422000.60045102</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x7f604D597c15b2e2F60DC645844f68b1D781b752</t>
+          <t>https://intel.arkm.com/explorer/address/0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x7f604D597c15b2e2F60DC645844f68b1D781b752</t>
+          <t>0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6946,63 +6778,43 @@
       <c r="E103" t="b">
         <v>0</v>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Bitstamp</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>https://bitstamp.net</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>12076628.14051428</v>
+        <v>1213036041.498139</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1213036040.993315</v>
       </c>
       <c r="M103" t="n">
-        <v>940434.4009390965</v>
+        <v>400379.9610025365</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>400379.9610025365</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xd312d0403a2196d95BC4eB5BEac60703a93B1944</t>
+          <t>https://intel.arkm.com/explorer/address/0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0xd312d0403a2196d95BC4eB5BEac60703a93B1944</t>
+          <t>0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7016,12 +6828,24 @@
       <c r="E104" t="b">
         <v>0</v>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Eth2 Staking</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7030,37 +6854,37 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1110263200</v>
       </c>
       <c r="L104" t="n">
-        <v>13034408</v>
+        <v>1102789560</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="N104" t="n">
-        <v>1024486.356466608</v>
+        <v>360000</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9B1c1752B6B6eAF62a8c491A8681B32C1F7ecDE9</t>
+          <t>https://intel.arkm.com/explorer/address/0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0x9B1c1752B6B6eAF62a8c491A8681B32C1F7ecDE9</t>
+          <t>0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7069,17 +6893,29 @@
         </is>
       </c>
       <c r="D105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ether.fi</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>misc</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://ether.fi/</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Binance Deposit</t>
+          <t>StakingManager (Proxy)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7088,37 +6924,37 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>116314976</v>
+        <v>1024680392</v>
       </c>
       <c r="L105" t="n">
-        <v>116379500</v>
+        <v>1024680400</v>
       </c>
       <c r="M105" t="n">
-        <v>9224998</v>
+        <v>340000</v>
       </c>
       <c r="N105" t="n">
-        <v>9225000</v>
+        <v>340000</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>https://intel.arkm.com/explorer/address/0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7134,22 +6970,22 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7158,37 +6994,37 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>75972994.53531809</v>
+        <v>1393302544.028083</v>
       </c>
       <c r="L106" t="n">
-        <v>76755203.00034046</v>
+        <v>1395170004.140732</v>
       </c>
       <c r="M106" t="n">
-        <v>5822669.652420743</v>
+        <v>456792.2656770762</v>
       </c>
       <c r="N106" t="n">
-        <v>5879527.71360408</v>
+        <v>457242.1943745955</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf440838830CC265DB72C81bfBa240E5A4cEb1CC4</t>
+          <t>https://intel.arkm.com/explorer/address/0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0xf440838830CC265DB72C81bfBa240E5A4cEb1CC4</t>
+          <t>0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7197,48 +7033,68 @@
         </is>
       </c>
       <c r="D107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Lido</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>liquid-staking</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://lido.fi</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Lido Staked Ether Token (STETH)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K107" t="n">
-        <v>21186788.51102374</v>
+        <v>1123518728.743322</v>
       </c>
       <c r="L107" t="n">
-        <v>16534754</v>
+        <v>1093206077.320312</v>
       </c>
       <c r="M107" t="n">
-        <v>1649999.498895133</v>
+        <v>365163.8866300993</v>
       </c>
       <c r="N107" t="n">
-        <v>1239816.64</v>
+        <v>354502.1732189195</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xa6Cc3C2531FdaA6Ae1A3CA84c2855806728693e8</t>
+          <t>https://intel.arkm.com/explorer/address/0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0xa6Cc3C2531FdaA6Ae1A3CA84c2855806728693e8</t>
+          <t>0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7252,24 +7108,12 @@
       <c r="E108" t="b">
         <v>0</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>Wrapped Ether (WETH)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7278,37 +7122,37 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>114301863.7321532</v>
+        <v>20259440632.19843</v>
       </c>
       <c r="L108" t="n">
-        <v>102948106.4250945</v>
+        <v>20366866580.14238</v>
       </c>
       <c r="M108" t="n">
-        <v>8850577.389278222</v>
+        <v>6642242.217483819</v>
       </c>
       <c r="N108" t="n">
-        <v>7982873.473790661</v>
+        <v>6672498.784429797</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-01-12 17:04:43</t>
+          <t>2026-01-12 17:08:09</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>ethereum</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xDdfF0cdb9A67fda3363488140ea3E2159A43c2D4</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0xDdfF0cdb9A67fda3363488140ea3E2159A43c2D4</t>
+          <t>0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7322,39 +7166,457 @@
       <c r="E109" t="b">
         <v>0</v>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>3792115862.31462</v>
+      </c>
+      <c r="L109" t="n">
+        <v>3763358411.55645</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1253444.469917728</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1244145.79143613</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Coinbase Prime</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/prime</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>3158175817.574128</v>
+      </c>
+      <c r="L110" t="n">
+        <v>3166011420.527831</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1031277.4065851</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1035451.67634964</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>2166026395.65625</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2166026369.46875</v>
+      </c>
+      <c r="M111" t="n">
+        <v>705536</v>
+      </c>
+      <c r="N111" t="n">
+        <v>705536</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
           <t>Coinbase Prime Custody</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>evm</t>
         </is>
       </c>
-      <c r="K109" t="n">
-        <v>24048506.95477332</v>
-      </c>
-      <c r="L109" t="n">
-        <v>15380007</v>
-      </c>
-      <c r="M109" t="n">
-        <v>1806049.954646585</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1229169.366962116</v>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:04:43</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>chainlink</t>
+      <c r="K112" t="n">
+        <v>1805690736.550816</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1789915482.375</v>
+      </c>
+      <c r="M112" t="n">
+        <v>594733.0817238287</v>
+      </c>
+      <c r="N112" t="n">
+        <v>589057.6272406335</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D113" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>1702646058.536583</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1702645343.315669</v>
+      </c>
+      <c r="M113" t="n">
+        <v>563496.1170835318</v>
+      </c>
+      <c r="N113" t="n">
+        <v>563495.8795240488</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1077965793.272252</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1069771773.855812</v>
+      </c>
+      <c r="M114" t="n">
+        <v>357123.4331164974</v>
+      </c>
+      <c r="N114" t="n">
+        <v>354504.66386355</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0xb23639385a208265f4891A89C27F37b084532DC3</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0xb23639385a208265f4891A89C27F37b084532DC3</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D115" t="b">
+        <v>0</v>
+      </c>
+      <c r="E115" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>975466362.038294</v>
+      </c>
+      <c r="L115" t="n">
+        <v>975466361.4588983</v>
+      </c>
+      <c r="M115" t="n">
+        <v>323450.2114232946</v>
+      </c>
+      <c r="N115" t="n">
+        <v>323450.2114232946</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://intel.arkm.com/explorer/address/0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+      <c r="E116" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Deposit</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>941419448.3637171</v>
+      </c>
+      <c r="L116" t="n">
+        <v>928499614</v>
+      </c>
+      <c r="M116" t="n">
+        <v>313972.6993268693</v>
+      </c>
+      <c r="N116" t="n">
+        <v>308954.4792646671</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-01-12 17:08:09</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>ethereum</t>
         </is>
       </c>
     </row>

--- a/data_cripto/top_flow.xlsx
+++ b/data_cripto/top_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,94 +513,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qvzgrkefd8v536de2vqhx4d25e5rly7lgk3p2vp</t>
+          <t>https://intel.arkm.com/explorer/address/0x16463c6ce596C91d337495AE699F44D627C8357D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bc1qvzgrkefd8v536de2vqhx4d25e5rly7lgk3p2vp</t>
+          <t>0x16463c6ce596C91d337495AE699F44D627C8357D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kraken</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>1915668582.754017</v>
+        <v>19406606.00152278</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>19561140.5</v>
       </c>
       <c r="M2" t="n">
-        <v>21901.75749903</v>
+        <v>1439999.000112</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1452824</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q9n37v8rdr2tla849xp2znxyp70lnqu8rw0m02a</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bc1q9n37v8rdr2tla849xp2znxyp70lnqu8rw0m02a</t>
+          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -610,345 +594,361 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://coinbase.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1408247624</v>
+        <v>217202021.8592823</v>
       </c>
       <c r="L3" t="n">
-        <v>1741029888</v>
+        <v>216817398.2960736</v>
       </c>
       <c r="M3" t="n">
-        <v>16172.69578732</v>
+        <v>17047341.1926138</v>
       </c>
       <c r="N3" t="n">
-        <v>19908.98001931</v>
+        <v>17020560.66328659</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1p2mlwrss9tmvtfvu0tcxul2h0w67ej8vyjpj3ksctt67vd9r752ksqx6uqm</t>
+          <t>https://intel.arkm.com/explorer/address/0xDdfF0cdb9A67fda3363488140ea3E2159A43c2D4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bc1p2mlwrss9tmvtfvu0tcxul2h0w67ej8vyjpj3ksctt67vd9r752ksqx6uqm</t>
+          <t>0xDdfF0cdb9A67fda3363488140ea3E2159A43c2D4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K4" t="n">
-        <v>833113965.0117188</v>
+        <v>24048506.95477332</v>
       </c>
       <c r="L4" t="n">
-        <v>754659271.2068161</v>
+        <v>15380007</v>
       </c>
       <c r="M4" t="n">
-        <v>9364.59320822</v>
+        <v>1806049.954646585</v>
       </c>
       <c r="N4" t="n">
-        <v>8476.64192532</v>
+        <v>1229169.366962116</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q4d2sd88fht2jsj6k530ga0ck8f8afr9yq4k0u7</t>
+          <t>https://intel.arkm.com/explorer/address/0x5fA0199427243EB13B14409Fb5197e641805c78B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bc1q4d2sd88fht2jsj6k530ga0ck8f8afr9yq4k0u7</t>
+          <t>0x5fA0199427243EB13B14409Fb5197e641805c78B</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Gnosis Safe Proxy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20519058.25</v>
       </c>
       <c r="L5" t="n">
-        <v>645647996</v>
+        <v>19617667.609375</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1521320.56</v>
       </c>
       <c r="N5" t="n">
-        <v>7276.00003787</v>
+        <v>1456373.058080187</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q0d3k8zue8z5ztqt0r35rsd7gua5z4ser6gt46c</t>
+          <t>https://intel.arkm.com/explorer/address/0x3db910Fac1dbE434f397c07c2B473983eFcf25DC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bc1q0d3k8zue8z5ztqt0r35rsd7gua5z4ser6gt46c</t>
+          <t>0x3db910Fac1dbE434f397c07c2B473983eFcf25DC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>2029878574.70939</v>
+        <v>13133860.875</v>
       </c>
       <c r="L6" t="n">
-        <v>2026472876.942573</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>22685.07717914</v>
+        <v>1052392.729393878</v>
       </c>
       <c r="N6" t="n">
-        <v>22657.64460305</v>
+        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3M219KR5vEneNb47ewrPfWyb5jQ2DjxRP6</t>
+          <t>https://intel.arkm.com/explorer/address/0xFAD57d2039C21811C8F2B5D5B65308aa99D31559</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3M219KR5vEneNb47ewrPfWyb5jQ2DjxRP6</t>
+          <t>0xFAD57d2039C21811C8F2B5D5B65308aa99D31559</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://uniswap.org</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>LINK-USDC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1614113024.495659</v>
+        <v>13179087.7193282</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>13127334.08421058</v>
       </c>
       <c r="M7" t="n">
-        <v>18419.33900546</v>
+        <v>1021232.436725803</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1020446.956855342</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qfnv2t4ntuhu52ykp06u6uy3nj7ctm2388cs80e</t>
+          <t>https://intel.arkm.com/explorer/address/0xD50f074Ec5c7997cE1DaacB513Ec194C480878Af</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bc1qfnv2t4ntuhu52ykp06u6uy3nj7ctm2388cs80e</t>
+          <t>0xD50f074Ec5c7997cE1DaacB513Ec194C480878Af</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Gnosis Safe Proxy</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>25535238</v>
       </c>
       <c r="L8" t="n">
-        <v>1412894464</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2024999</v>
       </c>
       <c r="N8" t="n">
-        <v>16450.04551928</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q0y5m6wdxjre0fs9m3u0j3pv2fcja6qw3a2f6ql</t>
+          <t>https://intel.arkm.com/explorer/address/0x651641299C7eC0aA44AD7eD9b7E12702fED2022f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bc1q0y5m6wdxjre0fs9m3u0j3pv2fcja6qw3a2f6ql</t>
+          <t>0x651641299C7eC0aA44AD7eD9b7E12702fED2022f</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -958,663 +958,681 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://bybit.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>20789303.70952347</v>
       </c>
       <c r="L9" t="n">
-        <v>1390938416</v>
+        <v>24857220.30625832</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1611418.109023147</v>
       </c>
       <c r="N9" t="n">
-        <v>15972.00001596</v>
+        <v>1929692.61043282</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1KbDEg1tDz2ErYgaDbaDhhawnLrSQFaFx5</t>
+          <t>https://intel.arkm.com/explorer/address/0xf440838830CC265DB72C81bfBa240E5A4cEb1CC4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1KbDEg1tDz2ErYgaDbaDhhawnLrSQFaFx5</t>
+          <t>0xf440838830CC265DB72C81bfBa240E5A4cEb1CC4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Binance Deposit</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>4333417509.065747</v>
+        <v>21186788.51102374</v>
       </c>
       <c r="L10" t="n">
-        <v>4316835249.657695</v>
+        <v>16534754</v>
       </c>
       <c r="M10" t="n">
-        <v>48634.95698303</v>
+        <v>1649999.498895134</v>
       </c>
       <c r="N10" t="n">
-        <v>48450.59731041</v>
+        <v>1239816.64</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1GrwDkr33gT6LuumniYjKEGjTLhsL5kmqC</t>
+          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1GrwDkr33gT6LuumniYjKEGjTLhsL5kmqC</t>
+          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Kyber Network</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://bybit.com</t>
+          <t>https://kyber.network</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Aggregator Executor V3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2242805250.209483</v>
+        <v>17336292.59719721</v>
       </c>
       <c r="L11" t="n">
-        <v>2247419338.196673</v>
+        <v>17338719.75190102</v>
       </c>
       <c r="M11" t="n">
-        <v>25233.07699274</v>
+        <v>1352184.495463426</v>
       </c>
       <c r="N11" t="n">
-        <v>25286.38075337</v>
+        <v>1352377.712523022</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qr4dl5wa7kl8yu792dceg9z5knl2gkn220lk7a9</t>
+          <t>https://intel.arkm.com/explorer/address/0x35264C7443CB18E22FC3fC0517519E769b644EBD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bc1qr4dl5wa7kl8yu792dceg9z5knl2gkn220lk7a9</t>
+          <t>0x35264C7443CB18E22FC3fC0517519E769b644EBD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Crypto.com</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://crypto.com</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Coinbase Deposit</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1790258067.125271</v>
+        <v>16534754</v>
       </c>
       <c r="L12" t="n">
-        <v>1590476152.710537</v>
+        <v>16525757</v>
       </c>
       <c r="M12" t="n">
-        <v>20125.72405849</v>
+        <v>1239816.64</v>
       </c>
       <c r="N12" t="n">
-        <v>17907.66361606</v>
+        <v>1239816.6401</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1PHpKcFBaUcNadBKEWutz3uMTWKupe8QHq</t>
+          <t>https://intel.arkm.com/explorer/address/0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1PHpKcFBaUcNadBKEWutz3uMTWKupe8QHq</t>
+          <t>0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nonfungible Position Manager</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14660567.20819966</v>
       </c>
       <c r="L13" t="n">
-        <v>711176192</v>
+        <v>15006904.95429163</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1179676.867001697</v>
       </c>
       <c r="N13" t="n">
-        <v>7658.50237493</v>
+        <v>1207587.055316765</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1Pzaqw98PeRfyHypfqyEgg5yycJRsENrE7</t>
+          <t>https://intel.arkm.com/explorer/address/0x177a7376860a04eEA6BF7fb3F39Bf10c49D3b42C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1Pzaqw98PeRfyHypfqyEgg5yycJRsENrE7</t>
+          <t>0x177a7376860a04eEA6BF7fb3F39Bf10c49D3b42C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Blackhole</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+          <t>https://blackhole.xyz/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>262179933.7406256</v>
       </c>
       <c r="L14" t="n">
-        <v>683098676</v>
+        <v>262219154.9168504</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>20401116.02492087</v>
       </c>
       <c r="N14" t="n">
-        <v>7522.0005088</v>
+        <v>20404906.0063914</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qcfkga3lyvflf53vt0n2hjd9mr03870pvjw2z72</t>
+          <t>https://intel.arkm.com/explorer/address/0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bc1qcfkga3lyvflf53vt0n2hjd9mr03870pvjw2z72</t>
+          <t>0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paxos</t>
+          <t>B2C2 Group</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>custodian</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://paxos.com</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Cold Wallet</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+          <t>https://www.b2c2.com</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>24003399.83726284</v>
       </c>
       <c r="L15" t="n">
-        <v>637261120</v>
+        <v>19574642.12304688</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1857918.800906841</v>
       </c>
       <c r="N15" t="n">
-        <v>6757.16150495</v>
+        <v>1547125.794475885</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3FsDiWdG76meMpdCLbVV4dUXhrFyaLrtxL</t>
+          <t>https://intel.arkm.com/explorer/address/0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3FsDiWdG76meMpdCLbVV4dUXhrFyaLrtxL</t>
+          <t>0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K16" t="n">
-        <v>2438636800</v>
+        <v>19629004.43666135</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>20273150.78455508</v>
       </c>
       <c r="M16" t="n">
-        <v>26916.22491951</v>
+        <v>1523763.185222645</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1566978.97891103</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q8wyf76hse8w4dr0qmmapmnuywlpf2upv5are5y9993gdsnvdt97qsem5pp</t>
+          <t>https://intel.arkm.com/explorer/address/0x345366e5142828A66Ee80163b1f30dbE2eAbd566</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bc1q8wyf76hse8w4dr0qmmapmnuywlpf2upv5are5y9993gdsnvdt97qsem5pp</t>
+          <t>0x345366e5142828A66Ee80163b1f30dbE2eAbd566</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K17" t="n">
-        <v>758845248</v>
+        <v>13254146</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8613.649007</v>
+        <v>1062030.95984429</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1FrFvcV3MEkPHViU5tsDNbKwC872xfXL2h</t>
+          <t>https://intel.arkm.com/explorer/address/0x4bD9a84F22bD479f630E2f6c3311285D6eb6B768</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1FrFvcV3MEkPHViU5tsDNbKwC872xfXL2h</t>
+          <t>0x4bD9a84F22bD479f630E2f6c3311285D6eb6B768</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>513114496</v>
+        <v>12826594.625</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5869.3979992</v>
+        <v>978232.900842485</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3KNViZo8uJwnLyxrWed5gRavbPZibEdAq3</t>
+          <t>https://intel.arkm.com/explorer/address/0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3KNViZo8uJwnLyxrWed5gRavbPZibEdAq3</t>
+          <t>0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anchorage Digital</t>
+          <t>CoW Protocol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>custodian</t>
+          <t>dex-aggregator</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.anchorage.com</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>https://cow.fi</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>25526807.42784308</v>
       </c>
       <c r="L19" t="n">
-        <v>985967603.09375</v>
+        <v>25525138.89712205</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1997334.962554621</v>
       </c>
       <c r="N19" t="n">
-        <v>11284.59564648</v>
+        <v>1997205.704562696</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qttmz4kvr8tr6alvmn3zpd5mg53e787rq8v06z0qyqrru4992hsmqxnzkyl</t>
+          <t>https://intel.arkm.com/explorer/address/0xf5213a6a2f0890321712520b8048D9886c1A9900</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bc1qttmz4kvr8tr6alvmn3zpd5mg53e787rq8v06z0qyqrru4992hsmqxnzkyl</t>
+          <t>0xf5213a6a2f0890321712520b8048D9886c1A9900</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
@@ -1624,51 +1642,53 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>23113137.42625093</v>
       </c>
       <c r="L20" t="n">
-        <v>890992256</v>
+        <v>22962400.11697388</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1787250.399245857</v>
       </c>
       <c r="N20" t="n">
-        <v>10113.64902039</v>
+        <v>1773772.35222</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3MqUP6G1daVS5YTD8fz3QgwjZortWwxXFd</t>
+          <t>https://intel.arkm.com/explorer/address/0x5a52E96BAcdaBb82fd05763E25335261B270Efcb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3MqUP6G1daVS5YTD8fz3QgwjZortWwxXFd</t>
+          <t>0x5a52E96BAcdaBb82fd05763E25335261B270Efcb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1678,235 +1698,251 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>12392146220.32094</v>
+        <v>16389601</v>
       </c>
       <c r="L21" t="n">
-        <v>12411872085.79762</v>
+        <v>60951732.25</v>
       </c>
       <c r="M21" t="n">
-        <v>138836.60664855</v>
+        <v>1189376</v>
       </c>
       <c r="N21" t="n">
-        <v>139055.14156168</v>
+        <v>4803824</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q9exg34dkmgxu28yektgn929jpjpzukhhl2r3zr</t>
+          <t>https://intel.arkm.com/explorer/address/0xa42D0A18B834F52e41bEDdEaA2940165db3DA9a3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bc1q9exg34dkmgxu28yektgn929jpjpzukhhl2r3zr</t>
+          <t>0xa42D0A18B834F52e41bEDdEaA2940165db3DA9a3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://chain.link</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Non-Circulating Supply</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1253649135.318622</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1293132826.946991</v>
+        <v>50479988</v>
       </c>
       <c r="M22" t="n">
-        <v>14038.9716853</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>14488.87039104</v>
+        <v>3999999</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3M7VitwPb1NytoSGb9C3TfrfoNPTt5nZqV</t>
+          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3M7VitwPb1NytoSGb9C3TfrfoNPTt5nZqV</t>
+          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K23" t="n">
-        <v>890987712</v>
+        <v>388838618.8703228</v>
       </c>
       <c r="L23" t="n">
-        <v>888248576</v>
+        <v>384595566.8322228</v>
       </c>
       <c r="M23" t="n">
-        <v>10144.91987561</v>
+        <v>30272473.60057416</v>
       </c>
       <c r="N23" t="n">
-        <v>10144.91987561</v>
+        <v>30006323.15754343</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/38ACfxHJwKnKFW2Evmnk58Aj9CBF7t3T88</t>
+          <t>https://intel.arkm.com/explorer/address/0xB1dB79aea0a13382DD9E279d96Bc9a468A2F4E87</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>38ACfxHJwKnKFW2Evmnk58Aj9CBF7t3T88</t>
+          <t>0xB1dB79aea0a13382DD9E279d96Bc9a468A2F4E87</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>574414355.6092997</v>
+        <v>258630504.3165404</v>
       </c>
       <c r="L24" t="n">
-        <v>631692726.9306631</v>
+        <v>258616717.1357428</v>
       </c>
       <c r="M24" t="n">
-        <v>6488.57436362</v>
+        <v>20126137.94290061</v>
       </c>
       <c r="N24" t="n">
-        <v>7096.85830225</v>
+        <v>20125062.2454878</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3P4Fjuyn8SMeMV3SVCLUw88zhTk38aqCB8</t>
+          <t>https://intel.arkm.com/explorer/address/0xa71Dbf81620EFc74E9089b413BC6357D6ad7edaf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3P4Fjuyn8SMeMV3SVCLUw88zhTk38aqCB8</t>
+          <t>0xa71Dbf81620EFc74E9089b413BC6357D6ad7edaf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
@@ -1916,107 +1952,123 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>28171344</v>
       </c>
       <c r="L25" t="n">
-        <v>890987712</v>
+        <v>28216598</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2262758.519376952</v>
       </c>
       <c r="N25" t="n">
-        <v>10144.91999566</v>
+        <v>2262758.519376952</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q7trt2zh5lzd5sap0mqgd246kuq9g0kwg6zhhy3</t>
+          <t>https://intel.arkm.com/explorer/address/0x9c17f630DBde24eECe8fd248fAA2E51f690FF79B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bc1q7trt2zh5lzd5sap0mqgd246kuq9g0kwg6zhhy3</t>
+          <t>0x9c17f630DBde24eECe8fd248fAA2E51f690FF79B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Chainlink</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://chain.link</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Non-Circulating Supply</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2739248825.129715</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2717886038</v>
+        <v>91370238.60000038</v>
       </c>
       <c r="M26" t="n">
-        <v>30536.40046463</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>30327.53268886</v>
+        <v>7249999</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q8s3h3vw5xufdas890q29lpuca56r0ezqar0mvs</t>
+          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bc1q8s3h3vw5xufdas890q29lpuca56r0ezqar0mvs</t>
+          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cumberland DRW</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2026,225 +2078,253 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://cumberland.io</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Market Maker</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K27" t="n">
-        <v>815350081.766449</v>
+        <v>126276076.1211203</v>
       </c>
       <c r="L27" t="n">
-        <v>733927690.8494632</v>
+        <v>126069258.0278089</v>
       </c>
       <c r="M27" t="n">
-        <v>9085.51926313</v>
+        <v>9745795.093062127</v>
       </c>
       <c r="N27" t="n">
-        <v>8174.84360642</v>
+        <v>9725863.032269988</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qsg6x2cvm75xuddn5g0ss9zglaamgz90q8vcp8w</t>
+          <t>https://intel.arkm.com/explorer/address/0x9B1c1752B6B6eAF62a8c491A8681B32C1F7ecDE9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bc1qsg6x2cvm75xuddn5g0ss9zglaamgz90q8vcp8w</t>
+          <t>0x9B1c1752B6B6eAF62a8c491A8681B32C1F7ecDE9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>custodian</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://paxos.com</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Binance Deposit</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K28" t="n">
-        <v>637261120</v>
+        <v>116314976</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>116379500</v>
       </c>
       <c r="M28" t="n">
-        <v>6757.16137194</v>
+        <v>9224998</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>9225000</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1KNm4K8GUK8sMoxc2Z3zU8Uv5FDVjrA72p</t>
+          <t>https://intel.arkm.com/explorer/address/0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1KNm4K8GUK8sMoxc2Z3zU8Uv5FDVjrA72p</t>
+          <t>0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Jump Crypto</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://jumptrading.com</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Market Maker</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K29" t="n">
-        <v>554282389.6969452</v>
+        <v>18744344.71636626</v>
       </c>
       <c r="L29" t="n">
-        <v>677227188.2988281</v>
+        <v>18713528.14398619</v>
       </c>
       <c r="M29" t="n">
-        <v>6224.57347929</v>
+        <v>1460533.54276921</v>
       </c>
       <c r="N29" t="n">
-        <v>7527.63991861</v>
+        <v>1457944.470146326</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3EX1HHEwPtkxitrcYpymHFWu91LNsn8wD4</t>
+          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3EX1HHEwPtkxitrcYpymHFWu91LNsn8wD4</t>
+          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>75972994.53531809</v>
       </c>
       <c r="L30" t="n">
-        <v>884654976</v>
+        <v>76755203.00034046</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5822669.652420743</v>
       </c>
       <c r="N30" t="n">
-        <v>10051.07</v>
+        <v>5879527.71360408</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3JZq4atUahhuA9rLhXLMhhTo133J9rF97j</t>
+          <t>https://intel.arkm.com/explorer/address/0x79dD9327352BcF1dd16941899705E97b61F4DEcB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3JZq4atUahhuA9rLhXLMhhTo133J9rF97j</t>
+          <t>0x79dD9327352BcF1dd16941899705E97b61F4DEcB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bitfinex</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2254,113 +2334,137 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://bitfinex.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>34448267.11122572</v>
       </c>
       <c r="L31" t="n">
-        <v>700752000</v>
+        <v>35643944.31552824</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2707327.399114304</v>
       </c>
       <c r="N31" t="n">
-        <v>8000.00008502</v>
+        <v>2786970.47889152</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/34PhCF947JMQtCn7FD1J3Xd3c2VSxAwda8</t>
+          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>34PhCF947JMQtCn7FD1J3Xd3c2VSxAwda8</t>
+          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Binance Deposit</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K32" t="n">
-        <v>840646976</v>
+        <v>68467747.39763168</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>68496976.63085938</v>
       </c>
       <c r="M32" t="n">
-        <v>9551.069985599999</v>
+        <v>5300003.494641677</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5300003.494641677</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q7cyrfmck2ffu2ud3rn5l5a8yv6f0chkp0zpemf</t>
+          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bc1q7cyrfmck2ffu2ud3rn5l5a8yv6f0chkp0zpemf</t>
+          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crypto.com</t>
+          <t>Coinbase Prime</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2370,7 +2474,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://crypto.com</t>
+          <t>https://www.coinbase.com/prime</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2380,115 +2484,127 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1543277924.057187</v>
+        <v>52032983.21669315</v>
       </c>
       <c r="L33" t="n">
-        <v>1659599051.558694</v>
+        <v>52029688.80140877</v>
       </c>
       <c r="M33" t="n">
-        <v>17361.00957206</v>
+        <v>4097981.268737036</v>
       </c>
       <c r="N33" t="n">
-        <v>18641.03400396</v>
+        <v>4097870.976269291</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qzzfkyk3z94fhk26fu545fchk5v947ghhjfuc2t</t>
+          <t>https://intel.arkm.com/explorer/address/0x5d4F3C6fA16908609BAC31Ff148Bd002AA6b8c83</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bc1qzzfkyk3z94fhk26fu545fchk5v947ghhjfuc2t</t>
+          <t>0x5d4F3C6fA16908609BAC31Ff148Bd002AA6b8c83</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LINK 2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K34" t="n">
-        <v>1368462592</v>
+        <v>20980780.62362562</v>
       </c>
       <c r="L34" t="n">
-        <v>1363357440</v>
+        <v>20856278.74215865</v>
       </c>
       <c r="M34" t="n">
-        <v>15611.91659811</v>
+        <v>1620712.109504189</v>
       </c>
       <c r="N34" t="n">
-        <v>15611.91659811</v>
+        <v>1612350.212795014</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q42kvqt0e3f27qhd2ucnprarl5ywpuj7tu0h9v2</t>
+          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bc1q42kvqt0e3f27qhd2ucnprarl5ywpuj7tu0h9v2</t>
+          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FalconX</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2498,7 +2614,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://falconx.io/</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2508,115 +2624,115 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1252858640.240402</v>
+        <v>104095106.5184093</v>
       </c>
       <c r="L35" t="n">
-        <v>1200412245.446109</v>
+        <v>93949095.64109012</v>
       </c>
       <c r="M35" t="n">
-        <v>14256.43421203</v>
+        <v>8051733.00265503</v>
       </c>
       <c r="N35" t="n">
-        <v>13640.51676859</v>
+        <v>7276679.69490672</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3JZ3byZy7TTrfy8zdxrm9iqJrdsaZ5CrNw</t>
+          <t>https://intel.arkm.com/explorer/address/0x2B83aaCB0dD973866B563cFb0EF0AEF24B93200b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3JZ3byZy7TTrfy8zdxrm9iqJrdsaZ5CrNw</t>
+          <t>0x2B83aaCB0dD973866B563cFb0EF0AEF24B93200b</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Crypto.com</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://crypto.com</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K36" t="n">
-        <v>727600715.354599</v>
+        <v>22546754.3841916</v>
       </c>
       <c r="L36" t="n">
-        <v>661005746.7650909</v>
+        <v>25562102.421875</v>
       </c>
       <c r="M36" t="n">
-        <v>8190.96423</v>
+        <v>1783210.356187327</v>
       </c>
       <c r="N36" t="n">
-        <v>7406.96123</v>
+        <v>2006886.552708601</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qjcm02r55a90v88xwe4alew4y4uyft2htvnywv2</t>
+          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bc1qjcm02r55a90v88xwe4alew4y4uyft2htvnywv2</t>
+          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2626,179 +2742,169 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://robinhood.com/</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>82361081.56773783</v>
       </c>
       <c r="L37" t="n">
-        <v>578351338.296875</v>
+        <v>79307599.98178592</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>6387366.921905444</v>
       </c>
       <c r="N37" t="n">
-        <v>6497.17225553</v>
+        <v>6151497.25202778</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/12DezRFkKToAiLTDNru1g7FuvtAWMwCZ7N</t>
+          <t>https://intel.arkm.com/explorer/address/0x628f0371870B0997914b29acE817C2281E4aB268</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12DezRFkKToAiLTDNru1g7FuvtAWMwCZ7N</t>
+          <t>0x628f0371870B0997914b29acE817C2281E4aB268</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>8519351280.572376</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>8517370211.078125</v>
+        <v>13848439.28125</v>
       </c>
       <c r="M38" t="n">
-        <v>94755.14042914999</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>94755.13992915</v>
+        <v>1093628.876695702</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3EaWHFAWjgG7189kFD2P3hrMqt8qgbdrzN</t>
+          <t>https://intel.arkm.com/explorer/address/0x7914663715665dB7BE9B17Af046292A879c06f48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3EaWHFAWjgG7189kFD2P3hrMqt8qgbdrzN</t>
+          <t>0x7914663715665dB7BE9B17Af046292A879c06f48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
-        <v>909467272.0109024</v>
+        <v>15439457.0640564</v>
       </c>
       <c r="L39" t="n">
-        <v>879535382</v>
+        <v>15439457.0640564</v>
       </c>
       <c r="M39" t="n">
-        <v>10143.97468692</v>
+        <v>1188891.18322697</v>
       </c>
       <c r="N39" t="n">
-        <v>9839.09337852</v>
+        <v>1188891.18322697</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qmakjy7ns2z8vwgptf9vs8fndp304fg0p9xafm2</t>
+          <t>https://intel.arkm.com/explorer/address/0xEff6cb8b614999d130E537751Ee99724D01aA167</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bc1qmakjy7ns2z8vwgptf9vs8fndp304fg0p9xafm2</t>
+          <t>0xEff6cb8b614999d130E537751Ee99724D01aA167</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
@@ -2807,236 +2913,248 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>MEV Bot</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>852237999.390131</v>
+        <v>13356031.31905337</v>
       </c>
       <c r="L40" t="n">
-        <v>752332957.5</v>
+        <v>13374846.82567835</v>
       </c>
       <c r="M40" t="n">
-        <v>9530.16326116</v>
+        <v>1024197.022098323</v>
       </c>
       <c r="N40" t="n">
-        <v>8401.94441846</v>
+        <v>1024596.241967763</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3LUATjKp4YfmCSSiN1h3juwrqNTyksXAjp</t>
+          <t>https://intel.arkm.com/explorer/address/0xD8B671d6f61f40025d8538208a1bD3B57A127805</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3LUATjKp4YfmCSSiN1h3juwrqNTyksXAjp</t>
+          <t>0xD8B671d6f61f40025d8538208a1bD3B57A127805</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Fidelity FBTC ETF Inflows</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://www.fidelity.com/</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FBTC Inflows (Fidelity Custody Deposit)</t>
+          <t>Gnosis Safe Proxy</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>12630000</v>
       </c>
       <c r="L41" t="n">
-        <v>674422062.8809814</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="N41" t="n">
-        <v>7603.32414266</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qactqjuk4kghfgaqqt454hzzzs5lsaysunf80gh</t>
+          <t>https://intel.arkm.com/explorer/address/0x5E8C8A7243651DB1384C0dDfDbE39761E8e7E51a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bc1qactqjuk4kghfgaqqt454hzzzs5lsaysunf80gh</t>
+          <t>0x5E8C8A7243651DB1384C0dDfDbE39761E8e7E51a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Aave</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>lending-decentralized</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://aave.com</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Aave Ethereum LINK (aEthLINK)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K42" t="n">
-        <v>6691793271.210578</v>
+        <v>27438966.90139333</v>
       </c>
       <c r="L42" t="n">
-        <v>6691935318.219632</v>
+        <v>16999564.22702047</v>
       </c>
       <c r="M42" t="n">
-        <v>75160.49887139999</v>
+        <v>2167282.538720507</v>
       </c>
       <c r="N42" t="n">
-        <v>75160.49887140001</v>
+        <v>1330037.131739111</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/335umQ4egqMjDo6wSXYwQZYPntZzMveNTJ</t>
+          <t>https://intel.arkm.com/explorer/address/0xAC64829CDa33bb11C26074CE66E8549e4b8a66A2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>335umQ4egqMjDo6wSXYwQZYPntZzMveNTJ</t>
+          <t>0xAC64829CDa33bb11C26074CE66E8549e4b8a66A2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Custody</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K43" t="n">
-        <v>1478593385.59375</v>
+        <v>22619529.95669994</v>
       </c>
       <c r="L43" t="n">
-        <v>1464197973.625</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>16432.04817912</v>
+        <v>1800871.669636466</v>
       </c>
       <c r="N43" t="n">
-        <v>16264.48841612</v>
+        <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1Kr6QSydW9bFQG1mXiPNNu6WpJGmUa9i1g</t>
+          <t>https://intel.arkm.com/explorer/address/0x7f604D597c15b2e2F60DC645844f68b1D781b752</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1Kr6QSydW9bFQG1mXiPNNu6WpJGmUa9i1g</t>
+          <t>0x7f604D597c15b2e2F60DC645844f68b1D781b752</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bitfinex</t>
+          <t>Bitstamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3046,7 +3164,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://bitfinex.com</t>
+          <t>https://bitstamp.net</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3056,55 +3174,57 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>931750222.3808618</v>
+        <v>12076628.14051428</v>
       </c>
       <c r="L44" t="n">
-        <v>1176093813.754185</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>10618.72915694</v>
+        <v>940434.4009390965</v>
       </c>
       <c r="N44" t="n">
-        <v>13338.28925354</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qx9n80t5q7tfmutzaj0ramzzzsvtveara68zntc</t>
+          <t>https://intel.arkm.com/explorer/address/0xF977814e90dA44bFA03b6295A0616a897441aceC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bc1qx9n80t5q7tfmutzaj0ramzzzsvtveara68zntc</t>
+          <t>0xF977814e90dA44bFA03b6295A0616a897441aceC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3114,609 +3234,699 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://kraken.com</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>5181755569.479836</v>
+        <v>90764924.25</v>
       </c>
       <c r="L45" t="n">
-        <v>5661058696.59375</v>
+        <v>41280000</v>
       </c>
       <c r="M45" t="n">
-        <v>58727.58783513</v>
+        <v>7178890.169000001</v>
       </c>
       <c r="N45" t="n">
-        <v>64186.61890506</v>
+        <v>3000000</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1HDbEPC4ATYM9iebLgyWMwsicSZtYLmnEq</t>
+          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1HDbEPC4ATYM9iebLgyWMwsicSZtYLmnEq</t>
+          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PoolManager</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K46" t="n">
-        <v>504081504</v>
+        <v>53890145.9819918</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>53353440.0549476</v>
       </c>
       <c r="M46" t="n">
-        <v>5869.39809786</v>
+        <v>4225919.641448482</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4173768.908944578</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qk0ukgq09wfuj43lfwrxc3cvcujrk5akvp0lqll</t>
+          <t>https://intel.arkm.com/explorer/address/0xA69babEF1cA67A37Ffaf7a485DfFF3382056e78C</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>bc1qk0ukgq09wfuj43lfwrxc3cvcujrk5akvp0lqll</t>
+          <t>0xA69babEF1cA67A37Ffaf7a485DfFF3382056e78C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Symbolic Capital Partners</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://symbolic.partners</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MEV Bot</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K47" t="n">
-        <v>1530858476</v>
+        <v>15441920.96195602</v>
       </c>
       <c r="L47" t="n">
-        <v>1478899958.034462</v>
+        <v>15485722.70824242</v>
       </c>
       <c r="M47" t="n">
-        <v>16895.22958233</v>
+        <v>1215029.865619221</v>
       </c>
       <c r="N47" t="n">
-        <v>16261.55363876</v>
+        <v>1218006.85231087</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qjasf9z3h7w3jspkhtgatgpyvvzgpa2wwd2lr0eh5tx44reyn2k7sfc27a4</t>
+          <t>https://intel.arkm.com/explorer/address/0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>bc1qjasf9z3h7w3jspkhtgatgpyvvzgpa2wwd2lr0eh5tx44reyn2k7sfc27a4</t>
+          <t>0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tether</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stablecoin</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://tether.to/</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Bitcoin Reserves</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>778702208.4915583</v>
+        <v>47871003.19878235</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>47973848.04608393</v>
       </c>
       <c r="M48" t="n">
-        <v>8888.888894260001</v>
+        <v>3669778.672544983</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3670200.277609042</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3MsfxyCEY5B4NUwKP66iqsbZsS5XRDm3Vj</t>
+          <t>https://intel.arkm.com/explorer/address/0x60030D523A80488e4c5D669E6608022Caba471d9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3MsfxyCEY5B4NUwKP66iqsbZsS5XRDm3Vj</t>
+          <t>0x60030D523A80488e4c5D669E6608022Caba471d9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Binance Deposit</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K49" t="n">
-        <v>713136640</v>
+        <v>21270900.5001344</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>21249335.80026245</v>
       </c>
       <c r="M49" t="n">
-        <v>8144.91996985</v>
+        <v>1589824.00001</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1589844.00003</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1G47mSr3oANXMafVrR8UC4pzV7FEAzo3r9</t>
+          <t>https://intel.arkm.com/explorer/address/0xd312d0403a2196d95BC4eB5BEac60703a93B1944</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1G47mSr3oANXMafVrR8UC4pzV7FEAzo3r9</t>
+          <t>0xd312d0403a2196d95BC4eB5BEac60703a93B1944</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>https://gate.com</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>550576330.3153577</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>13034408</v>
       </c>
       <c r="M50" t="n">
-        <v>6158.99849773</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1024486.356466608</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/3E8T3FPyyd4daRyjQdCNi8WV97v92XvQKu</t>
+          <t>https://intel.arkm.com/explorer/address/0xeFE267E44A58815DD2e319F3b9a679a5202da1ce</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3E8T3FPyyd4daRyjQdCNi8WV97v92XvQKu</t>
+          <t>0xeFE267E44A58815DD2e319F3b9a679a5202da1ce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Gnosis Safe Proxy</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K51" t="n">
-        <v>523105164</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>735605620</v>
+        <v>12630000</v>
       </c>
       <c r="M51" t="n">
-        <v>5949</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>7923.092641</v>
+        <v>1000000</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qptc9cz269u2mc5yguun5a5d6yd5c7f7ne4qj26</t>
+          <t>https://intel.arkm.com/explorer/address/0xa6Cc3C2531FdaA6Ae1A3CA84c2855806728693e8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bc1qptc9cz269u2mc5yguun5a5d6yd5c7f7ne4qj26</t>
+          <t>0xa6Cc3C2531FdaA6Ae1A3CA84c2855806728693e8</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>LINK</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K52" t="n">
-        <v>1408599936.265086</v>
+        <v>114301863.7321532</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>102948106.4250945</v>
       </c>
       <c r="M52" t="n">
-        <v>16400.04538128</v>
+        <v>8850577.389278222</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>7982873.473790661</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1q6ccnyxn32035zwzrlt7z9nkufwrn27d8ezm8xa</t>
+          <t>https://intel.arkm.com/explorer/address/0x835678a611B28684005a5e2233695fB6cbbB0007</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bc1q6ccnyxn32035zwzrlt7z9nkufwrn27d8ezm8xa</t>
+          <t>0x835678a611B28684005a5e2233695fB6cbbB0007</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Cold Wallet</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K53" t="n">
-        <v>830185264</v>
+        <v>19774932.25140645</v>
       </c>
       <c r="L53" t="n">
-        <v>834285328</v>
+        <v>16389601</v>
       </c>
       <c r="M53" t="n">
-        <v>8995.22959506</v>
+        <v>1443824.000102</v>
       </c>
       <c r="N53" t="n">
-        <v>8995.22959506</v>
+        <v>1189376</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/13XJwZdXMh7D4rGd2og4sowZRz4vxNH1LB</t>
+          <t>https://intel.arkm.com/explorer/address/0xA712eF381fA0e8c0733Bd281A17974FBFAeab0b3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13XJwZdXMh7D4rGd2og4sowZRz4vxNH1LB</t>
+          <t>0xA712eF381fA0e8c0733Bd281A17974FBFAeab0b3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Coinbase Deposit</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K54" t="n">
-        <v>711111168</v>
+        <v>14510156.75</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>14499727.25</v>
       </c>
       <c r="M54" t="n">
-        <v>7657.8023727</v>
+        <v>1168734.40484002</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1168734.405206887</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/37GgrfZcywSLuBpQDf1t6aJicWzHRf2GFB</t>
+          <t>https://intel.arkm.com/explorer/address/0x0D0707963952f2fBA59dD06f2b425ace40b492Fe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>37GgrfZcywSLuBpQDf1t6aJicWzHRf2GFB</t>
+          <t>0x0D0707963952f2fBA59dD06f2b425ace40b492Fe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Twenty One Capital</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://xxi.money/</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>https://gate.com</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>14800213.49018702</v>
       </c>
       <c r="L55" t="n">
-        <v>2438727424</v>
+        <v>14440999.72962726</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1147515.815346689</v>
       </c>
       <c r="N55" t="n">
-        <v>26917.22442797</v>
+        <v>1124207.685366812</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qppunwskzl7t3mtmcarlvpxjuzd8jy7l7ga49av2c78xg47fujncsrc76y6</t>
+          <t>https://intel.arkm.com/explorer/address/0x841ed663F2636863D40be4EE76243377dff13a34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bc1qppunwskzl7t3mtmcarlvpxjuzd8jy7l7ga49av2c78xg47fujncsrc76y6</t>
+          <t>0x841ed663F2636863D40be4EE76243377dff13a34</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bitstamp</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3726,133 +3936,117 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://bitstamp.net</t>
+          <t>https://robinhood.com/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1387214137.397675</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1448960083.95829</v>
+        <v>12852238.72442627</v>
       </c>
       <c r="M56" t="n">
-        <v>15532.23774416</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>16216.92452783</v>
+        <v>1013423.50366701</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qn2cpj0hrl37wqh5q94kwrlhtj2lx8ahtw7ef5rg35tswxsqtvufqfmmrq2</t>
+          <t>https://intel.arkm.com/explorer/address/0x7C876bdaA5c038E19F633714f622F6Def949B102</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>bc1qn2cpj0hrl37wqh5q94kwrlhtj2lx8ahtw7ef5rg35tswxsqtvufqfmmrq2</t>
+          <t>0x7C876bdaA5c038E19F633714f622F6Def949B102</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
-        <v>1051530232.55556</v>
+        <v>47250057.32232746</v>
       </c>
       <c r="L57" t="n">
-        <v>1026853849.833294</v>
+        <v>47260034.796875</v>
       </c>
       <c r="M57" t="n">
-        <v>11738.0355311</v>
+        <v>3715883.819405941</v>
       </c>
       <c r="N57" t="n">
-        <v>11472.53813037</v>
+        <v>3715882.828758016</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/324H9uyTV9bPgAVgmdJNxPKKKZmowk5CYq</t>
+          <t>https://intel.arkm.com/explorer/address/0x09ad18BD5D19d6893444B73b6245eC55319F046c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>324H9uyTV9bPgAVgmdJNxPKKKZmowk5CYq</t>
+          <t>0x09ad18BD5D19d6893444B73b6245eC55319F046c</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bullish.com</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3862,199 +4056,217 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://bullish.com/</t>
+          <t>https://coinbase.com</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Cold Wallet</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>633025663.25</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>12958983</v>
       </c>
       <c r="M58" t="n">
-        <v>7081.68847928</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1035062.502286183</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:15</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>chainlink</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/36YZXcTVLPdyapYuqXdJEt46oMVB2NrzVv</t>
+          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>36YZXcTVLPdyapYuqXdJEt46oMVB2NrzVv</t>
+          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Coinbase Prime</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/prime</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Coinbase Prime Deposit</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2056327465.400953</v>
+        <v>65041331.28089902</v>
       </c>
       <c r="L59" t="n">
-        <v>1997158098</v>
+        <v>65265554.94469833</v>
       </c>
       <c r="M59" t="n">
-        <v>23083.18547267</v>
+        <v>412752.7683716223</v>
       </c>
       <c r="N59" t="n">
-        <v>22444.11152656</v>
+        <v>412133.5571044118</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1quhruqrghgcca950rvhtrg7cpd7u8k6svpzgzmrjy8xyukacl5lkq0r8l2d</t>
+          <t>https://intel.arkm.com/explorer/address/0x5aB53EE1d50eeF2C1DD3d5402789cd27bB52c1bB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bc1quhruqrghgcca950rvhtrg7cpd7u8k6svpzgzmrjy8xyukacl5lkq0r8l2d</t>
+          <t>0x5aB53EE1d50eeF2C1DD3d5402789cd27bB52c1bB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
+          <t>https://uniswap.org</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>AAVE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>2378584146.543148</v>
+        <v>64199458.04150783</v>
       </c>
       <c r="L60" t="n">
-        <v>2371067480.086669</v>
+        <v>60665852.02735433</v>
       </c>
       <c r="M60" t="n">
-        <v>26761.81325754</v>
+        <v>383898.9764864586</v>
       </c>
       <c r="N60" t="n">
-        <v>26647.71028181</v>
+        <v>366355.1145627068</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/12XZMdaAGmcHf4ocFSqpd8jFd1WH7RHUPs</t>
+          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12XZMdaAGmcHf4ocFSqpd8jFd1WH7RHUPs</t>
+          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://bybit.com</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4064,251 +4276,235 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>2354140692.926308</v>
+        <v>50693442.19249003</v>
       </c>
       <c r="L61" t="n">
-        <v>2364741185.374374</v>
+        <v>51139307.30533504</v>
       </c>
       <c r="M61" t="n">
-        <v>26424.7920326</v>
+        <v>305041.0856406344</v>
       </c>
       <c r="N61" t="n">
-        <v>26544.55604981</v>
+        <v>309448.85035</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/352zzNHvsBTaUUNzqB5xbMo8EYdpvHJQB2</t>
+          <t>https://intel.arkm.com/explorer/address/0xA700b4eB416Be35b2911fd5Dee80678ff64fF6C9</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>352zzNHvsBTaUUNzqB5xbMo8EYdpvHJQB2</t>
+          <t>0xA700b4eB416Be35b2911fd5Dee80678ff64fF6C9</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>lending-decentralized</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>https://aave.com</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Aave Ethereum AAVE (aEthAAVE)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K62" t="n">
-        <v>6691920926.439903</v>
+        <v>33286446.09031866</v>
       </c>
       <c r="L62" t="n">
-        <v>6698443988.354437</v>
+        <v>37279145.17628589</v>
       </c>
       <c r="M62" t="n">
-        <v>75160.33694707</v>
+        <v>200326.1723389574</v>
       </c>
       <c r="N62" t="n">
-        <v>75224.13043725</v>
+        <v>224543.1809807224</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/1DLeNApsHNNzUMNZJVoXeyEY5sdp8vzx3w</t>
+          <t>https://intel.arkm.com/explorer/address/0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1DLeNApsHNNzUMNZJVoXeyEY5sdp8vzx3w</t>
+          <t>0xfBd4cdB413E45a52E2C8312f670e9cE67E794C37</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>https://bybit.com</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
-        <v>2394592469.560097</v>
+        <v>24379030.09971517</v>
       </c>
       <c r="L63" t="n">
-        <v>2401719580.873917</v>
+        <v>24369460.78646171</v>
       </c>
       <c r="M63" t="n">
-        <v>26902.33768776</v>
+        <v>144103.0099651756</v>
       </c>
       <c r="N63" t="n">
-        <v>26988.39510686</v>
+        <v>144240.214161047</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/15DomY3arDPw5jD658Mbf3AY3wT3YCDmW2</t>
+          <t>https://intel.arkm.com/explorer/address/0xC17A40852E4BfE04Bc81Af355Fdf132C539bA753</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15DomY3arDPw5jD658Mbf3AY3wT3YCDmW2</t>
+          <t>0xC17A40852E4BfE04Bc81Af355Fdf132C539bA753</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1594027023.150391</v>
+        <v>11287022.92022675</v>
       </c>
       <c r="L64" t="n">
-        <v>1688945221.837891</v>
+        <v>11089437.859375</v>
       </c>
       <c r="M64" t="n">
-        <v>17812.92640014</v>
+        <v>68605.86506391646</v>
       </c>
       <c r="N64" t="n">
-        <v>18855.98617503</v>
+        <v>68255.42206391646</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/bc1qm34lsc65zpw79lxes69zkqmk6ee3ewf0j77s3h</t>
+          <t>https://intel.arkm.com/explorer/address/0xAD85405cbB1476825B78a021fa9E543bF7937549</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bc1qm34lsc65zpw79lxes69zkqmk6ee3ewf0j77s3h</t>
+          <t>0xAD85405cbB1476825B78a021fa9E543bF7937549</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bitcoin</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4318,7 +4514,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://bybit.com</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4328,41 +4524,41 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>evm</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>15521368580.2511</v>
+        <v>24444306.43977574</v>
       </c>
       <c r="L65" t="n">
-        <v>15662862954.2443</v>
+        <v>22060614.44546628</v>
       </c>
       <c r="M65" t="n">
-        <v>174385.69436206</v>
+        <v>150624.8441244085</v>
       </c>
       <c r="N65" t="n">
-        <v>175892.51344249</v>
+        <v>134346.86686649</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-01-12 17:07:35</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>bitcoin</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
+          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4378,22 +4574,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kyber Network</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
+          <t>https://kyber.network</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Aggregator Executor V3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4402,37 +4598,37 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>6522565939.249249</v>
+        <v>17835434.72880337</v>
       </c>
       <c r="L66" t="n">
-        <v>6544378730.909774</v>
+        <v>17834591.16593454</v>
       </c>
       <c r="M66" t="n">
-        <v>2152167.118176993</v>
+        <v>109786.6615301793</v>
       </c>
       <c r="N66" t="n">
-        <v>2159928.146616589</v>
+        <v>109781.5540567412</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>https://intel.arkm.com/explorer/address/0xC30F6eE36a1746DD71C7E81529EEae7Ce2f52252</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
+          <t>0xC30F6eE36a1746DD71C7E81529EEae7Ce2f52252</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4446,63 +4642,43 @@
       <c r="E67" t="b">
         <v>0</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Market Maker</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
-        <v>3062792793.929688</v>
+        <v>17168900.25</v>
       </c>
       <c r="L67" t="n">
-        <v>3062702168.987412</v>
+        <v>17233665.7578125</v>
       </c>
       <c r="M67" t="n">
-        <v>1011451.927096179</v>
+        <v>99926.74939270625</v>
       </c>
       <c r="N67" t="n">
-        <v>1011445.098873791</v>
+        <v>100325.2573139125</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>https://intel.arkm.com/explorer/address/0x4A4aaA0155237881FBD5C34BfaE16e985A7B068D</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xCD531Ae9EFCCE479654c4926dec5F6209531Ca7b</t>
+          <t>0x4A4aaA0155237881FBD5C34BfaE16e985A7B068D</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4518,7 +4694,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4528,7 +4704,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
+          <t>https://okx.com</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4542,37 +4718,37 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>2526004292.352442</v>
+        <v>15011196.39321142</v>
       </c>
       <c r="L68" t="n">
-        <v>2520657881.674536</v>
+        <v>14808004.47106934</v>
       </c>
       <c r="M68" t="n">
-        <v>838106.0445600834</v>
+        <v>91223.50703274569</v>
       </c>
       <c r="N68" t="n">
-        <v>836593.2035643058</v>
+        <v>90398.03651497001</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
+          <t>https://intel.arkm.com/explorer/address/0x0e240e9A7B40aD11Fdd69f952bA3Bbd29a238BbD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x4752ba5DBc23f44D87826276BF6Fd6b1C372aD24</t>
+          <t>0x0e240e9A7B40aD11Fdd69f952bA3Bbd29a238BbD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4581,29 +4757,17 @@
         </is>
       </c>
       <c r="D69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Quoter</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4612,37 +4776,37 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>1816065916.698018</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1816066438.763736</v>
+        <v>23886750</v>
       </c>
       <c r="M69" t="n">
-        <v>596847.9614221724</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>596848.1282641541</v>
+        <v>156000.20005</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
+          <t>https://intel.arkm.com/explorer/address/0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x4976A4A02f38326660D17bf34b431dC6e2eb2327</t>
+          <t>0x9008D19f58AAbD9eD0D60971565AA8510560ab41</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4651,29 +4815,29 @@
         </is>
       </c>
       <c r="D70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>CoW Protocol</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex-aggregator</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://cow.fi</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Settlement</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4682,37 +4846,37 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1316808887.357698</v>
+        <v>129770220.8091253</v>
       </c>
       <c r="L70" t="n">
-        <v>1326097428.843616</v>
+        <v>129769975.1219842</v>
       </c>
       <c r="M70" t="n">
-        <v>434123.9310645718</v>
+        <v>779613.9414329217</v>
       </c>
       <c r="N70" t="n">
-        <v>437033.67578649</v>
+        <v>779599.7701927786</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>https://intel.arkm.com/explorer/address/0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x63242A4Ea82847b20E506b63B0e2e2eFF0CC6cB0</t>
+          <t>0xBEE3211ab312a8D065c4FeF0247448e17A8da000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4726,24 +4890,12 @@
       <c r="E71" t="b">
         <v>0</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Kyber Network</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>https://kyber.network</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Aggregator Executor V3</t>
+          <t>Market Maker</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4752,37 +4904,37 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1107493467.150809</v>
+        <v>25614300.97116536</v>
       </c>
       <c r="L71" t="n">
-        <v>1107947262.514511</v>
+        <v>25687248.41824517</v>
       </c>
       <c r="M71" t="n">
-        <v>362895.9410975733</v>
+        <v>156879.0726592117</v>
       </c>
       <c r="N71" t="n">
-        <v>363045.7600727631</v>
+        <v>157307.5587221999</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
+          <t>https://intel.arkm.com/explorer/address/0xF72d6A06Ea0066dc9694156Ca544F5d463a26bf4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
+          <t>0xF72d6A06Ea0066dc9694156Ca544F5d463a26bf4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4791,68 +4943,48 @@
         </is>
       </c>
       <c r="D72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Binance Deposit</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>4631714624.43821</v>
+        <v>18258227.953125</v>
       </c>
       <c r="L72" t="n">
-        <v>4633020367.695312</v>
+        <v>18365079.90625</v>
       </c>
       <c r="M72" t="n">
-        <v>1527482.304299085</v>
+        <v>110389.3342385961</v>
       </c>
       <c r="N72" t="n">
-        <v>1527427.73981932</v>
+        <v>111029.7415213561</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
+          <t>https://intel.arkm.com/explorer/address/0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xb5d85CBf7cB3EE0D56b3bB207D5Fc4B82f43F511</t>
+          <t>0xC333E80eF2deC2805F239E3f1e810612D294F771</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4868,61 +5000,53 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>B2C2 Group</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://coinbase.com</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://www.b2c2.com</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
-        <v>3368447720.767656</v>
+        <v>12261828.89010045</v>
       </c>
       <c r="L73" t="n">
-        <v>3349778437.088505</v>
+        <v>13696612.2166748</v>
       </c>
       <c r="M73" t="n">
-        <v>1112682.88413621</v>
+        <v>71935.19852265104</v>
       </c>
       <c r="N73" t="n">
-        <v>1105927.641922176</v>
+        <v>82621.63880818005</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>https://intel.arkm.com/explorer/address/0x0BB7a4Fdea32910038DEc59c20ccAe3a6E66b09f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
+          <t>0x0BB7a4Fdea32910038DEc59c20ccAe3a6E66b09f</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4931,68 +5055,48 @@
         </is>
       </c>
       <c r="D74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
-        <v>1380449619.705878</v>
+        <v>7326132.582962036</v>
       </c>
       <c r="L74" t="n">
-        <v>1362671509.547991</v>
+        <v>7326132.542770261</v>
       </c>
       <c r="M74" t="n">
-        <v>453489.1777541857</v>
+        <v>44771.0441099437</v>
       </c>
       <c r="N74" t="n">
-        <v>448556.73441576</v>
+        <v>44771.04400404834</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
+          <t>https://intel.arkm.com/explorer/address/0x33fcf9c2c057b3d4e16F2eef8296a3f97B61d4d6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xB0A27099582833c0Cb8C7A0565759fF145113d64</t>
+          <t>0x33fcf9c2c057b3d4e16F2eef8296a3f97B61d4d6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5006,24 +5110,12 @@
       <c r="E75" t="b">
         <v>0</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Cold Wallet</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5032,37 +5124,37 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>1293343038.434332</v>
+        <v>12216604.6111277</v>
       </c>
       <c r="L75" t="n">
-        <v>1324391575.568359</v>
+        <v>9545697</v>
       </c>
       <c r="M75" t="n">
-        <v>429238.3701466272</v>
+        <v>74781.05557799786</v>
       </c>
       <c r="N75" t="n">
-        <v>438759.19883991</v>
+        <v>58846.4902698841</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
+          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xbD216513d74C8cf14cf4747E6AaA6420FF64ee9e</t>
+          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5071,29 +5163,29 @@
         </is>
       </c>
       <c r="D76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://uniswap.org</t>
+          <t>https://binance.com</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Uniswap v4 Positions NFT (UNI-V4-POSM)</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5102,37 +5194,37 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1193275638.45775</v>
+        <v>135821899.8161055</v>
       </c>
       <c r="L76" t="n">
-        <v>1193275638.115657</v>
+        <v>137556567.2007458</v>
       </c>
       <c r="M76" t="n">
-        <v>394289.2296557389</v>
+        <v>825305.1581284256</v>
       </c>
       <c r="N76" t="n">
-        <v>394289.2296557389</v>
+        <v>832608.55076638</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
+          <t>https://intel.arkm.com/explorer/address/0xd85A69Ec2C7A0d42E599519c574b15571F3C60CA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xB38e8c17e38363aF6EbdCb3dAE12e0243582891D</t>
+          <t>0xd85A69Ec2C7A0d42E599519c574b15571F3C60CA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5146,24 +5238,12 @@
       <c r="E77" t="b">
         <v>0</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Coinbase Prime Custody</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5172,37 +5252,37 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1173967760.719858</v>
+        <v>28224716.9190239</v>
       </c>
       <c r="L77" t="n">
-        <v>1270163981.644237</v>
+        <v>18313278.6875</v>
       </c>
       <c r="M77" t="n">
-        <v>386660.557370076</v>
+        <v>179781.7323103313</v>
       </c>
       <c r="N77" t="n">
-        <v>418910.38675825</v>
+        <v>113197.3437390483</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x000000000004444c5dc75cB358380D2e3dE08A90</t>
+          <t>https://intel.arkm.com/explorer/address/0x8f85D8d9d232883d63c992DFf303C10DDA2e428F</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x000000000004444c5dc75cB358380D2e3dE08A90</t>
+          <t>0x8f85D8d9d232883d63c992DFf303C10DDA2e428F</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5211,29 +5291,17 @@
         </is>
       </c>
       <c r="D78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Uniswap</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>dex</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>https://uniswap.org</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PoolManager</t>
+          <t>HitBTC Deposit</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5242,37 +5310,37 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>3174969695.376192</v>
+        <v>18839898.13611194</v>
       </c>
       <c r="L78" t="n">
-        <v>3166875855.470942</v>
+        <v>18872064.39892578</v>
       </c>
       <c r="M78" t="n">
-        <v>1047880.449141952</v>
+        <v>114597.4496126732</v>
       </c>
       <c r="N78" t="n">
-        <v>1045395.793743831</v>
+        <v>114202.0696026732</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
+          <t>https://intel.arkm.com/explorer/address/0x80787af194C33b74a811f5e5c549316269d7Ee1A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x9696f59E4d72E237BE84fFD425DCaD154Bf96976</t>
+          <t>0x80787af194C33b74a811f5e5c549316269d7Ee1A</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5288,7 +5356,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>HitBTC</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5298,7 +5366,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://hitbtc.com</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5312,37 +5380,37 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>1344068978.838293</v>
+        <v>17872908.30516368</v>
       </c>
       <c r="L79" t="n">
-        <v>1328928020.547524</v>
+        <v>18064155.43359375</v>
       </c>
       <c r="M79" t="n">
-        <v>442305.5390923287</v>
+        <v>108056.6874525968</v>
       </c>
       <c r="N79" t="n">
-        <v>437842.39226071</v>
+        <v>110819.7566118507</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
+          <t>https://intel.arkm.com/explorer/address/0x7D94077f58593F8b97c5cAB56c8924E13b49946E</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xF17ACEd3c7A8DAA29ebb90Db8D1b6efD8C364a18</t>
+          <t>0x7D94077f58593F8b97c5cAB56c8924E13b49946E</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5358,7 +5426,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Kraken</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5368,12 +5436,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://kraken.com</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Eth2 Staking</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5382,37 +5450,37 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>15818051.81690161</v>
       </c>
       <c r="L80" t="n">
-        <v>1110263200</v>
+        <v>16411178.72861157</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>99618.440801886</v>
       </c>
       <c r="N80" t="n">
-        <v>360000</v>
+        <v>102430.65650883</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
+          <t>https://intel.arkm.com/explorer/address/0xBA12222222228d8Ba445958a75a0704d566BF2C8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
+          <t>0xBA12222222228d8Ba445958a75a0704d566BF2C8</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5421,29 +5489,29 @@
         </is>
       </c>
       <c r="D81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FalconX</t>
+          <t>Balancer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://falconx.io/</t>
+          <t>https://balancer.fi</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Vault</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5452,37 +5520,37 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>996835501.585402</v>
+        <v>42989215.93569303</v>
       </c>
       <c r="L81" t="n">
-        <v>913513631.0803859</v>
+        <v>38187386.26613178</v>
       </c>
       <c r="M81" t="n">
-        <v>337423.6618982208</v>
+        <v>258310.6169426625</v>
       </c>
       <c r="N81" t="n">
-        <v>309146.26829891</v>
+        <v>228892.5518474707</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
+          <t>https://intel.arkm.com/explorer/address/0x5A1b2aCd0c9992e14F2b6d8a326023E35a097A3a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x3304E22DDaa22bCdC5fCa2269b418046aE7b566A</t>
+          <t>0x5A1b2aCd0c9992e14F2b6d8a326023E35a097A3a</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5491,29 +5559,29 @@
         </is>
       </c>
       <c r="D82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>0x</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://binance.com</t>
+          <t>https://0x.org</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>MainnetSettler</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5522,37 +5590,37 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>947683471.8005881</v>
+        <v>41206215.71718927</v>
       </c>
       <c r="L82" t="n">
-        <v>927957507.0837395</v>
+        <v>41206215.55362017</v>
       </c>
       <c r="M82" t="n">
-        <v>314588.904508293</v>
+        <v>246810.8715642646</v>
       </c>
       <c r="N82" t="n">
-        <v>305710.772442</v>
+        <v>246810.8715642646</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x4200000000000000000000000000000000000006</t>
+          <t>https://intel.arkm.com/explorer/address/0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x4200000000000000000000000000000000000006</t>
+          <t>0x91D40E4818F4D4C57b4578d9ECa6AFc92aC8DEbE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5566,43 +5634,63 @@
       <c r="E83" t="b">
         <v>0</v>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://okx.com</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K83" t="n">
-        <v>5488477326.124804</v>
+        <v>14847004.20944018</v>
       </c>
       <c r="L83" t="n">
-        <v>5475374837.41299</v>
+        <v>14389143.62116385</v>
       </c>
       <c r="M83" t="n">
-        <v>1811581.583997438</v>
+        <v>91299.52459177992</v>
       </c>
       <c r="N83" t="n">
-        <v>1807661.347392329</v>
+        <v>89256.52128335</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
+          <t>https://intel.arkm.com/explorer/address/0xE91B373212f8aE32925CbCf39AB3a7B0763C27C9</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x0003B5Aa5E30E97FcC596BB5D0F3A75255E08D4e</t>
+          <t>0xE91B373212f8aE32925CbCf39AB3a7B0763C27C9</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5616,24 +5704,12 @@
       <c r="E84" t="b">
         <v>0</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5642,37 +5718,37 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>3312587733.3741</v>
+        <v>13363217.90536661</v>
       </c>
       <c r="L84" t="n">
-        <v>3152875530.776313</v>
+        <v>12717098.3984375</v>
       </c>
       <c r="M84" t="n">
-        <v>1097564.703663301</v>
+        <v>82338.11461266951</v>
       </c>
       <c r="N84" t="n">
-        <v>1045229.99456863</v>
+        <v>78654.4303276695</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>https://intel.arkm.com/explorer/address/0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xf8191D98ae98d2f7aBDFB63A9b0b812b93C873AA</t>
+          <t>0x1157A2076b9bB22a85CC2C162f20fAB3898F4101</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5688,17 +5764,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wintermute</t>
+          <t>FalconX</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cex</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.wintermute.com/</t>
+          <t>https://falconx.io/</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5712,37 +5788,37 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>1828583320.51047</v>
+        <v>10507022.22328352</v>
       </c>
       <c r="L85" t="n">
-        <v>1817198543.676425</v>
+        <v>10724260.90294695</v>
       </c>
       <c r="M85" t="n">
-        <v>600960.0841306447</v>
+        <v>66087.94986831218</v>
       </c>
       <c r="N85" t="n">
-        <v>597144.7303148605</v>
+        <v>64895.80447279</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
+          <t>https://intel.arkm.com/explorer/address/0x3cf2E61F85A95fC964C1ad9D8208D069f5Cf2bc8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x131bf4Cc1E4C60734B64e908D35f0F5cB9727dc7</t>
+          <t>0x3cf2E61F85A95fC964C1ad9D8208D069f5Cf2bc8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5762,37 +5838,37 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
-        <v>1796617438.186003</v>
+        <v>45853847.77490953</v>
       </c>
       <c r="L86" t="n">
-        <v>1796617436.308729</v>
+        <v>45824204.30992083</v>
       </c>
       <c r="M86" t="n">
-        <v>594652.6468261391</v>
+        <v>280877.096942142</v>
       </c>
       <c r="N86" t="n">
-        <v>594652.6468261391</v>
+        <v>280667.5984426902</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
+          <t>https://intel.arkm.com/explorer/address/0x8A6d3630928802e157595eE18d6D10A4cd4fAB0D</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x3606f0F14828cBF4962A284a4bFF93Bc94b63665</t>
+          <t>0x8A6d3630928802e157595eE18d6D10A4cd4fAB0D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5809,48 +5885,40 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Coinbase Prime Custody</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
-        <v>1539116512.23613</v>
+        <v>10685062.625</v>
       </c>
       <c r="L87" t="n">
-        <v>1468841741</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>507035.1332085576</v>
+        <v>68731.90945583291</v>
       </c>
       <c r="N87" t="n">
-        <v>486483.7066143855</v>
+        <v>0</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
+          <t>https://intel.arkm.com/explorer/address/0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x308861A430be4cce5502d0A12724771Fc6DaF216</t>
+          <t>0x51C72848c68a965f66FA7a88855F9f7784502a7F</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5866,22 +5934,22 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://ether.fi/</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>LiquidityPool (Proxy)</t>
+          <t>Market Maker</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5890,37 +5958,37 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>1078237598.939264</v>
+        <v>55962005.63759355</v>
       </c>
       <c r="L88" t="n">
-        <v>1075335264.820105</v>
+        <v>55315622.05393706</v>
       </c>
       <c r="M88" t="n">
-        <v>346848.2185119853</v>
+        <v>336290.6018757278</v>
       </c>
       <c r="N88" t="n">
-        <v>356677.2505183262</v>
+        <v>333271.9351651787</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
+          <t>https://intel.arkm.com/explorer/address/0x9bA0CF1588E1DFA905eC948F7FE5104dD40EDa31</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xa217D7d31f95b3c1BA0E0a7394ACCe92a1D566E9</t>
+          <t>0x9bA0CF1588E1DFA905eC948F7FE5104dD40EDa31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5934,43 +6002,59 @@
       <c r="E89" t="b">
         <v>0</v>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TrustedVolumes</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Market Maker</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K89" t="n">
-        <v>3139024069.153679</v>
+        <v>29664205.66925109</v>
       </c>
       <c r="L89" t="n">
-        <v>3139024076.247688</v>
+        <v>29181573.3799693</v>
       </c>
       <c r="M89" t="n">
-        <v>1030681.991847288</v>
+        <v>179360.4861079397</v>
       </c>
       <c r="N89" t="n">
-        <v>1030681.991847288</v>
+        <v>179168.3311440358</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
+          <t>https://intel.arkm.com/explorer/address/0x59c38b6775Ded821f010DbD30eCabdCF84E04756</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x7CcD5095284bc8265301DC0C8b4E9a22f012B1f6</t>
+          <t>0x59c38b6775Ded821f010DbD30eCabdCF84E04756</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5984,43 +6068,63 @@
       <c r="E90" t="b">
         <v>0</v>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>UNI-AAVE 2</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K90" t="n">
-        <v>2984899075.064578</v>
+        <v>8438715.804674095</v>
       </c>
       <c r="L90" t="n">
-        <v>2984899247.759352</v>
+        <v>7989608.231104204</v>
       </c>
       <c r="M90" t="n">
-        <v>938725.8018690519</v>
+        <v>50192.30545940617</v>
       </c>
       <c r="N90" t="n">
-        <v>938725.8573831373</v>
+        <v>48094.06204352286</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
+          <t>https://intel.arkm.com/explorer/address/0x549d835356d92983AbB76E4cae639f7857963425</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x631452Cd3aa391162f0E078f3b0b3d0566D1e13a</t>
+          <t>0x549d835356d92983AbB76E4cae639f7857963425</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6029,7 +6133,7 @@
         </is>
       </c>
       <c r="D91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
@@ -6040,37 +6144,37 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
-        <v>1562000453.175918</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>1561998837.875261</v>
+        <v>7813237.970905304</v>
       </c>
       <c r="M91" t="n">
-        <v>506460.5407311035</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>506460.0250524727</v>
+        <v>44998.01731</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
+          <t>https://intel.arkm.com/explorer/address/0x4da27a545c0c5B758a6BA100e3a049001de870f5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xcD7a6C118Ac8F6544BC5076F2D8Fb86D2C546756</t>
+          <t>0x4da27a545c0c5B758a6BA100e3a049001de870f5</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6084,12 +6188,24 @@
       <c r="E92" t="b">
         <v>0</v>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Aave</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>lending-decentralized</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://aave.com</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BatchDeposit</t>
+          <t>Staked Aave (stkAAVE)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6098,37 +6214,37 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>1545610913.739746</v>
+        <v>20327385.41520842</v>
       </c>
       <c r="L92" t="n">
-        <v>1545878735.992676</v>
+        <v>57796966.31281979</v>
       </c>
       <c r="M92" t="n">
-        <v>504146.34</v>
+        <v>123388.0004989238</v>
       </c>
       <c r="N92" t="n">
-        <v>504235.746</v>
+        <v>334159.6782401801</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>https://intel.arkm.com/explorer/address/0x91bf7e6FFA4608FA2280F81D2B23a8b8FB70b14B</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
+          <t>0x91bf7e6FFA4608FA2280F81D2B23a8b8FB70b14B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6142,63 +6258,43 @@
       <c r="E93" t="b">
         <v>0</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
-        <v>1254014411.370105</v>
+        <v>12406568.10605987</v>
       </c>
       <c r="L93" t="n">
-        <v>1259960331.731031</v>
+        <v>12406568.10361554</v>
       </c>
       <c r="M93" t="n">
-        <v>413614.5619807786</v>
+        <v>69138.3068572881</v>
       </c>
       <c r="N93" t="n">
-        <v>414970.95241538</v>
+        <v>69138.30685728809</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
+          <t>https://intel.arkm.com/explorer/address/0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x00000000219ab540356cBB839Cbe05303d7705Fa</t>
+          <t>0xA9D1e08C7793af67e9d92fe308d5697FB81d3E43</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6212,12 +6308,24 @@
       <c r="E94" t="b">
         <v>0</v>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://coinbase.com</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Eth2 Beacon Deposit Contract</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6226,37 +6334,37 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>9743785746.779785</v>
+        <v>68382611.43131302</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>67955501.11731529</v>
       </c>
       <c r="M94" t="n">
-        <v>3185819.797795997</v>
+        <v>401122.5778898222</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>398248.70054278</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x28C6c06298d514Db089934071355E5743bf21d60</t>
+          <t>https://intel.arkm.com/explorer/address/0xf3fB9691c4BFF980C0352339fb297c5bF52Dd354</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x28C6c06298d514Db089934071355E5743bf21d60</t>
+          <t>0xf3fB9691c4BFF980C0352339fb297c5bF52Dd354</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6270,63 +6378,43 @@
       <c r="E95" t="b">
         <v>0</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
-        <v>9376187036.164282</v>
+        <v>50971792.34091795</v>
       </c>
       <c r="L95" t="n">
-        <v>9091454821.006443</v>
+        <v>50975271.70155907</v>
       </c>
       <c r="M95" t="n">
-        <v>3102964.586759099</v>
+        <v>304211.2624097264</v>
       </c>
       <c r="N95" t="n">
-        <v>3006182.85966278</v>
+        <v>304251.7486101647</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
+          <t>https://intel.arkm.com/explorer/address/0xa923B13270F8622B5d5960634200Dc4302b7611E</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xaF682DE1f2e6f710731121A05A44Cb3C1B511f7d</t>
+          <t>0xa923B13270F8622B5d5960634200Dc4302b7611E</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6343,40 +6431,48 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Gnosis Safe Proxy</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K96" t="n">
-        <v>1920208281.705265</v>
+        <v>40917945.5625</v>
       </c>
       <c r="L96" t="n">
-        <v>1920208272.921999</v>
+        <v>39380708.04328918</v>
       </c>
       <c r="M96" t="n">
-        <v>634951.9741911336</v>
+        <v>231775.4541938402</v>
       </c>
       <c r="N96" t="n">
-        <v>634951.9742317306</v>
+        <v>231770.4148689859</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
+          <t>https://intel.arkm.com/explorer/address/0xe401A6A38024d8f5aB88f1B08cad476cCaCA45E8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x82aF49447D8a07e3bd95BD0d56f35241523fBab1</t>
+          <t>0xe401A6A38024d8f5aB88f1B08cad476cCaCA45E8</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6390,43 +6486,63 @@
       <c r="E97" t="b">
         <v>0</v>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Wintermute</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.wintermute.com/</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Bybit Deposit</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K97" t="n">
-        <v>1621625210.809175</v>
+        <v>12255815.69881986</v>
       </c>
       <c r="L97" t="n">
-        <v>1615197603.046842</v>
+        <v>12250235.046875</v>
       </c>
       <c r="M97" t="n">
-        <v>535150.2837216775</v>
+        <v>74189.981212706</v>
       </c>
       <c r="N97" t="n">
-        <v>532597.2069405273</v>
+        <v>74189.98120865</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
+          <t>https://intel.arkm.com/explorer/address/0x70Fedb8c3cddC74f238DAb098AbF956a17936F39</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xf30ba13e4b04Ce5dC4D254Ae5FA95477800F0EB0</t>
+          <t>0x70Fedb8c3cddC74f238DAb098AbF956a17936F39</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6440,63 +6556,43 @@
       <c r="E98" t="b">
         <v>0</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Kraken</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>https://kraken.com</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
-        <v>1380580877.141225</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>1488601158.993964</v>
+        <v>6238865.84375</v>
       </c>
       <c r="M98" t="n">
-        <v>459867.8170880997</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>492935.4977716298</v>
+        <v>39361.79458921947</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
+          <t>https://intel.arkm.com/explorer/address/0xDDC4eAb490469f073Ab8Cd5937B1a0f585687931</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0xbdAeDf327F5bc552a8479326562F6EfEAB2D8d96</t>
+          <t>0xDDC4eAb490469f073Ab8Cd5937B1a0f585687931</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6510,55 +6606,43 @@
       <c r="E99" t="b">
         <v>0</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Wintermute</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>fund</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
-        <v>918001940.1768073</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>918598516.78125</v>
+        <v>6658000.125</v>
       </c>
       <c r="M99" t="n">
-        <v>302134.900001667</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>302134.9</v>
+        <v>39332.58495218402</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xd01607c3C5eCABa394D8be377a08590149325722</t>
+          <t>https://intel.arkm.com/explorer/address/0xe792b339818Ae6fc4C43C8BEF57352D28E7f7aFb</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0xd01607c3C5eCABa394D8be377a08590149325722</t>
+          <t>0xe792b339818Ae6fc4C43C8BEF57352D28E7f7aFb</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6567,68 +6651,48 @@
         </is>
       </c>
       <c r="D100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Aave</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>lending-decentralized</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>https://aave.com</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>WrappedTokenGatewayV3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
-        <v>3233979215.459034</v>
+        <v>7505042</v>
       </c>
       <c r="L100" t="n">
-        <v>3233979217.135644</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>1078159.414922242</v>
+        <v>43354.17999999999</v>
       </c>
       <c r="N100" t="n">
-        <v>1078159.414922242</v>
+        <v>0</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
+          <t>https://intel.arkm.com/explorer/address/0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0x1f2F10D1C40777AE1Da742455c65828FF36Df387</t>
+          <t>0xDFd5293D8e347dFe59E90eFd55b2956a1343963d</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6637,25 +6701,29 @@
         </is>
       </c>
       <c r="D101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>jaredfromsubway (MEV)</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>mev</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>MEV Bot</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6664,37 +6732,37 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>2429887582.636902</v>
+        <v>44951044.56505139</v>
       </c>
       <c r="L101" t="n">
-        <v>2429887579.240764</v>
+        <v>46008783.03503126</v>
       </c>
       <c r="M101" t="n">
-        <v>802000.1996770022</v>
+        <v>272264.4201498198</v>
       </c>
       <c r="N101" t="n">
-        <v>802000.2012989126</v>
+        <v>279291.77901067</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
+          <t>https://intel.arkm.com/explorer/address/0x47cA539b3F546078d97bD851130741c6bF370100</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x536c4921D1aAfDE6a5cda882fb5cA046f3601c65</t>
+          <t>0x47cA539b3F546078d97bD851130741c6bF370100</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6703,29 +6771,25 @@
         </is>
       </c>
       <c r="D102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Stani Kulechov</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Gnosis Safe Proxy</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6734,37 +6798,37 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>1297623623.14208</v>
+        <v>14636410.97094727</v>
       </c>
       <c r="L102" t="n">
-        <v>1273155395.23965</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>429917.0145423929</v>
+        <v>84032.94725614057</v>
       </c>
       <c r="N102" t="n">
-        <v>422000.60045102</v>
+        <v>0</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
+          <t>https://intel.arkm.com/explorer/address/0x927C6aaA6aAd7aF5252237af8B85be10B2DE0DBB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x6C9Cb54A8E1931F0aB5523e5a54E731BB4a72708</t>
+          <t>0x927C6aaA6aAd7aF5252237af8B85be10B2DE0DBB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6784,37 +6848,37 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>1213036041.498139</v>
+        <v>106019549.926618</v>
       </c>
       <c r="L103" t="n">
-        <v>1213036040.993315</v>
+        <v>106050539.7503563</v>
       </c>
       <c r="M103" t="n">
-        <v>400379.9610025365</v>
+        <v>639106.9701238592</v>
       </c>
       <c r="N103" t="n">
-        <v>400379.9610025365</v>
+        <v>639216.9630778197</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
+          <t>https://intel.arkm.com/explorer/address/0x6A6f987882E0D19aAA1155e96beab1e4a9ed474C</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0xBdD75A97c29294FF805FB2fEe65aBd99492b32A8</t>
+          <t>0x6A6f987882E0D19aAA1155e96beab1e4a9ed474C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6828,63 +6892,43 @@
       <c r="E104" t="b">
         <v>0</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Eth2 Staking</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>1110263200</v>
+        <v>9063341</v>
       </c>
       <c r="L104" t="n">
-        <v>1102789560</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>360000</v>
+        <v>58450.53999999999</v>
       </c>
       <c r="N104" t="n">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
+          <t>https://intel.arkm.com/explorer/address/0x73E4E2726c688A09af7e72107eE92a372EeB3012</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0x25e821b7197B146F7713C3b89B6A4D83516B912d</t>
+          <t>0x73E4E2726c688A09af7e72107eE92a372EeB3012</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6893,29 +6937,17 @@
         </is>
       </c>
       <c r="D105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Ether.fi</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>misc</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>https://ether.fi/</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>StakingManager (Proxy)</t>
+          <t>Coinbase Deposit</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6924,37 +6956,37 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>1024680392</v>
+        <v>8468227.906531449</v>
       </c>
       <c r="L105" t="n">
-        <v>1024680400</v>
+        <v>8464954</v>
       </c>
       <c r="M105" t="n">
-        <v>340000</v>
+        <v>51763.97394</v>
       </c>
       <c r="N105" t="n">
-        <v>340000</v>
+        <v>51763.97394</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
+          <t>https://intel.arkm.com/explorer/address/0x5eE84D30c7EE57F63f71c92247Ff31f95E26916B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0xE69f81b825d7Dc31ee9becef4DbEab5cf30e3Abb</t>
+          <t>0x5eE84D30c7EE57F63f71c92247Ff31f95E26916B</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6968,63 +7000,43 @@
       <c r="E106" t="b">
         <v>0</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>1393302544.028083</v>
+        <v>8096674.170935631</v>
       </c>
       <c r="L106" t="n">
-        <v>1395170004.140732</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>456792.2656770762</v>
+        <v>47370.4370073888</v>
       </c>
       <c r="N106" t="n">
-        <v>457242.1943745955</v>
+        <v>0</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
+          <t>https://intel.arkm.com/explorer/address/0x990636ecB3FF04d33D92e970d3d588bF5cD8d086</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0xae7ab96520DE3A18E5e111B5EaAb095312D7fE84</t>
+          <t>0x990636ecB3FF04d33D92e970d3d588bF5cD8d086</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7038,63 +7050,43 @@
       <c r="E107" t="b">
         <v>0</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Lido</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>liquid-staking</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>https://lido.fi</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Lido Staked Ether Token (STETH)</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>1123518728.743322</v>
+        <v>7282430.563576777</v>
       </c>
       <c r="L107" t="n">
-        <v>1093206077.320312</v>
+        <v>7290536.871422145</v>
       </c>
       <c r="M107" t="n">
-        <v>365163.8866300993</v>
+        <v>45073.76635700264</v>
       </c>
       <c r="N107" t="n">
-        <v>354502.1732189195</v>
+        <v>45123.29227136062</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
+          <t>https://intel.arkm.com/explorer/address/0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0xC02aaA39b223FE8D0A0e5C4F27eAD9083C756Cc2</t>
+          <t>0xC36442b4a4522E871399CD717aBDD847Ab11FE88</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7108,12 +7100,24 @@
       <c r="E108" t="b">
         <v>0</v>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Uniswap</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>dex</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://uniswap.org</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Wrapped Ether (WETH)</t>
+          <t>Nonfungible Position Manager</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7122,37 +7126,37 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>20259440632.19843</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>20366866580.14238</v>
+        <v>6419935.3072404</v>
       </c>
       <c r="M108" t="n">
-        <v>6642242.217483819</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>6672498.784429797</v>
+        <v>41847.30403062452</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
+          <t>https://intel.arkm.com/explorer/address/0x4a79B0168296c0eF7b8F314973B82aD406a29f1B</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0xA9Ac43f5b5e38155A288d1A01D2cbc4478E14573</t>
+          <t>0x4a79B0168296c0eF7b8F314973B82aD406a29f1B</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7168,61 +7172,53 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://okx.com</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
+          <t>https://aerodrome.finance/</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>3792115862.31462</v>
+        <v>217115183.763593</v>
       </c>
       <c r="L109" t="n">
-        <v>3763358411.55645</v>
+        <v>216879298.1866629</v>
       </c>
       <c r="M109" t="n">
-        <v>1253444.469917728</v>
+        <v>1306511.307052288</v>
       </c>
       <c r="N109" t="n">
-        <v>1244145.79143613</v>
+        <v>1305368.277372938</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
+          <t>https://intel.arkm.com/explorer/address/0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0xceB69F6342eCE283b2F5c9088Ff249B5d0Ae66ea</t>
+          <t>0xEae7380dD4CeF6fbD1144F49E4D1e6964258A4F4</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7238,22 +7234,22 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Coinbase Prime</t>
+          <t>Wintermute</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>cex</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/prime</t>
+          <t>https://www.wintermute.com/</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Hot Wallet</t>
+          <t>Binance Deposit</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7262,37 +7258,37 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>3158175817.574128</v>
+        <v>58514406.16923433</v>
       </c>
       <c r="L110" t="n">
-        <v>3166011420.527831</v>
+        <v>58493737.51171875</v>
       </c>
       <c r="M110" t="n">
-        <v>1031277.4065851</v>
+        <v>354572.107293369</v>
       </c>
       <c r="N110" t="n">
-        <v>1035451.67634964</v>
+        <v>354572.107293369</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
+          <t>https://intel.arkm.com/explorer/address/0xA3222357a0eCCF60C73606170be6c99ADeCb59b3</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0x9212f40aB99cdE4F3D72923B849A873A89636DFC</t>
+          <t>0xA3222357a0eCCF60C73606170be6c99ADeCb59b3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7306,43 +7302,63 @@
       <c r="E111" t="b">
         <v>0</v>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HitBTC</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://hitbtc.com</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Hot Wallet</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K111" t="n">
-        <v>2166026395.65625</v>
+        <v>22121695.236926</v>
       </c>
       <c r="L111" t="n">
-        <v>2166026369.46875</v>
+        <v>22139940.38245201</v>
       </c>
       <c r="M111" t="n">
-        <v>705536</v>
+        <v>136646.8711714712</v>
       </c>
       <c r="N111" t="n">
-        <v>705536</v>
+        <v>136845.45605223</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
+          <t>https://intel.arkm.com/explorer/address/0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0xC2BF398B4805893089Ed4Eb4Fa25Cb2E78c0CE87</t>
+          <t>0x21a31Ee1afC51d94C2eFcCAa2092aD1028285549</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7356,12 +7372,24 @@
       <c r="E112" t="b">
         <v>0</v>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>cex</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://binance.com</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Coinbase Prime Custody</t>
+          <t>Hot Wallet</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7370,37 +7398,37 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>1805690736.550816</v>
+        <v>44269518.61017749</v>
       </c>
       <c r="L112" t="n">
-        <v>1789915482.375</v>
+        <v>45898991.04729974</v>
       </c>
       <c r="M112" t="n">
-        <v>594733.0817238287</v>
+        <v>267852.13568369</v>
       </c>
       <c r="N112" t="n">
-        <v>589057.6272406335</v>
+        <v>278172.98877498</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://intel.arkm.com/explorer/address/0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
+          <t>https://intel.arkm.com/explorer/address/0x41a5E4A6c3679CF253D0D0f74251F40D587A518f</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0x1E8540d60a7B34E79DA540FFf2d11bC4ad832f76</t>
+          <t>0x41a5E4A6c3679CF253D0D0f74251F40D587A518f</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7409,7 +7437,7 @@
         </is>
       </c>
       <c r="D113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
@@ -7417,206 +7445,36 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Coinbase Prime Deposit</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>evm</t>
+        </is>
+      </c>
       <c r="K113" t="n">
-        <v>1702646058.536583</v>
+        <v>23886750</v>
       </c>
       <c r="L113" t="n">
-        <v>1702645343.315669</v>
+        <v>23925750</v>
       </c>
       <c r="M113" t="n">
-        <v>563496.1170835318</v>
+        <v>156000.20005</v>
       </c>
       <c r="N113" t="n">
-        <v>563495.8795240488</v>
+        <v>156000.20005</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-01-12 17:08:09</t>
+          <t>2026-01-12 17:10:19</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>0x56Eddb7aa87536c09CCc2793473599fD21A8b17F</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D114" t="b">
-        <v>0</v>
-      </c>
-      <c r="E114" t="b">
-        <v>0</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>cex</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>https://binance.com</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Hot Wallet</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
-        <v>1077965793.272252</v>
-      </c>
-      <c r="L114" t="n">
-        <v>1069771773.855812</v>
-      </c>
-      <c r="M114" t="n">
-        <v>357123.4331164974</v>
-      </c>
-      <c r="N114" t="n">
-        <v>354504.66386355</v>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:08:09</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xb23639385a208265f4891A89C27F37b084532DC3</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>0xb23639385a208265f4891A89C27F37b084532DC3</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D115" t="b">
-        <v>0</v>
-      </c>
-      <c r="E115" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="n">
-        <v>975466362.038294</v>
-      </c>
-      <c r="L115" t="n">
-        <v>975466361.4588983</v>
-      </c>
-      <c r="M115" t="n">
-        <v>323450.2114232946</v>
-      </c>
-      <c r="N115" t="n">
-        <v>323450.2114232946</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:08:09</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://intel.arkm.com/explorer/address/0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>0xC8c557506a5240dcEC094e614C665Ff9CA815b95</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D116" t="b">
-        <v>0</v>
-      </c>
-      <c r="E116" t="b">
-        <v>0</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Coinbase Prime Deposit</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>evm</t>
-        </is>
-      </c>
-      <c r="K116" t="n">
-        <v>941419448.3637171</v>
-      </c>
-      <c r="L116" t="n">
-        <v>928499614</v>
-      </c>
-      <c r="M116" t="n">
-        <v>313972.6993268693</v>
-      </c>
-      <c r="N116" t="n">
-        <v>308954.4792646671</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>2026-01-12 17:08:09</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>ethereum</t>
+          <t>aave</t>
         </is>
       </c>
     </row>
